--- a/naver-place-crawler/results_nail/종로_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/종로_네일샵.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -1210,6 +1210,9882 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>오브 코코네일</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1371-8921</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ofconail</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>651</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>47</v>
+      </c>
+      <c r="R9" t="n">
+        <v>698</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1009626425</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1009626425</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>에이커뷰티네일</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>happymin_life@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>02-722-5558</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>http://instagram.com/acre_beauty</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>120</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1812848399</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1812848399</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>레푸스 종로점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>refuss_jong_ro@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>chy0802@ahasoft.co.kr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>02-720-4544</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/13/bizes/857013</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>856</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>359</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1215</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1237692187</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1237692187</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JIN네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jin_nail6453@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1392-5159</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>65</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1530291597</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1530291597</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>다리아네일 안국역</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>puppyholic@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1347-1494</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/daria_nail_ssu</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>185</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1165184706</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1165184706</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>키튼네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dbgpwn0626@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02-765-8566</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>470</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>54</v>
+      </c>
+      <c r="R14" t="n">
+        <v>524</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1065031131</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1065031131</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>네일 을지로지하쇼핑센터3구역점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02-2278-2990</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>37588249</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37588249</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>디디 네일바</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>heeja090@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1476-0228</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/didi___nailbar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>24</v>
+      </c>
+      <c r="R16" t="n">
+        <v>217</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1134899134</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134899134</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>네일리</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>happyjj163@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1358-8653</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_lee____</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9</v>
+      </c>
+      <c r="R17" t="n">
+        <v>109</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2065943871</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2065943871</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>지호네일</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>yongsanly@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1314-5759</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 265 5층,6층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jihonail</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1285361463</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1285361463</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>네일쏘이</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>annoi_@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1334-9677</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailssoi_</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>55</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1009120766</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1009120766</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>영심이손톱</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>lovellies@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02-735-0031</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 88 701호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1116851430</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1116851430</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>엔79 Nail</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>tmsla_zz@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1390-0326</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>19</v>
+      </c>
+      <c r="R21" t="n">
+        <v>182</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1756267523</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1756267523</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>안젤라네일샵</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>angella3977@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1493-3335</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/angella3977</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>658</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11</v>
+      </c>
+      <c r="R22" t="n">
+        <v>669</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1274163754</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1274163754</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>오드리네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ardusy@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>02-722-1384</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/audreynail_official</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>257</v>
+      </c>
+      <c r="R23" t="n">
+        <v>484</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>13450587</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13450587</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>네일멜로우</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>qnlwls@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1356-7672</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_mellow_11/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>387</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>34</v>
+      </c>
+      <c r="R24" t="n">
+        <v>421</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1933958367</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1933958367</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>나비네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>052young@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>02-319-7844</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>http://instagram.com/navinailnavinail</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>28</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>735546684</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/735546684</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>말짜네일 광화문점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>malzzanail@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1402-3734</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/malzzanail</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>423</v>
+      </c>
+      <c r="R26" t="n">
+        <v>726</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>37997776</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37997776</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>릴리엔젤네일</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>kiyu0987@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://instagram.com/lilyangel_nail</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>52</v>
+      </c>
+      <c r="R27" t="n">
+        <v>288</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1110775717</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110775717</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>오토젯네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>yr19850217@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 돈화문로 68</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>http://www.autoznail.com/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>35506860</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35506860</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>네일온 명동본점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>nailon_myeongdong@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1302-8995</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 88 을특8호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nailon_myeongdong</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>33</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2054691209</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2054691209</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>루다네일</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rudanail1515@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1357-1516</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>http://instagram.com/rudanail_daehakro</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>112</v>
+      </c>
+      <c r="R30" t="n">
+        <v>366</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>34551572</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34551572</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>이츠네일</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>icacc89@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_duxhxdn</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>90</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>31949587</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31949587</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>폭시네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>aikastory@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1403-4791</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 동망산길 13 2층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>40986070</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/40986070</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>굿모닝네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nailnstyle_@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1400-8607</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>244</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>13051690</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13051690</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>찰스네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>hamilworld@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1307-4179</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로12길 9 3층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/charles__nail</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>528</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>56</v>
+      </c>
+      <c r="R34" t="n">
+        <v>584</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>13034248</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13034248</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>프로뷰티</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>probeauty_blog@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1435-2789</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동8가길 9 3층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/probeauty_blog</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>556</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>670</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1226</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>19997455</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19997455</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nail by Jade</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>hankyuldata@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1360-1011</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_by_jade</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>28</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>944614599</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/944614599</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>아머네일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hahaha__0@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1364-4429</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_pzkMG</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>96</v>
+      </c>
+      <c r="R37" t="n">
+        <v>358</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1312237193</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1312237193</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>네일그리미</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>tory0413@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1322-4179</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sdED0A2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>15</v>
+      </c>
+      <c r="R38" t="n">
+        <v>264</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1054499609</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054499609</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>리라뷰티</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>rira_225@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1403-3136</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lira_4994/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>271</v>
+      </c>
+      <c r="R39" t="n">
+        <v>392</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1100664846</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1100664846</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>엘로아네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>hhhong88@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1314-9339</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eloa__nail/</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>8</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2087274322</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087274322</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>네일문</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>llkn@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>02-730-0010</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailgate._.mr</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>590</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>181</v>
+      </c>
+      <c r="R41" t="n">
+        <v>771</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>13534535</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13534535</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>비조네일</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ozllzln17@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 379</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>5</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19813956</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19813956</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>네일바이안</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ye1yang@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>02-511-5621</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로9길 12</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbyahn</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>42</v>
+      </c>
+      <c r="R43" t="n">
+        <v>99</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1084164588</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1084164588</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>꽃소니 네일아트</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>070-8615-3478</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로5길 8 2층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/flower_handnails</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>108</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1593950281</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593950281</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>빌러브드 네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>brunchbear0825@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>02-733-8318</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/beloved_nail_</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>367</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>29</v>
+      </c>
+      <c r="R45" t="n">
+        <v>396</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>877681682</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/877681682</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>미스에이 네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>kinetixart@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>070-8277-3597</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_jhDaG</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>10</v>
+      </c>
+      <c r="R46" t="n">
+        <v>64</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1758327919</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758327919</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>네일하루</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nail_haru@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1361-1445</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_haru</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>346</v>
+      </c>
+      <c r="R47" t="n">
+        <v>413</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>37089409</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37089409</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>가빈네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>happyhannj@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1431-8259</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>59</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>38500996</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38500996</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>라라네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>redpepper30@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1344-7250</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>431</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1431</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1303128966</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303128966</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>9층네일 명동점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dmgktnqls@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1359-1372</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/9.nailstudio</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>23</v>
+      </c>
+      <c r="R50" t="n">
+        <v>281</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1681308543</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1681308543</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>삼층네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>wang8241@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1327-8241</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wang8241</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>530</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>13</v>
+      </c>
+      <c r="R51" t="n">
+        <v>543</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1894370134</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1894370134</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GK네일 현대시티아울렛 동대문점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>liziah@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>46</v>
+      </c>
+      <c r="R52" t="n">
+        <v>377</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1245812382</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1245812382</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>드네일 광화문점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dahaeyoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1351-9192</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>16</v>
+      </c>
+      <c r="R53" t="n">
+        <v>36</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1372444756</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1372444756</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>네일브러쉬</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ss7370306@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1332-0306</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ss7370306</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>14</v>
+      </c>
+      <c r="R54" t="n">
+        <v>79</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>35559430</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35559430</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>모스네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>buzzerrbeate@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/moss.nail_</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>13</v>
+      </c>
+      <c r="R55" t="n">
+        <v>233</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1061088069</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1061088069</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>꾸밈네일아트</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>fusion02@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02-733-7942</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>7</v>
+      </c>
+      <c r="R56" t="n">
+        <v>9</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>614593678</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/614593678</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>해피네일데이</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>happynailday@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1362-9334</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/happynailday</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>183</v>
+      </c>
+      <c r="R57" t="n">
+        <v>349</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>298136226</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/298136226</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>위치네일스 종로점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>witch_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1364-9020</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 51</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/witch_nail</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1057</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>149</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1206</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1543496206</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1543496206</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>네일원</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>nail_one@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1338-0475</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 지봉로 52-1 2층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_nail_one</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>4</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1105911364</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105911364</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>제이뷰티 눈썹&amp;네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jbeauty4022@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1422-4022</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jbeauty4022</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>3306</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>227</v>
+      </c>
+      <c r="R60" t="n">
+        <v>3533</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1776791877</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1776791877</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>살롱드소피</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>skincare25@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/salon_de_sophie_</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>64</v>
+      </c>
+      <c r="R61" t="n">
+        <v>174</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>13434920</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13434920</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>네일해요</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>elliestar@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로44길 9 2층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1213168091</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213168091</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>네일, 사월</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>pooddin@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__april</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>595</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>14</v>
+      </c>
+      <c r="R63" t="n">
+        <v>609</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1448977317</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1448977317</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>그리다네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>gridanail2@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>02-745-8375</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로12길 77</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3</v>
+      </c>
+      <c r="R64" t="n">
+        <v>23</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>142708597</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/142708597</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>오프엠네일</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>hazelnutt7@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동4길 40 4층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>63</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2099192808</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099192808</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>02-756-4143</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>4</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>31315234</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31315234</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>수야디나 네일&amp;래쉬</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>purinxoxo@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1305-2499</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 충무로 36 2층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yun_ju423/</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>32</v>
+      </c>
+      <c r="R67" t="n">
+        <v>215</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1324800762</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324800762</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>네일누하</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>annoi_@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1348-9398</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.nuha</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>18</v>
+      </c>
+      <c r="R68" t="n">
+        <v>34</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1370069746</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370069746</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>무아네일</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sunry038@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1436-1716</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2038424794</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038424794</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>네일,현</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>qkrwlsk126@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1316-0133</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_hyun.__</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>23</v>
+      </c>
+      <c r="R70" t="n">
+        <v>198</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1120708839</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1120708839</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>드팜므</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>mellowryu@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1317-3395</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로8길 42 B110호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/defemmeeee</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>70</v>
+      </c>
+      <c r="R71" t="n">
+        <v>144</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1741921081</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1741921081</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>베리네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>llrainryuell@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1419-6623</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/berry_nail_</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>7</v>
+      </c>
+      <c r="R72" t="n">
+        <v>84</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1394925944</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1394925944</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>꽁냥네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>qorgh1236@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1418-2440</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>40</v>
+      </c>
+      <c r="R73" t="n">
+        <v>314</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1570914826</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1570914826</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>네일&amp;페일아트</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>seon9550@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 진흥로 446</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>20871402</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20871402</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>꾸미다</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>yem1104@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>3</v>
+      </c>
+      <c r="R75" t="n">
+        <v>4</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1095499576</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1095499576</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>어나더네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>soojinpo@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 지봉로 56-1 1층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/another_n_ail</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>11</v>
+      </c>
+      <c r="R76" t="n">
+        <v>69</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1214193406</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1214193406</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>르모네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>mylifegoal@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1374-9858</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 동숭4가길 2 2층</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_lmonail</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>16</v>
+      </c>
+      <c r="R77" t="n">
+        <v>24</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1493224095</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1493224095</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>루아르블랑 네일</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>hyperreal03@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1483-9411</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sHajSJei</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>59</v>
+      </c>
+      <c r="R78" t="n">
+        <v>230</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2013893243</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2013893243</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>르노브네일</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>hshee069@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1307-5439</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 성균관로 38 1층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_XxbVPn</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>18</v>
+      </c>
+      <c r="R79" t="n">
+        <v>413</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1890443515</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1890443515</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>맥스네일</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>machojj@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>02-2272-4141</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 204 3층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/machojj</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>532</v>
+      </c>
+      <c r="R80" t="n">
+        <v>728</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>32786203</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32786203</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>아셀네일</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>asher9809@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 253 10층 11호</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>23</v>
+      </c>
+      <c r="R81" t="n">
+        <v>82</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1229434440</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1229434440</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>네일로드</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>lordnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>02-734-1730</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>206289152</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/206289152</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>혜리앤케어</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>micahyesung@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>02-725-1741</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>3</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>155402276</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/155402276</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>뉴문네일</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>xdaredare@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1354-6577</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 성균관로 7 2층</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>http://instagram.com/newmoonnail_</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>4</v>
+      </c>
+      <c r="R84" t="n">
+        <v>152</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1689136529</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1689136529</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>네일아토</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sk3374@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1416-6630</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_ato</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>22</v>
+      </c>
+      <c r="R85" t="n">
+        <v>213</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1446399532</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1446399532</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>네일라이트</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>elegant1025@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 세종대로23길 5 3층</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_nail_light_</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>6</v>
+      </c>
+      <c r="R86" t="n">
+        <v>547</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1105652769</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105652769</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>뷰티숲</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>smallwarestore@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1438-7477</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 지봉로 37-29 103호</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailsoop_sj/</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>57</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1158436638</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1158436638</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>에이탑네일</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>adw1223@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1372-2148</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동4길 12-1 3층</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.top_nail</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>66</v>
+      </c>
+      <c r="R88" t="n">
+        <v>315</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1446197361</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1446197361</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>마이파우치</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>323redtree@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1402-0809</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mypouch.kangbbin</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>183</v>
+      </c>
+      <c r="R89" t="n">
+        <v>194</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>38642341</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38642341</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>블링네일 종로점</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>beaulynail@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1448-0036</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로 16-1 1층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/beaulynail</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>73</v>
+      </c>
+      <c r="R90" t="n">
+        <v>217</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>60890323</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/60890323</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>네일 오우브</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>jian_725@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1407-0437</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.ouv</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>153</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1559030900</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1559030900</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>바움네일</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>harulov@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1330-3151</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로9길 37 2층</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baum_nail</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>559</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>47</v>
+      </c>
+      <c r="R92" t="n">
+        <v>606</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1954514000</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1954514000</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>디비노뷰티랩 속눈썹&amp;네일 혜화</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>junu8858@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1487-8858</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로 83 3층</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/junu8858</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>379</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>204</v>
+      </c>
+      <c r="R93" t="n">
+        <v>583</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1650485583</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1650485583</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>올리브네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>djdjqq1663@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>02-2075-7775</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/djdjqq1663</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>3087</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>248</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3335</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>35751284</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35751284</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>바비 네일왁싱</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>uchka247@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1490-9887</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로44길 6-9 4층</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barbie.waxnail</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>3</v>
+      </c>
+      <c r="R95" t="n">
+        <v>164</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1019484164</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1019484164</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>세아현대아울렛동대문점</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>anne0504@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로13길 20 현대아울렛동대문점B1</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1421171519</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1421171519</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>kikiu30@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1378-0246</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_pAtmG</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>1847</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>61</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1908</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1712141242</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1712141242</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>네일 김미쉘터</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>patent37435@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0507-1320-1993</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 필운대로 55</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>4</v>
+      </c>
+      <c r="R98" t="n">
+        <v>269</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>1802694964</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1802694964</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>페이브 네일 스튜디오</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>twolf97@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sUKlei7f</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>33</v>
+      </c>
+      <c r="R99" t="n">
+        <v>96</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1109114407</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109114407</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Diamond Nails</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ksj673232@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1420-1393</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마른내로 155 1동 102호</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>2040524360</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2040524360</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>크리스탈손톱</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>juyean123@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>02-3398-4445</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 275</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1</v>
+      </c>
+      <c r="R101" t="n">
+        <v>4</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>1895018257</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1895018257</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>종로네일샵</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>sohyun1304@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 62</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>1928832758</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928832758</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>치즈네일</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>43995@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>02-6405-4578</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cheesenail</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1</v>
+      </c>
+      <c r="R103" t="n">
+        <v>58</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>37542182</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37542182</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>아트만네일</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>kpk0105@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Txkxgfxj</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>20</v>
+      </c>
+      <c r="R104" t="n">
+        <v>36</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>1284929161</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284929161</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>네일지니</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>hjung9612@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xeTiCG</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>1744</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>89</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1833</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1073291540</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1073291540</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>핸더뷰티</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>koenji_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0507-1380-1146</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/koenji_nail</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>412</v>
+      </c>
+      <c r="R106" t="n">
+        <v>769</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>37558905</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37558905</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>네일하트</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>nailheart053@naver.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1484-8604</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>9</v>
+      </c>
+      <c r="R107" t="n">
+        <v>382</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>1101101042</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101101042</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jjuahlee@naver.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>02-318-6668</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>14</v>
+      </c>
+      <c r="R108" t="n">
+        <v>102</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1874418389</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874418389</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>안0네일</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ysl6161015@naver.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>02-6052-7778</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>18</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>1487336161</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1487336161</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>파라테라피네일</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>anrgudtkd@naver.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail._.again</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>9</v>
+      </c>
+      <c r="R110" t="n">
+        <v>299</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>1996157285</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1996157285</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>아따걸네일</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>addagirl2@naver.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0507-1328-8505</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_GWaij</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>648</v>
+      </c>
+      <c r="R111" t="n">
+        <v>933</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>13047890</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13047890</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>을지네일해</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>dear_jade@naver.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1366-2991</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/euljinail_hae</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>2038116522</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038116522</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>네일해썸</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>llllcmalll@naver.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0507-1342-3168</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_hatssome</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>10</v>
+      </c>
+      <c r="R113" t="n">
+        <v>95</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>1991633917</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1991633917</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>네일스토리</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>yeju0414@naver.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>02-765-5525</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 지봉로 53-1 1층</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>3</v>
+      </c>
+      <c r="R114" t="n">
+        <v>10</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>34352879</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34352879</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver-place-crawler/results_nail/종로_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/종로_네일샵.xlsx
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>미스에이 네일</t>
+          <t>루아르블랑 네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kinetixart@naver.com</t>
+          <t>failuredw@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>070-8277-3597</t>
+          <t>0507-1483-9411</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
+          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_jhDaG</t>
+          <t>https://open.kakao.com/o/sHajSJei</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="R2" t="n">
-        <v>64</v>
+        <v>240</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1758327919</t>
+          <t>2013893243</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758327919</t>
+          <t>https://m.place.naver.com/place/2013893243</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>찰스네일</t>
+          <t>혜리앤케어</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spotv_sports@naver.com</t>
+          <t>micahyesung@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1307-4179</t>
+          <t>02-725-1741</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로12길 9 3층</t>
+          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/charles__nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>529</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>585</v>
+        <v>3</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13034248</t>
+          <t>155402276</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13034248</t>
+          <t>https://m.place.naver.com/place/155402276</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>무아네일</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>loowowool@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1436-1716</t>
+          <t>02-318-6668</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
+          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2038424794</t>
+          <t>1874418389</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038424794</t>
+          <t>https://m.place.naver.com/place/1874418389</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일하루</t>
+          <t>바움네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nail_haru@naver.com</t>
+          <t>harulov@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1361-1445</t>
+          <t>0507-1330-3151</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
+          <t>서울특별시 종로구 대학로9길 37 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_haru</t>
+          <t>https://www.instagram.com/baum_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>67</v>
+        <v>559</v>
       </c>
       <c r="Q5" t="n">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>413</v>
+        <v>606</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37089409</t>
+          <t>1954514000</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37089409</t>
+          <t>https://m.place.naver.com/place/1954514000</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일온 명동본점</t>
+          <t>해피네일데이</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nailon_myeongdong@naver.com</t>
+          <t>happynailday@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1302-8995</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 을특8호</t>
+          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon_myeongdong</t>
+          <t>https://blog.naver.com/happynailday</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>184</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>350</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2054691209</t>
+          <t>298136226</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054691209</t>
+          <t>https://m.place.naver.com/place/298136226</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일 김미쉘터</t>
+          <t>네일하루</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>patent37435@naver.com</t>
+          <t>nail_haru@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1320-1993</t>
+          <t>0507-1361-1445</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 55</t>
+          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nail_haru</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,12 +1062,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>266</v>
+        <v>67</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>346</v>
       </c>
       <c r="R7" t="n">
-        <v>270</v>
+        <v>413</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1802694964</t>
+          <t>37089409</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802694964</t>
+          <t>https://m.place.naver.com/place/37089409</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>르노브네일</t>
+          <t>베리네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hshee069@naver.com</t>
+          <t>ems0619@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1307-5439</t>
+          <t>0507-1419-6623</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 38 1층</t>
+          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XxbVPn</t>
+          <t>https://www.instagram.com/berry_nail_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1176,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>404</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>424</v>
+        <v>84</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1890443515</t>
+          <t>1394925944</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1890443515</t>
+          <t>https://m.place.naver.com/place/1394925944</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일멜로우</t>
+          <t>살롱드벨르네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sc09mc@naver.com</t>
+          <t>salondebelle_nail@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1356-7672</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
+          <t>서울특별시 종로구 종로 65 2층 208호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mellow_11/</t>
+          <t>https://blog.naver.com/salondebelle_nail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>391</v>
+        <v>355</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="R9" t="n">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1933958367</t>
+          <t>1768571536</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933958367</t>
+          <t>https://m.place.naver.com/place/1768571536</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>9층네일 명동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>dmgktnqls@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-765-5525</t>
+          <t>0507-1359-1372</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 53-1 1층</t>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/9.nailstudio</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,7 +1340,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1369,17 +1361,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>281</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>34352879</t>
+          <t>1681308543</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34352879</t>
+          <t>https://m.place.naver.com/place/1681308543</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1410,25 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일, 사월</t>
+          <t>꽃소니 네일아트</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pooddin@naver.com</t>
+          <t>qhpw4cpk@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>070-8615-3478</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
+          <t>서울특별시 종로구 대학로5길 8 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__april</t>
+          <t>https://www.instagram.com/flower_handnails</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>635</v>
+        <v>105</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>649</v>
+        <v>109</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1448977317</t>
+          <t>1593950281</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448977317</t>
+          <t>https://m.place.naver.com/place/1593950281</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1500,34 +1496,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>꽃소니 네일아트</t>
+          <t>르노브네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>qhpw4cpk@naver.com</t>
+          <t>hshee069@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>070-8615-3478</t>
+          <t>0507-1307-5439</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로5길 8 2층</t>
+          <t>서울특별시 종로구 성균관로 38 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flower_handnails</t>
+          <t>http://pf.kakao.com/_XxbVPn</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1548,7 +1544,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1557,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>105</v>
+        <v>405</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="R12" t="n">
-        <v>109</v>
+        <v>426</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1593950281</t>
+          <t>1890443515</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593950281</t>
+          <t>https://m.place.naver.com/place/1890443515</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1594,30 +1590,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GK네일 현대시티아울렛 동대문점</t>
+          <t>올리브네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>liziah@naver.com</t>
+          <t>djdjqq1663@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>02-2075-7775</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
+          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/djdjqq1663</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1638,7 +1638,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>331</v>
+        <v>3106</v>
       </c>
       <c r="Q13" t="n">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="R13" t="n">
-        <v>377</v>
+        <v>3356</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1245812382</t>
+          <t>35751284</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245812382</t>
+          <t>https://m.place.naver.com/place/35751284</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1684,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>루다네일</t>
+          <t>너 참 예쁘다</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rudanail1515@naver.com</t>
+          <t>yuiu1401@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1357-1516</t>
+          <t>0507-1434-8892</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://instagram.com/rudanail_daehakro</t>
+          <t>http://www.instagram.com/youarebeautiful_seoul</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1726,13 +1726,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1741,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="Q14" t="n">
-        <v>112</v>
+        <v>840</v>
       </c>
       <c r="R14" t="n">
-        <v>366</v>
+        <v>1369</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>34551572</t>
+          <t>1466732665</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34551572</t>
+          <t>https://m.place.naver.com/place/1466732665</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1778,34 +1782,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아머네일</t>
+          <t>바비 네일왁싱</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dntndus111@naver.com</t>
+          <t>uchka247@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1364-4429</t>
+          <t>0507-1490-9887</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
+          <t>서울특별시 중구 을지로44길 6-9 4층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_pzkMG</t>
+          <t>https://www.instagram.com/barbie.waxnail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1826,7 +1830,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1835,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>262</v>
+        <v>161</v>
       </c>
       <c r="Q15" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>359</v>
+        <v>164</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1312237193</t>
+          <t>1019484164</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312237193</t>
+          <t>https://m.place.naver.com/place/1019484164</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1876,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일 을지로지하쇼핑센터3구역점</t>
+          <t>키튼네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>dbgpwn0626@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02-2278-2990</t>
+          <t>02-765-8566</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
+          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1904,7 +1908,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1925,17 +1929,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>483</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="R16" t="n">
-        <v>6</v>
+        <v>537</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>37588249</t>
+          <t>1065031131</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588249</t>
+          <t>https://m.place.naver.com/place/1065031131</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2052,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2060,25 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>살롱드소피</t>
+          <t>디디 네일바</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>skincare25@naver.com</t>
+          <t>heeja090@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1476-0228</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
+          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salon_de_sophie_</t>
+          <t>https://www.instagram.com/didi___nailbar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2113,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="Q18" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="R18" t="n">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13434920</t>
+          <t>1134899134</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13434920</t>
+          <t>https://m.place.naver.com/place/1134899134</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2150,29 +2158,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>핸더뷰티</t>
+          <t>손톱그림</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>koenji_nail@naver.com</t>
+          <t>on_calli@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1380-1146</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
+          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/koenji_nail</t>
+          <t>https://www.instagram.com/nail_sketch_8478/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2187,7 +2191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2207,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>357</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>412</v>
+        <v>73</v>
       </c>
       <c r="R19" t="n">
-        <v>769</v>
+        <v>76</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>37558905</t>
+          <t>1124095560</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37558905</t>
+          <t>https://m.place.naver.com/place/1124095560</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2248,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>바움네일</t>
+          <t>뷰티숲</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>harulov@naver.com</t>
+          <t>smallwarestore@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1330-3151</t>
+          <t>0507-1438-7477</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로9길 37 2층</t>
+          <t>서울특별시 종로구 지봉로 37-29 103호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/baum_nail</t>
+          <t>https://www.instagram.com/nailsoop_sj/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2301,13 +2305,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>559</v>
+        <v>58</v>
       </c>
       <c r="Q20" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>606</v>
+        <v>58</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2320,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1954514000</t>
+          <t>1158436638</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954514000</t>
+          <t>https://m.place.naver.com/place/1158436638</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2338,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nail by Jade</t>
+          <t>네일누하</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>annoi_@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1360-1011</t>
+          <t>0507-1348-9398</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
+          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_by_jade</t>
+          <t>https://www.instagram.com/nail.nuha</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2395,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R21" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2414,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>944614599</t>
+          <t>1370069746</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/944614599</t>
+          <t>https://m.place.naver.com/place/1370069746</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2436,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일블라썸</t>
+          <t>모스네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>buzzerrbeate@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1347-8173</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 95호</t>
+          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/moss.nail_</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2480,22 +2480,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>333</v>
+        <v>226</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R22" t="n">
-        <v>343</v>
+        <v>239</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2504,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1794862527</t>
+          <t>1061088069</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794862527</t>
+          <t>https://m.place.naver.com/place/1061088069</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2526,34 +2526,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>올리브네일&amp;속눈썹</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>djdjqq1663@naver.com</t>
+          <t>kikiu30@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>02-2075-7775</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
+          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/djdjqq1663</t>
+          <t>http://pf.kakao.com/_pAtmG</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2563,7 +2559,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2583,13 +2579,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3102</v>
+        <v>1852</v>
       </c>
       <c r="Q23" t="n">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="R23" t="n">
-        <v>3352</v>
+        <v>1913</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2594,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>35751284</t>
+          <t>1712141242</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35751284</t>
+          <t>https://m.place.naver.com/place/1712141242</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2620,29 +2616,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일문</t>
+          <t>안0네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>llkn@naver.com</t>
+          <t>ysl6161015@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02-730-0010</t>
+          <t>02-6052-7778</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
+          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgate._.mr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2652,7 +2648,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2673,17 +2669,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>592</v>
+        <v>19</v>
       </c>
       <c r="Q24" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>773</v>
+        <v>19</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2688,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>13534535</t>
+          <t>1487336161</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13534535</t>
+          <t>https://m.place.naver.com/place/1487336161</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2714,29 +2710,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>블링네일 종로점</t>
+          <t>오토젯네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>beaulynail@naver.com</t>
+          <t>yr19850217@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0507-1448-0036</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 16-1 1층</t>
+          <t>서울특별시 종로구 돈화문로 68</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beaulynail</t>
+          <t>http://www.autoznail.com/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2751,7 +2743,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2767,17 +2759,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2778,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>60890323</t>
+          <t>35506860</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60890323</t>
+          <t>https://m.place.naver.com/place/35506860</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2808,29 +2800,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Diamond Nails</t>
+          <t>아셀네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ksj673232@naver.com</t>
+          <t>asher9809@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1420-1393</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 155 1동 102호</t>
+          <t>서울특별시 중구 장충단로 253 10층 11호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2840,7 +2828,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2861,17 +2849,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2868,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2040524360</t>
+          <t>1229434440</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040524360</t>
+          <t>https://m.place.naver.com/place/1229434440</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2902,30 +2890,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일지니</t>
+          <t>그리드네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1231yc@naver.com</t>
+          <t>boye_like@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1405-0461</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
+          <t>서울특별시 종로구 옥인길 44</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xeTiCG</t>
+          <t>http://instagram.com/love_grid</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2946,7 +2938,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2955,13 +2947,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1771</v>
+        <v>53</v>
       </c>
       <c r="Q27" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1864</v>
+        <v>55</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2962,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1073291540</t>
+          <t>38531607</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073291540</t>
+          <t>https://m.place.naver.com/place/38531607</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2992,29 +2984,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>빌러브드 네일</t>
+          <t>페이브 네일 스튜디오</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>novembro_12@naver.com</t>
+          <t>ekdmaekfdpqnwk@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>02-733-8318</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beloved_nail_</t>
+          <t>https://open.kakao.com/o/sUKlei7f</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3040,7 +3028,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3049,13 +3037,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>371</v>
+        <v>63</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R28" t="n">
-        <v>400</v>
+        <v>96</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3052,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>877681682</t>
+          <t>1109114407</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/877681682</t>
+          <t>https://m.place.naver.com/place/1109114407</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3086,25 +3074,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아셀네일</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>asher9809@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1358-8653</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 253 10층 11호</t>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_lee____</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3114,7 +3106,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3135,17 +3127,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="R29" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,17 +3146,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1229434440</t>
+          <t>2065943871</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229434440</t>
+          <t>https://m.place.naver.com/place/2065943871</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3176,29 +3168,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>드팜므</t>
+          <t>오브 코코네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mellowryu@naver.com</t>
+          <t>xiah15holic@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1317-3395</t>
+          <t>0507-1371-8921</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 42 B110호</t>
+          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/defemmeeee</t>
+          <t>https://www.instagram.com/ofconail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3233,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>75</v>
+        <v>658</v>
       </c>
       <c r="Q30" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="R30" t="n">
-        <v>145</v>
+        <v>705</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,17 +3240,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1741921081</t>
+          <t>1009626425</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1741921081</t>
+          <t>https://m.place.naver.com/place/1009626425</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3270,29 +3262,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>너 참 예쁘다</t>
+          <t>수야디나 네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>yuiu1401@naver.com</t>
+          <t>vastron@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1434-8892</t>
+          <t>0507-1305-2499</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
+          <t>서울특별시 중구 충무로 36 2층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/youarebeautiful_seoul</t>
+          <t>https://www.instagram.com/yun_ju423/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3312,14 +3304,10 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3331,13 +3319,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>529</v>
+        <v>184</v>
       </c>
       <c r="Q31" t="n">
-        <v>840</v>
+        <v>32</v>
       </c>
       <c r="R31" t="n">
-        <v>1369</v>
+        <v>216</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,17 +3334,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1466732665</t>
+          <t>1324800762</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466732665</t>
+          <t>https://m.place.naver.com/place/1324800762</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3368,34 +3356,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>마이파우치</t>
+          <t>미스에이 네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>323redtree@naver.com</t>
+          <t>kinetixart@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1402-0809</t>
+          <t>070-8277-3597</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
+          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mypouch.kangbbin</t>
+          <t>https://pf.kakao.com/_jhDaG</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3416,7 +3404,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3425,13 +3413,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="Q32" t="n">
-        <v>183</v>
+        <v>10</v>
       </c>
       <c r="R32" t="n">
-        <v>194</v>
+        <v>64</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,17 +3428,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>38642341</t>
+          <t>1758327919</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38642341</t>
+          <t>https://m.place.naver.com/place/1758327919</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3462,29 +3450,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일 오우브</t>
+          <t>드네일 광화문점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>keroo90@naver.com</t>
+          <t>dahaeyoo@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1407-0437</t>
+          <t>0507-1351-9192</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
+          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.ouv</t>
+          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3519,13 +3507,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R33" t="n">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,17 +3522,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1559030900</t>
+          <t>1372444756</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559030900</t>
+          <t>https://m.place.naver.com/place/1372444756</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3556,29 +3544,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오드리네일</t>
+          <t>핸더뷰티</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ardusy@naver.com</t>
+          <t>koenji_nail@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>02-722-1384</t>
+          <t>0507-1380-1146</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
+          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreynail_official</t>
+          <t>https://blog.naver.com/koenji_nail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3593,7 +3581,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3604,7 +3592,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3613,13 +3601,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>228</v>
+        <v>357</v>
       </c>
       <c r="Q34" t="n">
-        <v>256</v>
+        <v>412</v>
       </c>
       <c r="R34" t="n">
-        <v>484</v>
+        <v>769</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,17 +3616,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>13450587</t>
+          <t>37558905</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13450587</t>
+          <t>https://m.place.naver.com/place/37558905</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3650,12 +3638,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>살롱드벨르네일</t>
+          <t>네일, 사월</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>salondebelle_nail@naver.com</t>
+          <t>pooddin@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3663,12 +3651,12 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 65 2층 208호</t>
+          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/salondebelle_nail</t>
+          <t>https://www.instagram.com/nail__april</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3683,7 +3671,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3703,13 +3691,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>354</v>
+        <v>644</v>
       </c>
       <c r="Q35" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="R35" t="n">
-        <v>415</v>
+        <v>658</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,17 +3706,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1768571536</t>
+          <t>1448977317</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768571536</t>
+          <t>https://m.place.naver.com/place/1448977317</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3740,25 +3728,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>모스네일</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>buzzerrbeate@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1322-4179</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
+          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss.nail_</t>
+          <t>https://open.kakao.com/o/sdED0A2</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3793,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R36" t="n">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3808,17 +3800,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1061088069</t>
+          <t>1054499609</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061088069</t>
+          <t>https://m.place.naver.com/place/1054499609</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3830,39 +3822,43 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>리빈네일</t>
+          <t>레푸스 종로점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jcj0217@naver.com</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>refuss_jong_ro@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>chy0802@ahasoft.co.kr</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1349-9808</t>
+          <t>02-720-4544</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
+          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rivin_nail</t>
+          <t>https://booking.naver.com/booking/13/bizes/857013</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3887,13 +3883,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>128</v>
+        <v>862</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="R37" t="n">
-        <v>130</v>
+        <v>1222</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,17 +3898,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1315671750</t>
+          <t>1237692187</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315671750</t>
+          <t>https://m.place.naver.com/place/1237692187</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3924,29 +3920,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>루이비네일</t>
+          <t>네일아토</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>zhengyinji888@naver.com</t>
+          <t>sk3374@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1445-2047</t>
+          <t>0507-1416-6630</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
+          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://instagram.com/luyibi_nail8</t>
+          <t>https://www.instagram.com/nail_ato</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3981,13 +3977,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>481</v>
+        <v>192</v>
       </c>
       <c r="Q38" t="n">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="R38" t="n">
-        <v>570</v>
+        <v>215</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,17 +3992,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>21306056</t>
+          <t>1446399532</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21306056</t>
+          <t>https://m.place.naver.com/place/1446399532</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4018,29 +4014,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>그리드네일</t>
+          <t>네일 김미쉘터</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>boye_like@naver.com</t>
+          <t>patent37435@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1405-0461</t>
+          <t>0507-1320-1993</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 44</t>
+          <t>서울특별시 종로구 필운대로 55</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://instagram.com/love_grid</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4050,7 +4046,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4071,17 +4067,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>53</v>
+        <v>266</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,17 +4086,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>38531607</t>
+          <t>1802694964</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531607</t>
+          <t>https://m.place.naver.com/place/1802694964</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4112,29 +4108,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일누하</t>
+          <t>블링네일 종로점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>beaulynail@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1348-9398</t>
+          <t>0507-1448-0036</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
+          <t>서울특별시 종로구 대학로 16-1 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.nuha</t>
+          <t>https://blog.naver.com/beaulynail</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4149,7 +4145,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4169,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="R40" t="n">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4184,17 +4180,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1370069746</t>
+          <t>60890323</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370069746</t>
+          <t>https://m.place.naver.com/place/60890323</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4206,39 +4202,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>아따걸네일</t>
+          <t>엔79 Nail</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>addagirl2@naver.com</t>
+          <t>loveucream@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1328-8505</t>
+          <t>0507-1390-0326</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
+          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_GWaij</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4254,22 +4250,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>285</v>
+        <v>163</v>
       </c>
       <c r="Q41" t="n">
-        <v>649</v>
+        <v>19</v>
       </c>
       <c r="R41" t="n">
-        <v>934</v>
+        <v>182</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4278,17 +4274,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13047890</t>
+          <t>1756267523</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13047890</t>
+          <t>https://m.place.naver.com/place/1756267523</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4300,29 +4296,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>가빈네일</t>
+          <t>네일바이안</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>happyhannj@naver.com</t>
+          <t>ye1yang@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1431-8259</t>
+          <t>02-511-5621</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
+          <t>서울특별시 중구 남대문로9길 12 8층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
+          <t>https://www.instagram.com/nailbyahn</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4357,13 +4353,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="R42" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,17 +4368,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>38500996</t>
+          <t>1084164588</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38500996</t>
+          <t>https://m.place.naver.com/place/1084164588</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4394,34 +4390,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>수야디나 네일&amp;래쉬</t>
+          <t>이츠네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>purinxoxo@naver.com</t>
+          <t>icacc89@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1305-2499</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 중구 충무로 36 2층</t>
+          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yun_ju423/</t>
+          <t>http://pf.kakao.com/_duxhxdn</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4442,7 +4434,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4451,13 +4443,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="Q43" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4466,17 +4458,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1324800762</t>
+          <t>31949587</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324800762</t>
+          <t>https://m.place.naver.com/place/31949587</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4488,25 +4480,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일라이트</t>
+          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>elegant1025@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>02-756-4143</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 5 3층</t>
+          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_light_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4516,7 +4512,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4537,17 +4533,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>540</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>546</v>
+        <v>4</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4552,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1105652769</t>
+          <t>31315234</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105652769</t>
+          <t>https://m.place.naver.com/place/31315234</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4578,29 +4574,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>영심이손톱</t>
+          <t>비조네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>lovellies@naver.com</t>
+          <t>shoot13445@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>02-735-0031</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 88 701호</t>
+          <t>서울특별시 종로구 종로 379</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4610,7 +4602,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4631,17 +4623,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,17 +4642,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1116851430</t>
+          <t>19813956</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116851430</t>
+          <t>https://m.place.naver.com/place/19813956</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4672,38 +4664,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>레푸스 종로점</t>
+          <t>네일라이트</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>refuss_jong_ro@naver.com</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>chy0802@ahasoft.co.kr</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>02-720-4544</t>
-        </is>
-      </c>
+          <t>elegant1025@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
+          <t>서울특별시 종로구 세종대로23길 5 3층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/857013</t>
+          <t>http://instagram.com/_nail_light_</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4733,13 +4717,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>863</v>
+        <v>540</v>
       </c>
       <c r="Q46" t="n">
-        <v>360</v>
+        <v>6</v>
       </c>
       <c r="R46" t="n">
-        <v>1223</v>
+        <v>546</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4748,17 +4732,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1237692187</t>
+          <t>1105652769</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237692187</t>
+          <t>https://m.place.naver.com/place/1105652769</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4770,29 +4754,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>디디 네일바</t>
+          <t>JIN네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>heeja090@naver.com</t>
+          <t>jin_nail6453@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1476-0228</t>
+          <t>0507-1392-5159</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
+          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/didi___nailbar</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4802,7 +4786,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4823,17 +4807,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>189</v>
+        <v>64</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>213</v>
+        <v>65</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4842,17 +4826,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1134899134</t>
+          <t>1530291597</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134899134</t>
+          <t>https://m.place.naver.com/place/1530291597</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4864,29 +4848,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일아토</t>
+          <t>드팜므</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sk3374@naver.com</t>
+          <t>mellowryu@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1416-6630</t>
+          <t>0507-1317-3395</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
+          <t>서울특별시 종로구 사직로8길 42 B110호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ato</t>
+          <t>http://www.instagram.com/defemmeeee</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4921,13 +4905,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="R48" t="n">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,17 +4920,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1446399532</t>
+          <t>1741921081</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446399532</t>
+          <t>https://m.place.naver.com/place/1741921081</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4958,24 +4942,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>안0네일</t>
+          <t>오프엠네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ysl6161015@naver.com</t>
+          <t>hgy___g@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>02-6052-7778</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
+          <t>서울특별시 중구 명동4길 40 4층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5015,13 +4995,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5010,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1487336161</t>
+          <t>2099192808</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487336161</t>
+          <t>https://m.place.naver.com/place/2099192808</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5052,29 +5032,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일바이안</t>
+          <t>세아현대아울렛동대문점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ye1yang@naver.com</t>
+          <t>anne0504@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>02-511-5621</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로9길 12 8층</t>
+          <t>서울특별시 중구 장충단로13길 20 현대아울렛동대문점B1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyahn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5084,7 +5060,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5105,17 +5081,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,17 +5100,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1084164588</t>
+          <t>1421171519</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084164588</t>
+          <t>https://m.place.naver.com/place/1421171519</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5146,34 +5122,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>나비네일</t>
+          <t>아트만네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jytgh@naver.com</t>
+          <t>ppangsun238@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>02-319-7844</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://instagram.com/navinailnavinail</t>
+          <t>http://pf.kakao.com/_Txkxgfxj</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5194,7 +5166,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5203,13 +5175,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="R51" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5190,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>735546684</t>
+          <t>1284929161</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/735546684</t>
+          <t>https://m.place.naver.com/place/1284929161</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5240,24 +5212,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
+          <t>폭시네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>tomebooy@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02-756-4143</t>
+          <t>0507-1403-4791</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
+          <t>서울특별시 종로구 동망산길 13 2층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5297,13 +5269,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,17 +5284,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>31315234</t>
+          <t>40986070</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315234</t>
+          <t>https://m.place.naver.com/place/40986070</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5334,29 +5306,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>파라테라피네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>anrgudtkd@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>02-318-6668</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail._.again</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5366,7 +5334,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5387,17 +5355,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R53" t="n">
-        <v>102</v>
+        <v>300</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5406,17 +5374,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1874418389</t>
+          <t>1996157285</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874418389</t>
+          <t>https://m.place.naver.com/place/1996157285</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5428,29 +5396,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>에이탑네일</t>
+          <t>맥스네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kyoung057@naver.com</t>
+          <t>machojj@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1372-2148</t>
+          <t>02-2272-4141</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 12-1 3층</t>
+          <t>서울특별시 중구 퇴계로 204 3층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.top_nail</t>
+          <t>https://blog.naver.com/machojj</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5465,7 +5433,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5485,13 +5453,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>255</v>
+        <v>198</v>
       </c>
       <c r="Q54" t="n">
-        <v>66</v>
+        <v>532</v>
       </c>
       <c r="R54" t="n">
-        <v>321</v>
+        <v>730</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,17 +5468,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1446197361</t>
+          <t>32786203</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446197361</t>
+          <t>https://m.place.naver.com/place/32786203</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5522,29 +5490,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>효녀네일</t>
+          <t>위치네일스 종로점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hy0d0ng2@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1366-2991</t>
+          <t>0507-1364-9020</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
+          <t>서울특별시 종로구 종로 51</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyonyeo_nail</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5559,7 +5527,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5579,13 +5547,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>4</v>
+        <v>1060</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="R55" t="n">
-        <v>4</v>
+        <v>1209</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5594,17 +5562,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2038116522</t>
+          <t>1543496206</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038116522</t>
+          <t>https://m.place.naver.com/place/1543496206</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5616,12 +5584,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>세아현대아울렛동대문점</t>
+          <t>지아네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>anne0504@naver.com</t>
+          <t>jjaa1334@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -5629,12 +5597,12 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 현대아울렛동대문점B1</t>
+          <t>서울특별시 중구 명동10길 40 6층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jeonjia9</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5644,7 +5612,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5665,17 +5633,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5684,17 +5652,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1421171519</t>
+          <t>1279897442</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421171519</t>
+          <t>https://m.place.naver.com/place/1279897442</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5706,29 +5674,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>프로뷰티</t>
+          <t>무아네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>probeauty_blog@naver.com</t>
+          <t>loowowool@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1435-2789</t>
+          <t>0507-1436-1716</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8가길 9 3층</t>
+          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/probeauty_blog</t>
+          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5743,7 +5711,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5763,13 +5731,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>566</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1245</v>
+        <v>1</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5778,17 +5746,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>19997455</t>
+          <t>2038424794</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19997455</t>
+          <t>https://m.place.naver.com/place/2038424794</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5800,29 +5768,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>엔79 Nail</t>
+          <t>마이파우치</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>loveucream@naver.com</t>
+          <t>323redtree@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1390-0326</t>
+          <t>0507-1402-0809</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
+          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mypouch.kangbbin</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5832,7 +5800,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5853,17 +5821,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="Q58" t="n">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="R58" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5872,17 +5840,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1756267523</t>
+          <t>38642341</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756267523</t>
+          <t>https://m.place.naver.com/place/38642341</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5894,29 +5862,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>뷰티숲</t>
+          <t>꾸밈네일아트</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>smallwarestore@naver.com</t>
+          <t>fusion02@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1438-7477</t>
+          <t>02-733-7942</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 37-29 103호</t>
+          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailsoop_sj/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5926,7 +5894,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5947,17 +5915,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R59" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5966,17 +5934,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1158436638</t>
+          <t>614593678</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158436638</t>
+          <t>https://m.place.naver.com/place/614593678</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5988,29 +5956,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>강앤니네일스</t>
+          <t>네일문</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>llkn@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1468-2316</t>
+          <t>02-730-0010</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 227-2 4층</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://instagram.com/kangannynails</t>
+          <t>https://www.instagram.com/nailgate._.mr</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6045,13 +6013,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>773</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6060,17 +6028,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1711237836</t>
+          <t>13534535</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1711237836</t>
+          <t>https://m.place.naver.com/place/13534535</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6082,29 +6050,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일브러쉬</t>
+          <t>강앤니네일스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ss7370306@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1332-0306</t>
+          <t>0507-1468-2316</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
+          <t>서울특별시 중구 장충단로 227-2 4층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ss7370306</t>
+          <t>http://instagram.com/kangannynails</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6119,7 +6087,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6135,17 +6103,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6154,17 +6122,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>35559430</t>
+          <t>1711237836</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35559430</t>
+          <t>https://m.place.naver.com/place/1711237836</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6176,29 +6144,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>네일블라썸</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>wilklove@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1322-4179</t>
+          <t>0507-1347-8173</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
+          <t>서울특별시 중구 소공로 102 95호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sdED0A2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6208,7 +6176,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6224,22 +6192,22 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>249</v>
+        <v>333</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R62" t="n">
-        <v>264</v>
+        <v>343</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6248,17 +6216,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1054499609</t>
+          <t>1794862527</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054499609</t>
+          <t>https://m.place.naver.com/place/1794862527</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6270,29 +6238,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>그리다네일</t>
+          <t>리라뷰티</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>gridanail2@naver.com</t>
+          <t>rira_225@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>02-745-8375</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로12길 77</t>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lira_4994/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6302,7 +6266,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6323,17 +6287,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>276</v>
       </c>
       <c r="R63" t="n">
-        <v>23</v>
+        <v>396</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6342,17 +6306,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>142708597</t>
+          <t>1100664846</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142708597</t>
+          <t>https://m.place.naver.com/place/1100664846</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6364,29 +6328,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>바비 네일왁싱</t>
+          <t>네일쏘이</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>uchka247@naver.com</t>
+          <t>annoi_@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1490-9887</t>
+          <t>0507-1334-9677</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로44길 6-9 4층</t>
+          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barbie.waxnail</t>
+          <t>https://www.instagram.com/nailssoi_</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6421,13 +6385,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6436,17 +6400,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1019484164</t>
+          <t>1009120766</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1019484164</t>
+          <t>https://m.place.naver.com/place/1009120766</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6458,29 +6422,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>맥스네일</t>
+          <t>네일 오우브</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>machojj@naver.com</t>
+          <t>keroo90@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>02-2272-4141</t>
+          <t>0507-1407-0437</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 204 3층</t>
+          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/machojj</t>
+          <t>https://www.instagram.com/nail.ouv</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6495,7 +6459,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6515,13 +6479,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="Q65" t="n">
-        <v>532</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>730</v>
+        <v>155</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6530,17 +6494,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>32786203</t>
+          <t>1559030900</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32786203</t>
+          <t>https://m.place.naver.com/place/1559030900</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6552,25 +6516,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>오토젯네일</t>
+          <t>네일로드</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>yr19850217@naver.com</t>
+          <t>lordnail@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>02-734-1730</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로 68</t>
+          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.autoznail.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6580,7 +6548,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6620,17 +6588,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>35506860</t>
+          <t>206289152</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35506860</t>
+          <t>https://m.place.naver.com/place/206289152</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6642,29 +6610,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>루아르블랑 네일</t>
+          <t>루이비네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>failuredw@naver.com</t>
+          <t>zhengyinji888@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1483-9411</t>
+          <t>0507-1445-2047</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
+          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHajSJei</t>
+          <t>http://instagram.com/luyibi_nail8</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6690,7 +6658,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6699,13 +6667,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>175</v>
+        <v>481</v>
       </c>
       <c r="Q67" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="R67" t="n">
-        <v>235</v>
+        <v>570</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6714,17 +6682,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2013893243</t>
+          <t>21306056</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013893243</t>
+          <t>https://m.place.naver.com/place/21306056</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6736,39 +6704,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>네일 을지로지하쇼핑센터3구역점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kikiu30@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1378-0246</t>
+          <t>02-2278-2990</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
+          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pAtmG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6784,22 +6752,22 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1851</v>
+        <v>3</v>
       </c>
       <c r="Q68" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>1912</v>
+        <v>6</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6808,17 +6776,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1712141242</t>
+          <t>37588249</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712141242</t>
+          <t>https://m.place.naver.com/place/37588249</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6830,25 +6798,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>파라테라피네일</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>anrgudtkd@naver.com</t>
+          <t>yeju0414@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>02-765-5525</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
+          <t>서울특별시 종로구 지봉로 53-1 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail._.again</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6858,7 +6830,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6879,17 +6851,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>291</v>
+        <v>7</v>
       </c>
       <c r="Q69" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R69" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6898,17 +6870,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1996157285</t>
+          <t>34352879</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996157285</t>
+          <t>https://m.place.naver.com/place/34352879</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6920,29 +6892,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>드네일 광화문점</t>
+          <t>다리아네일 안국역</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>dahaeyoo@naver.com</t>
+          <t>puppyholic@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1351-9192</t>
+          <t>0507-1347-1494</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
+          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
+          <t>https://www.instagram.com/daria_nail_ssu</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6977,13 +6949,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="Q70" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>37</v>
+        <v>186</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6992,17 +6964,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1372444756</t>
+          <t>1165184706</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1372444756</t>
+          <t>https://m.place.naver.com/place/1165184706</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7014,30 +6986,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>페이브 네일 스튜디오</t>
+          <t>아따걸네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ekdmaekfdpqnwk@naver.com</t>
+          <t>addagirl2@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1328-8505</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sUKlei7f</t>
+          <t>https://pf.kakao.com/_GWaij</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7067,13 +7043,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>63</v>
+        <v>285</v>
       </c>
       <c r="Q71" t="n">
-        <v>33</v>
+        <v>649</v>
       </c>
       <c r="R71" t="n">
-        <v>96</v>
+        <v>934</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7082,17 +7058,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1109114407</t>
+          <t>13047890</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109114407</t>
+          <t>https://m.place.naver.com/place/13047890</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7104,29 +7080,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>뉴문네일</t>
+          <t>제이뷰티 눈썹&amp;네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>xdaredare@naver.com</t>
+          <t>jbeauty4022@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1354-6577</t>
+          <t>0507-1422-4022</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 7 2층</t>
+          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://instagram.com/newmoonnail_</t>
+          <t>https://blog.naver.com/jbeauty4022</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7141,7 +7117,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7161,13 +7137,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>149</v>
+        <v>3316</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="R72" t="n">
-        <v>153</v>
+        <v>3542</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7176,17 +7152,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1689136529</t>
+          <t>1776791877</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689136529</t>
+          <t>https://m.place.naver.com/place/1776791877</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7198,29 +7174,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>지호네일</t>
+          <t>네일,현</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>yongsanly@naver.com</t>
+          <t>qkrwlsk126@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1314-5759</t>
+          <t>0507-1316-0133</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 265 5층,6층</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jihonail</t>
+          <t>https://www.instagram.com/nail_hyun.__</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7255,13 +7231,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="R73" t="n">
-        <v>2</v>
+        <v>197</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7270,17 +7246,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1285361463</t>
+          <t>1120708839</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285361463</t>
+          <t>https://m.place.naver.com/place/1120708839</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7292,12 +7268,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>이츠네일</t>
+          <t>어나더네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>icacc89@naver.com</t>
+          <t>soojinpo@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -7305,17 +7281,17 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
+          <t>서울특별시 종로구 지봉로 56-1 1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_duxhxdn</t>
+          <t>https://www.instagram.com/another_n_ail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7336,7 +7312,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7345,13 +7321,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R74" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7360,17 +7336,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>31949587</t>
+          <t>1214193406</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31949587</t>
+          <t>https://m.place.naver.com/place/1214193406</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7382,30 +7358,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>아트만네일</t>
+          <t>에이탑네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ppangsun238@naver.com</t>
+          <t>kyoung057@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1372-2148</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
+          <t>서울특별시 중구 명동4길 12-1 3층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Txkxgfxj</t>
+          <t>https://www.instagram.com/a.top_nail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7426,7 +7406,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7435,13 +7415,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>16</v>
+        <v>259</v>
       </c>
       <c r="Q75" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="R75" t="n">
-        <v>36</v>
+        <v>325</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7450,17 +7430,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1284929161</t>
+          <t>1446197361</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284929161</t>
+          <t>https://m.place.naver.com/place/1446197361</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7472,29 +7452,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>키튼네일</t>
+          <t>네일멜로우</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dbgpwn0626@naver.com</t>
+          <t>sc09mc@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>02-765-8566</t>
+          <t>0507-1356-7672</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
+          <t>https://www.instagram.com/nail_mellow_11/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7529,13 +7509,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>473</v>
+        <v>389</v>
       </c>
       <c r="Q76" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="R76" t="n">
-        <v>527</v>
+        <v>423</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7544,17 +7524,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1065031131</t>
+          <t>1933958367</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065031131</t>
+          <t>https://m.place.naver.com/place/1933958367</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7566,25 +7546,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일&amp;페일아트</t>
+          <t>찰스네일</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>lsbangel@naver.com</t>
+          <t>spotv_sports@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1307-4179</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 446</t>
+          <t>서울특별시 종로구 종로12길 9 3층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/charles__nail</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7594,7 +7578,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7615,17 +7599,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2</v>
+        <v>529</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R77" t="n">
-        <v>2</v>
+        <v>585</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7634,17 +7618,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>20871402</t>
+          <t>13034248</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20871402</t>
+          <t>https://m.place.naver.com/place/13034248</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7656,29 +7640,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>오브 코코네일</t>
+          <t>굿모닝네일</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>xiah15holic@naver.com</t>
+          <t>clsrn9606@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1371-8921</t>
+          <t>0507-1400-8607</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ofconail</t>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7704,7 +7688,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7713,13 +7697,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>657</v>
+        <v>241</v>
       </c>
       <c r="Q78" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="R78" t="n">
-        <v>704</v>
+        <v>247</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7728,17 +7712,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1009626425</t>
+          <t>13051690</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009626425</t>
+          <t>https://m.place.naver.com/place/13051690</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7750,29 +7734,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>혜리앤케어</t>
+          <t>네일해썸</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>micahyesung@naver.com</t>
+          <t>llllcmalll@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>02-725-1741</t>
+          <t>0507-1342-3168</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
+          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_hatssome</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7782,7 +7766,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7798,22 +7782,22 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R79" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7822,17 +7806,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>155402276</t>
+          <t>1991633917</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/155402276</t>
+          <t>https://m.place.naver.com/place/1991633917</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7844,25 +7828,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>해피네일데이</t>
+          <t>GK네일 현대시티아울렛 동대문점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>happynailday@naver.com</t>
+          <t>liziah@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1339-5357</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
+          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/happynailday</t>
+          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7877,7 +7865,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7897,13 +7885,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>166</v>
+        <v>332</v>
       </c>
       <c r="Q80" t="n">
-        <v>184</v>
+        <v>46</v>
       </c>
       <c r="R80" t="n">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7912,17 +7900,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>298136226</t>
+          <t>1245812382</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/298136226</t>
+          <t>https://m.place.naver.com/place/1245812382</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7922,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>릴리엔젤네일</t>
+          <t>네일해요</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>kiyu0987@naver.com</t>
+          <t>elliestar@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -7947,12 +7935,12 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
+          <t>서울특별시 종로구 종로44길 9 2층</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>http://instagram.com/lilyangel_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7962,7 +7950,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7983,17 +7971,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>236</v>
+        <v>6</v>
       </c>
       <c r="Q81" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8002,17 +7990,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1110775717</t>
+          <t>1213168091</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110775717</t>
+          <t>https://m.place.naver.com/place/1213168091</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8024,24 +8012,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>네일로드</t>
+          <t>네일&amp;페일아트</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>lordnail@naver.com</t>
+          <t>lsbangel@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>02-734-1730</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
+          <t>서울특별시 종로구 진흥로 446</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8081,13 +8065,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8096,17 +8080,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>206289152</t>
+          <t>20871402</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/206289152</t>
+          <t>https://m.place.naver.com/place/20871402</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8118,25 +8102,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>리라뷰티</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>rira_225@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>02-722-1384</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lira_4994/</t>
+          <t>https://www.instagram.com/audreynail_official</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8162,7 +8150,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8171,13 +8159,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>121</v>
+        <v>228</v>
       </c>
       <c r="Q83" t="n">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="R83" t="n">
-        <v>397</v>
+        <v>484</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8186,17 +8174,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1100664846</t>
+          <t>13450587</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100664846</t>
+          <t>https://m.place.naver.com/place/13450587</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8208,29 +8196,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>엘로아네일</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>hhhong88@naver.com</t>
+          <t>jytgh@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1314-9339</t>
+          <t>02-319-7844</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eloa__nail/</t>
+          <t>http://instagram.com/navinailnavinail</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8265,13 +8253,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R84" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8280,17 +8268,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>2087274322</t>
+          <t>735546684</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087274322</t>
+          <t>https://m.place.naver.com/place/735546684</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8302,29 +8290,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>안젤라네일샵</t>
+          <t>삼층네일</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>angella3977@naver.com</t>
+          <t>wang8241@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1493-3335</t>
+          <t>0507-1327-8241</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/angella3977</t>
+          <t>https://blog.naver.com/wang8241</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8355,17 +8343,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>663</v>
+        <v>531</v>
       </c>
       <c r="Q85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R85" t="n">
-        <v>675</v>
+        <v>544</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8374,17 +8362,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1274163754</t>
+          <t>1894370134</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274163754</t>
+          <t>https://m.place.naver.com/place/1894370134</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8396,29 +8384,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>꽁냥네일</t>
+          <t>드로잉쇼</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>qorgh1236@naver.com</t>
+          <t>odshow@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1418-2440</t>
+          <t>02-777-1090</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 249-28 3층</t>
+          <t>서울특별시 중구 남대문로 60</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ggongnyang_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8428,7 +8416,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8449,17 +8437,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>276</v>
+        <v>2</v>
       </c>
       <c r="Q86" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>318</v>
+        <v>7</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8468,17 +8456,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1570914826</t>
+          <t>1726036993</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570914826</t>
+          <t>https://m.place.naver.com/place/1726036993</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8490,29 +8478,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>다리아네일 안국역</t>
+          <t>네일하트</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>puppyholic@naver.com</t>
+          <t>nailheart053@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1347-1494</t>
+          <t>0507-1484-8604</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daria_nail_ssu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8522,7 +8510,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8543,17 +8531,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>184</v>
+        <v>373</v>
       </c>
       <c r="Q87" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R87" t="n">
-        <v>186</v>
+        <v>382</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8562,17 +8550,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1165184706</t>
+          <t>1101101042</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165184706</t>
+          <t>https://m.place.naver.com/place/1101101042</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8584,25 +8572,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>오프엠네일</t>
+          <t>르모네일스튜디오</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>hgy___g@naver.com</t>
+          <t>borareview@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1374-9858</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 40 4층</t>
+          <t>서울특별시 종로구 동숭4가길 2 2층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/_lmonail</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8612,7 +8604,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8633,17 +8625,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="Q88" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="R88" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8652,17 +8644,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2099192808</t>
+          <t>1493224095</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099192808</t>
+          <t>https://m.place.naver.com/place/1493224095</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8674,29 +8666,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>네일쏘이</t>
+          <t>뉴문네일</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>xdaredare@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1334-9677</t>
+          <t>0507-1354-6577</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
+          <t>서울특별시 종로구 성균관로 7 2층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailssoi_</t>
+          <t>http://instagram.com/newmoonnail_</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8731,13 +8723,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R89" t="n">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8746,17 +8738,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1009120766</t>
+          <t>1689136529</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009120766</t>
+          <t>https://m.place.naver.com/place/1689136529</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8768,29 +8760,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>삼층네일</t>
+          <t>라라네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>wang8241@naver.com</t>
+          <t>redpepper30@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1327-8241</t>
+          <t>0507-1344-7250</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wang8241</t>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8805,7 +8797,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8821,17 +8813,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>531</v>
+        <v>1001</v>
       </c>
       <c r="Q90" t="n">
-        <v>13</v>
+        <v>431</v>
       </c>
       <c r="R90" t="n">
-        <v>544</v>
+        <v>1432</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8840,17 +8832,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1894370134</t>
+          <t>1303128966</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1894370134</t>
+          <t>https://m.place.naver.com/place/1303128966</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8862,29 +8854,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>위치네일스 종로점</t>
+          <t>꽁냥네일</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>qorgh1236@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1364-9020</t>
+          <t>0507-1418-2440</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 51</t>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8899,7 +8891,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8919,13 +8911,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1060</v>
+        <v>276</v>
       </c>
       <c r="Q91" t="n">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="R91" t="n">
-        <v>1209</v>
+        <v>318</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8934,17 +8926,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1543496206</t>
+          <t>1570914826</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543496206</t>
+          <t>https://m.place.naver.com/place/1570914826</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8956,29 +8948,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>꾸밈네일아트</t>
+          <t>프로뷰티</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>fusion02@naver.com</t>
+          <t>probeauty_blog@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>02-733-7942</t>
+          <t>0507-1435-2789</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
+          <t>서울특별시 중구 명동8가길 9 3층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/probeauty_blog</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8988,12 +8980,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9009,17 +9001,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2</v>
+        <v>570</v>
       </c>
       <c r="Q92" t="n">
-        <v>7</v>
+        <v>679</v>
       </c>
       <c r="R92" t="n">
-        <v>9</v>
+        <v>1249</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9028,17 +9020,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>614593678</t>
+          <t>19997455</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/614593678</t>
+          <t>https://m.place.naver.com/place/19997455</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9050,39 +9042,35 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JIN네일</t>
+          <t>네일지니</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jin_nail6453@naver.com</t>
+          <t>1231yc@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0507-1392-5159</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
+          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xeTiCG</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -9098,22 +9086,22 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>64</v>
+        <v>1772</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="R93" t="n">
-        <v>65</v>
+        <v>1865</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9122,17 +9110,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1530291597</t>
+          <t>1073291540</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1530291597</t>
+          <t>https://m.place.naver.com/place/1073291540</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9132,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>종로네일샵</t>
+          <t>그리다네일</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>bitna0614@naver.com</t>
+          <t>gridanail2@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>02-745-8375</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 62</t>
+          <t>서울특별시 종로구 대학로12길 77</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9197,13 +9189,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9212,17 +9204,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1928832758</t>
+          <t>142708597</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928832758</t>
+          <t>https://m.place.naver.com/place/142708597</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9234,29 +9226,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>드로잉쇼</t>
+          <t>nail by Jade</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>odshow@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>02-777-1090</t>
+          <t>0507-1360-1011</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 60</t>
+          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_by_jade</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9266,7 +9258,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9287,17 +9279,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Q95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9306,17 +9298,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1726036993</t>
+          <t>944614599</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726036993</t>
+          <t>https://m.place.naver.com/place/944614599</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9328,29 +9320,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>네일하트</t>
+          <t>에이커뷰티네일</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>nailheart053@naver.com</t>
+          <t>happymin_life@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1484-8604</t>
+          <t>02-722-5558</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/acre_beauty</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9360,7 +9352,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9381,17 +9373,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>373</v>
+        <v>117</v>
       </c>
       <c r="Q96" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R96" t="n">
-        <v>382</v>
+        <v>121</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9400,17 +9392,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1101101042</t>
+          <t>1812848399</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101101042</t>
+          <t>https://m.place.naver.com/place/1812848399</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9422,29 +9414,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>굿모닝네일</t>
+          <t>리빈네일</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>clsrn9606@naver.com</t>
+          <t>jcj0217@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1400-8607</t>
+          <t>0507-1349-9808</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gmnail_eyelash</t>
+          <t>https://www.instagram.com/rivin_nail</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9470,7 +9462,7 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -9479,13 +9471,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>241</v>
+        <v>128</v>
       </c>
       <c r="Q97" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9494,17 +9486,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>13051690</t>
+          <t>1315671750</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13051690</t>
+          <t>https://m.place.naver.com/place/1315671750</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9590,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9610,25 +9602,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>손톱그림</t>
+          <t>안젤라네일샵</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>on_calli@naver.com</t>
+          <t>angella3977@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1493-3335</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_sketch_8478/</t>
+          <t>https://blog.naver.com/angella3977</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9643,7 +9639,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9663,13 +9659,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3</v>
+        <v>664</v>
       </c>
       <c r="Q99" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="R99" t="n">
-        <v>76</v>
+        <v>676</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9678,17 +9674,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1124095560</t>
+          <t>1274163754</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1124095560</t>
+          <t>https://m.place.naver.com/place/1274163754</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9700,29 +9696,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>제이뷰티 눈썹&amp;네일</t>
+          <t>꾸미다</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jbeauty4022@naver.com</t>
+          <t>yem1104@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0507-1422-4022</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
+          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jbeauty4022</t>
+          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9737,7 +9729,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9757,13 +9749,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3316</v>
+        <v>1</v>
       </c>
       <c r="Q100" t="n">
-        <v>226</v>
+        <v>3</v>
       </c>
       <c r="R100" t="n">
-        <v>3542</v>
+        <v>4</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9772,17 +9764,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1776791877</t>
+          <t>1095499576</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776791877</t>
+          <t>https://m.place.naver.com/place/1095499576</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9794,29 +9786,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>폭시네일</t>
+          <t>Diamond Nails</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>tomebooy@naver.com</t>
+          <t>ksj673232@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1403-4791</t>
+          <t>0507-1420-1393</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동망산길 13 2층</t>
+          <t>서울특별시 중구 마른내로 155 1동 102호</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9826,7 +9818,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9847,17 +9839,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9866,17 +9858,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>40986070</t>
+          <t>2040524360</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/40986070</t>
+          <t>https://m.place.naver.com/place/2040524360</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9888,29 +9880,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>네일해썸</t>
+          <t>네일브러쉬</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>llllcmalll@naver.com</t>
+          <t>ss7370306@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0507-1342-3168</t>
+          <t>0507-1332-0306</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
+          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hatssome</t>
+          <t>https://blog.naver.com/ss7370306</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9925,7 +9917,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9936,22 +9928,22 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="Q102" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R102" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9960,17 +9952,17 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1991633917</t>
+          <t>35559430</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991633917</t>
+          <t>https://m.place.naver.com/place/35559430</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9982,29 +9974,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>베리네일</t>
+          <t>가빈네일</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ems0619@naver.com</t>
+          <t>happyhannj@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0507-1419-6623</t>
+          <t>0507-1431-8259</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
+          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/berry_nail_</t>
+          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10039,13 +10031,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="Q103" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R103" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10054,17 +10046,17 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1394925944</t>
+          <t>38500996</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394925944</t>
+          <t>https://m.place.naver.com/place/38500996</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10076,29 +10068,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>르모네일스튜디오</t>
+          <t>영심이손톱</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>mylifegoal@naver.com</t>
+          <t>lovellies@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1374-9858</t>
+          <t>02-735-0031</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동숭4가길 2 2층</t>
+          <t>서울특별시 종로구 종로 88 701호</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>http://instagram.com/_lmonail</t>
+          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10133,13 +10125,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10148,17 +10140,17 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1493224095</t>
+          <t>1116851430</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493224095</t>
+          <t>https://m.place.naver.com/place/1116851430</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10170,25 +10162,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>네일해요</t>
+          <t>치즈네일</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>elliestar@naver.com</t>
+          <t>43995@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>02-6405-4578</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로44길 9 2층</t>
+          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cheesenail</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10198,7 +10194,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10219,17 +10215,17 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10238,17 +10234,17 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1213168091</t>
+          <t>37542182</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213168091</t>
+          <t>https://m.place.naver.com/place/37542182</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10260,29 +10256,25 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>9층네일 명동점</t>
+          <t>릴리엔젤네일</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>dmgktnqls@naver.com</t>
+          <t>kiyu0987@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>0507-1359-1372</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 25-1 303호</t>
+          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9.nailstudio</t>
+          <t>http://instagram.com/lilyangel_nail</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10317,13 +10309,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="Q106" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="R106" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10332,17 +10324,17 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1681308543</t>
+          <t>1110775717</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681308543</t>
+          <t>https://m.place.naver.com/place/1110775717</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10354,39 +10346,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>크리스탈손톱</t>
+          <t>아머네일</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>juyean123@naver.com</t>
+          <t>dntndus111@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>02-3398-4445</t>
+          <t>0507-1364-4429</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 275</t>
+          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_pzkMG</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -10402,22 +10394,22 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3</v>
+        <v>262</v>
       </c>
       <c r="Q107" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="R107" t="n">
-        <v>4</v>
+        <v>359</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10426,17 +10418,17 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1895018257</t>
+          <t>1312237193</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895018257</t>
+          <t>https://m.place.naver.com/place/1312237193</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10448,12 +10440,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>비조네일</t>
+          <t>살롱드소피</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>shoot13445@naver.com</t>
+          <t>skincare25@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -10461,12 +10453,12 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 379</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/salon_de_sophie_</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10476,7 +10468,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10497,17 +10489,17 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="Q108" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="R108" t="n">
-        <v>5</v>
+        <v>175</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10516,17 +10508,17 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>19813956</t>
+          <t>13434920</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19813956</t>
+          <t>https://m.place.naver.com/place/13434920</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10538,29 +10530,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>에이커뷰티네일</t>
+          <t>종로네일샵</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>happymin_life@naver.com</t>
+          <t>bitna0614@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>02-722-5558</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
+          <t>서울특별시 종로구 종로 62</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>http://instagram.com/acre_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10570,7 +10558,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -10591,17 +10579,17 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10610,17 +10598,17 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1812848399</t>
+          <t>1928832758</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1812848399</t>
+          <t>https://m.place.naver.com/place/1928832758</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10632,29 +10620,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>라라네일</t>
+          <t>루다네일</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>redpepper30@naver.com</t>
+          <t>rudanail1515@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0507-1344-7250</t>
+          <t>0507-1357-1516</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lalanail_myeongdong</t>
+          <t>http://instagram.com/rudanail_daehakro</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10680,7 +10668,7 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -10689,13 +10677,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1001</v>
+        <v>254</v>
       </c>
       <c r="Q110" t="n">
-        <v>431</v>
+        <v>112</v>
       </c>
       <c r="R110" t="n">
-        <v>1432</v>
+        <v>366</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10704,17 +10692,17 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1303128966</t>
+          <t>34551572</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303128966</t>
+          <t>https://m.place.naver.com/place/34551572</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10726,25 +10714,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>지아네일</t>
+          <t>엘로아네일</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>jjaa1334@naver.com</t>
+          <t>hhhong88@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0507-1314-9339</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 40 6층</t>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeonjia9</t>
+          <t>https://www.instagram.com/eloa__nail/</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10779,13 +10771,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="Q111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10794,17 +10786,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1279897442</t>
+          <t>2087274322</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279897442</t>
+          <t>https://m.place.naver.com/place/2087274322</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10816,29 +10808,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>빌러브드 네일</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ksy3315@naver.com</t>
+          <t>novembro_12@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0507-1358-8653</t>
+          <t>02-733-8318</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lee____</t>
+          <t>http://www.instagram.com/beloved_nail_</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10873,13 +10865,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>110</v>
+        <v>371</v>
       </c>
       <c r="Q112" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="R112" t="n">
-        <v>119</v>
+        <v>400</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10888,17 +10880,17 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>2065943871</t>
+          <t>877681682</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065943871</t>
+          <t>https://m.place.naver.com/place/877681682</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10910,29 +10902,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>네일,현</t>
+          <t>네일온 명동본점</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>qkrwlsk126@naver.com</t>
+          <t>nailon_myeongdong@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0507-1316-0133</t>
+          <t>0507-1302-8995</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
+          <t>서울특별시 중구 을지로 88 을특8호</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hyun.__</t>
+          <t>https://blog.naver.com/nailon_myeongdong</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10947,7 +10939,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10967,13 +10959,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>174</v>
+        <v>28</v>
       </c>
       <c r="Q113" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="R113" t="n">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10982,17 +10974,17 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1120708839</t>
+          <t>2054691209</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120708839</t>
+          <t>https://m.place.naver.com/place/2054691209</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -11004,25 +10996,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>꾸미다</t>
+          <t>크리스탈손톱</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>yem1104@naver.com</t>
+          <t>juyean123@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>02-3398-4445</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
+          <t>서울특별시 중구 장충단로 275</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11032,7 +11028,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11053,14 +11049,14 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P114" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q114" t="n">
         <v>1</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>3</v>
       </c>
       <c r="R114" t="n">
         <v>4</v>
@@ -11072,17 +11068,17 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1095499576</t>
+          <t>1895018257</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095499576</t>
+          <t>https://m.place.naver.com/place/1895018257</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -11094,25 +11090,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>어나더네일</t>
+          <t>효녀네일</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>soojinpo@naver.com</t>
+          <t>hy0d0ng2@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0507-1366-2991</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 56-1 1층</t>
+          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/another_n_ail</t>
+          <t>https://www.instagram.com/hyonyeo_nail</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11147,13 +11147,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="Q115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11162,17 +11162,17 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1214193406</t>
+          <t>2038116522</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214193406</t>
+          <t>https://m.place.naver.com/place/2038116522</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/종로_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/종로_네일샵.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>루아르블랑 네일</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>failuredw@naver.com</t>
-        </is>
-      </c>
+          <t>오드리네일</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1483-9411</t>
+          <t>02-722-1384</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
+          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHajSJei</t>
+          <t>https://www.instagram.com/audreynail_official</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>256</v>
       </c>
       <c r="R2" t="n">
-        <v>240</v>
+        <v>484</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2013893243</t>
+          <t>13450587</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013893243</t>
+          <t>https://m.place.naver.com/place/13450587</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,24 +654,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>혜리앤케어</t>
+          <t>아셀네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>micahyesung@naver.com</t>
+          <t>asher9809@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>02-725-1741</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
+          <t>서울특별시 중구 장충단로 253 10층 11호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -715,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +722,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>155402276</t>
+          <t>1229434440</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/155402276</t>
+          <t>https://m.place.naver.com/place/1229434440</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +744,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>빌러브드 네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>novembro_12@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-318-6668</t>
+          <t>02-733-8318</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
+          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/beloved_nail_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +776,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +797,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>88</v>
+        <v>371</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="R4" t="n">
-        <v>102</v>
+        <v>400</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +816,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1874418389</t>
+          <t>877681682</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874418389</t>
+          <t>https://m.place.naver.com/place/877681682</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +838,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바움네일</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>harulov@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티숲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1330-3151</t>
+          <t>0507-1438-7477</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로9길 37 2층</t>
+          <t>서울특별시 종로구 지봉로 37-29 103호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/baum_nail</t>
+          <t>https://www.instagram.com/nailsoop_sj/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +891,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>559</v>
+        <v>58</v>
       </c>
       <c r="Q5" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>606</v>
+        <v>58</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +906,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1954514000</t>
+          <t>1158436638</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954514000</t>
+          <t>https://m.place.naver.com/place/1158436638</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,25 +928,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>해피네일데이</t>
+          <t>꾸밈네일아트</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>happynailday@naver.com</t>
+          <t>fusion02@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>02-733-7942</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
+          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/happynailday</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -968,12 +960,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -989,17 +981,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>166</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>184</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1000,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>298136226</t>
+          <t>614593678</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/298136226</t>
+          <t>https://m.place.naver.com/place/614593678</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,29 +1022,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일하루</t>
+          <t>효녀네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nail_haru@naver.com</t>
+          <t>hy0d0ng2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1361-1445</t>
+          <t>0507-1366-2991</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
+          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_haru</t>
+          <t>https://www.instagram.com/hyonyeo_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1067,7 +1059,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1083,17 +1075,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>413</v>
+        <v>4</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1094,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37089409</t>
+          <t>2038116522</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37089409</t>
+          <t>https://m.place.naver.com/place/2038116522</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,29 +1116,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베리네일</t>
+          <t>지아네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ems0619@naver.com</t>
+          <t>jjaa1334@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1419-6623</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
+          <t>서울특별시 중구 명동10길 40 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/berry_nail_</t>
+          <t>https://www.instagram.com/jeonjia9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1184,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1394925944</t>
+          <t>1279897442</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394925944</t>
+          <t>https://m.place.naver.com/place/1279897442</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1218,25 +1206,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>살롱드벨르네일</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>salondebelle_nail@naver.com</t>
-        </is>
-      </c>
+          <t>오프엠네일</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 65 2층 208호</t>
+          <t>서울특별시 중구 명동4길 40 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/salondebelle_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1246,12 +1230,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1267,17 +1251,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>355</v>
+        <v>95</v>
       </c>
       <c r="Q9" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>416</v>
+        <v>101</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1768571536</t>
+          <t>2099192808</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768571536</t>
+          <t>https://m.place.naver.com/place/2099192808</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,29 +1292,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9층네일 명동점</t>
+          <t>네일아토</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dmgktnqls@naver.com</t>
+          <t>sk3374@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-1372</t>
+          <t>0507-1416-6630</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 25-1 303호</t>
+          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9.nailstudio</t>
+          <t>https://www.instagram.com/nail_ato</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,13 +1349,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="Q10" t="n">
         <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>281</v>
+        <v>215</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1364,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1681308543</t>
+          <t>1446399532</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681308543</t>
+          <t>https://m.place.naver.com/place/1446399532</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,29 +1386,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>꽃소니 네일아트</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>qhpw4cpk@naver.com</t>
-        </is>
-      </c>
+          <t>찰스네일</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>070-8615-3478</t>
+          <t>0507-1307-4179</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로5길 8 2층</t>
+          <t>서울특별시 종로구 종로12길 9 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flower_handnails</t>
+          <t>http://www.instagram.com/charles__nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1439,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>105</v>
+        <v>529</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="R11" t="n">
-        <v>109</v>
+        <v>585</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1454,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1593950281</t>
+          <t>13034248</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593950281</t>
+          <t>https://m.place.naver.com/place/13034248</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,34 +1476,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>르노브네일</t>
+          <t>릴리엔젤네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hshee069@naver.com</t>
+          <t>kiyu0987@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1307-5439</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 38 1층</t>
+          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XxbVPn</t>
+          <t>http://instagram.com/lilyangel_nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1544,7 +1520,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1553,13 +1529,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>405</v>
+        <v>235</v>
       </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="R12" t="n">
-        <v>426</v>
+        <v>287</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,12 +1544,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1890443515</t>
+          <t>1110775717</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1890443515</t>
+          <t>https://m.place.naver.com/place/1110775717</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1590,29 +1566,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>올리브네일&amp;속눈썹</t>
+          <t>네일멜로우</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>djdjqq1663@naver.com</t>
+          <t>sc09mc@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>02-2075-7775</t>
+          <t>0507-1356-7672</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/djdjqq1663</t>
+          <t>https://www.instagram.com/nail_mellow_11/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1627,7 +1603,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1638,7 +1614,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1647,13 +1623,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3106</v>
+        <v>389</v>
       </c>
       <c r="Q13" t="n">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="R13" t="n">
-        <v>3356</v>
+        <v>423</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,12 +1638,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>35751284</t>
+          <t>1933958367</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35751284</t>
+          <t>https://m.place.naver.com/place/1933958367</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1684,29 +1660,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>너 참 예쁘다</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>yuiu1401@naver.com</t>
-        </is>
-      </c>
+          <t>바움네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1434-8892</t>
+          <t>0507-1330-3151</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
+          <t>서울특별시 종로구 대학로9길 37 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/youarebeautiful_seoul</t>
+          <t>https://www.instagram.com/baum_nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1726,14 +1698,10 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1745,13 +1713,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="Q14" t="n">
-        <v>840</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>1369</v>
+        <v>606</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,12 +1728,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1466732665</t>
+          <t>1954514000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466732665</t>
+          <t>https://m.place.naver.com/place/1954514000</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1782,29 +1750,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>바비 네일왁싱</t>
+          <t>말짜네일 광화문점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>uchka247@naver.com</t>
+          <t>malzzanail@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1490-9887</t>
+          <t>0507-1402-3734</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로44길 6-9 4층</t>
+          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barbie.waxnail</t>
+          <t>https://blog.naver.com/malzzanail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,7 +1787,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1830,7 +1798,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1839,13 +1807,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>161</v>
+        <v>305</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>424</v>
       </c>
       <c r="R15" t="n">
-        <v>164</v>
+        <v>729</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,12 +1822,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1019484164</t>
+          <t>37997776</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1019484164</t>
+          <t>https://m.place.naver.com/place/37997776</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1876,29 +1844,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>키튼네일</t>
+          <t>네일로드</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dbgpwn0626@naver.com</t>
+          <t>lordnail@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02-765-8566</t>
+          <t>02-734-1730</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
+          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1908,7 +1876,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1929,17 +1897,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>537</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,12 +1916,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1065031131</t>
+          <t>206289152</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065031131</t>
+          <t>https://m.place.naver.com/place/206289152</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1970,29 +1938,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>말짜네일 광화문점</t>
+          <t>네일라이트</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>malzzanail@naver.com</t>
+          <t>elegant1025@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1402-3734</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
+          <t>서울특별시 종로구 세종대로23길 5 3층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/malzzanail</t>
+          <t>http://instagram.com/_nail_light_</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2007,7 +1971,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2018,7 +1982,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2027,13 +1991,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>305</v>
+        <v>540</v>
       </c>
       <c r="Q17" t="n">
-        <v>424</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>729</v>
+        <v>546</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,12 +2006,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>37997776</t>
+          <t>1105652769</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37997776</t>
+          <t>https://m.place.naver.com/place/1105652769</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2064,29 +2028,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>디디 네일바</t>
+          <t>꽃소니 네일아트</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>heeja090@naver.com</t>
+          <t>qhpw4cpk@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1476-0228</t>
+          <t>070-8615-3478</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
+          <t>서울특별시 종로구 대학로5길 8 2층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/didi___nailbar</t>
+          <t>https://www.instagram.com/flower_handnails</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2121,13 +2085,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,12 +2100,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1134899134</t>
+          <t>1593950281</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134899134</t>
+          <t>https://m.place.naver.com/place/1593950281</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2158,12 +2122,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>손톱그림</t>
+          <t>이츠네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>on_calli@naver.com</t>
+          <t>icacc89@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2171,17 +2135,17 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
+          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_sketch_8478/</t>
+          <t>http://pf.kakao.com/_duxhxdn</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2202,7 +2166,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2211,13 +2175,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="Q19" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,12 +2190,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1124095560</t>
+          <t>31949587</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1124095560</t>
+          <t>https://m.place.naver.com/place/31949587</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2248,29 +2212,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>뷰티숲</t>
+          <t>가빈네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>smallwarestore@naver.com</t>
+          <t>happyhannj@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1438-7477</t>
+          <t>0507-1431-8259</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 37-29 103호</t>
+          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailsoop_sj/</t>
+          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2308,10 +2272,10 @@
         <v>58</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,12 +2284,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1158436638</t>
+          <t>38500996</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158436638</t>
+          <t>https://m.place.naver.com/place/38500996</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2342,29 +2306,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일누하</t>
+          <t>그리다네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>gridanail2@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1348-9398</t>
+          <t>02-745-8375</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
+          <t>서울특별시 종로구 대학로12길 77</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.nuha</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2374,7 +2338,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2395,17 +2359,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,12 +2378,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1370069746</t>
+          <t>142708597</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370069746</t>
+          <t>https://m.place.naver.com/place/142708597</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2436,12 +2400,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>모스네일</t>
+          <t>네일&amp;페일아트</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>buzzerrbeate@naver.com</t>
+          <t>lsbangel@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2449,12 +2413,12 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
+          <t>서울특별시 종로구 진흥로 446</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss.nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2464,7 +2428,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2480,22 +2444,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>239</v>
+        <v>2</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,12 +2468,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1061088069</t>
+          <t>20871402</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061088069</t>
+          <t>https://m.place.naver.com/place/20871402</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2526,35 +2490,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>비비네일</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>kikiu30@naver.com</t>
-        </is>
-      </c>
+          <t>엔79 Nail</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1390-0326</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
+          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pAtmG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2570,22 +2534,22 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1852</v>
+        <v>163</v>
       </c>
       <c r="Q23" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="R23" t="n">
-        <v>1913</v>
+        <v>182</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,12 +2558,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1712141242</t>
+          <t>1756267523</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712141242</t>
+          <t>https://m.place.naver.com/place/1756267523</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2616,29 +2580,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>안0네일</t>
+          <t>올리브네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ysl6161015@naver.com</t>
+          <t>djdjqq1663@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02-6052-7778</t>
+          <t>02-2075-7775</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
+          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/djdjqq1663</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2648,12 +2612,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2664,22 +2628,22 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>19</v>
+        <v>3106</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R24" t="n">
-        <v>19</v>
+        <v>3356</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,12 +2652,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1487336161</t>
+          <t>35751284</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487336161</t>
+          <t>https://m.place.naver.com/place/35751284</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2800,25 +2764,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>아셀네일</t>
+          <t>키튼네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>asher9809@naver.com</t>
+          <t>dbgpwn0626@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>02-765-8566</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 253 10층 11호</t>
+          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2828,7 +2796,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2849,17 +2817,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>59</v>
+        <v>484</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="R26" t="n">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2868,12 +2836,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1229434440</t>
+          <t>1065031131</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229434440</t>
+          <t>https://m.place.naver.com/place/1065031131</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2890,29 +2858,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>그리드네일</t>
+          <t>핸더뷰티</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>boye_like@naver.com</t>
+          <t>koenji_nail@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1405-0461</t>
+          <t>0507-1380-1146</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 44</t>
+          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://instagram.com/love_grid</t>
+          <t>https://blog.naver.com/koenji_nail</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2927,7 +2895,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2947,13 +2915,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>53</v>
+        <v>357</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>412</v>
       </c>
       <c r="R27" t="n">
-        <v>55</v>
+        <v>769</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,12 +2930,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38531607</t>
+          <t>37558905</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531607</t>
+          <t>https://m.place.naver.com/place/37558905</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2984,25 +2952,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>페이브 네일 스튜디오</t>
+          <t>프로뷰티</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ekdmaekfdpqnwk@naver.com</t>
+          <t>probeauty_blog@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1435-2789</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
+          <t>서울특별시 중구 명동8가길 9 3층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sUKlei7f</t>
+          <t>https://blog.naver.com/probeauty_blog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3017,7 +2989,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3028,7 +3000,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3037,13 +3009,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>63</v>
+        <v>570</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>679</v>
       </c>
       <c r="R28" t="n">
-        <v>96</v>
+        <v>1249</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3052,12 +3024,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1109114407</t>
+          <t>19997455</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109114407</t>
+          <t>https://m.place.naver.com/place/19997455</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3074,29 +3046,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>페이브 네일 스튜디오</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ysbfly@naver.com</t>
+          <t>ekdmaekfdpqnwk@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1358-8653</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lee____</t>
+          <t>https://open.kakao.com/o/sUKlei7f</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3122,7 +3090,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3131,13 +3099,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="R29" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,12 +3114,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2065943871</t>
+          <t>1109114407</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065943871</t>
+          <t>https://m.place.naver.com/place/1109114407</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3168,29 +3136,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>오브 코코네일</t>
+          <t>네일해요</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>xiah15holic@naver.com</t>
+          <t>elliestar@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1371-8921</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
+          <t>서울특별시 종로구 종로44길 9 2층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ofconail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3200,7 +3164,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3221,17 +3185,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>658</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>705</v>
+        <v>6</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,12 +3204,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1009626425</t>
+          <t>1213168091</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009626425</t>
+          <t>https://m.place.naver.com/place/1213168091</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3262,29 +3226,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>수야디나 네일&amp;래쉬</t>
+          <t>삼층네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>vastron@naver.com</t>
+          <t>wang8241@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1305-2499</t>
+          <t>0507-1327-8241</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 중구 충무로 36 2층</t>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yun_ju423/</t>
+          <t>https://blog.naver.com/wang8241</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3299,7 +3263,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3315,17 +3279,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="Q31" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>216</v>
+        <v>544</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3334,12 +3298,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1324800762</t>
+          <t>1894370134</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324800762</t>
+          <t>https://m.place.naver.com/place/1894370134</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3356,29 +3320,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>미스에이 네일</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>kinetixart@naver.com</t>
-        </is>
-      </c>
+          <t>르모네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>070-8277-3597</t>
+          <t>0507-1374-9858</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
+          <t>서울특별시 종로구 동숭4가길 2 2층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_jhDaG</t>
+          <t>http://instagram.com/_lmonail</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3393,7 +3353,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3404,7 +3364,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3413,13 +3373,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R32" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3428,12 +3388,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1758327919</t>
+          <t>1493224095</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758327919</t>
+          <t>https://m.place.naver.com/place/1493224095</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3450,29 +3410,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>드네일 광화문점</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dahaeyoo@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1351-9192</t>
+          <t>0507-1322-4179</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
+          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
+          <t>https://open.kakao.com/o/sdED0A2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3498,7 +3458,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3507,13 +3467,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="Q33" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
-        <v>37</v>
+        <v>264</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,12 +3482,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1372444756</t>
+          <t>1054499609</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1372444756</t>
+          <t>https://m.place.naver.com/place/1054499609</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3544,29 +3504,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>핸더뷰티</t>
+          <t>블링네일 종로점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>koenji_nail@naver.com</t>
+          <t>beaulynail@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1380-1146</t>
+          <t>0507-1448-0036</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
+          <t>서울특별시 종로구 대학로 16-1 1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/koenji_nail</t>
+          <t>https://blog.naver.com/beaulynail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3601,13 +3561,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>357</v>
+        <v>143</v>
       </c>
       <c r="Q34" t="n">
-        <v>412</v>
+        <v>73</v>
       </c>
       <c r="R34" t="n">
-        <v>769</v>
+        <v>216</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,12 +3576,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>37558905</t>
+          <t>60890323</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37558905</t>
+          <t>https://m.place.naver.com/place/60890323</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3638,25 +3598,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일, 사월</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>pooddin@naver.com</t>
-        </is>
-      </c>
+          <t>Diamond Nails</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1420-1393</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
+          <t>서울특별시 중구 마른내로 155 1동 102호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__april</t>
+          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3691,13 +3651,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>644</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3706,12 +3666,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1448977317</t>
+          <t>2040524360</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448977317</t>
+          <t>https://m.place.naver.com/place/2040524360</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3728,29 +3688,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일그리미</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>tory0413@naver.com</t>
-        </is>
-      </c>
+          <t>네일, 사월</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0507-1322-4179</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
+          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sdED0A2</t>
+          <t>https://www.instagram.com/nail__april</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3776,7 +3728,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3785,13 +3737,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>249</v>
+        <v>644</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R36" t="n">
-        <v>264</v>
+        <v>658</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3800,12 +3752,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1054499609</t>
+          <t>1448977317</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054499609</t>
+          <t>https://m.place.naver.com/place/1448977317</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3822,43 +3774,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>레푸스 종로점</t>
+          <t>라라네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>refuss_jong_ro@naver.com</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>chy0802@ahasoft.co.kr</t>
-        </is>
-      </c>
+          <t>redpepper30@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>02-720-4544</t>
+          <t>0507-1344-7250</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/857013</t>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3883,13 +3831,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>862</v>
+        <v>1001</v>
       </c>
       <c r="Q37" t="n">
-        <v>360</v>
+        <v>431</v>
       </c>
       <c r="R37" t="n">
-        <v>1222</v>
+        <v>1432</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3898,12 +3846,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1237692187</t>
+          <t>1303128966</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237692187</t>
+          <t>https://m.place.naver.com/place/1303128966</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3920,34 +3868,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네일아토</t>
+          <t>르노브네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sk3374@naver.com</t>
+          <t>hshee069@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1416-6630</t>
+          <t>0507-1307-5439</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
+          <t>서울특별시 종로구 성균관로 38 1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ato</t>
+          <t>http://pf.kakao.com/_XxbVPn</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3968,7 +3916,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3977,13 +3925,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>192</v>
+        <v>406</v>
       </c>
       <c r="Q38" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R38" t="n">
-        <v>215</v>
+        <v>427</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,12 +3940,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1446399532</t>
+          <t>1890443515</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446399532</t>
+          <t>https://m.place.naver.com/place/1890443515</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4014,24 +3962,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일 김미쉘터</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>patent37435@naver.com</t>
-        </is>
-      </c>
+          <t>비조네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1320-1993</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 55</t>
+          <t>서울특별시 종로구 종로 379</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4071,13 +4011,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>266</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>270</v>
+        <v>5</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,12 +4026,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1802694964</t>
+          <t>19813956</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802694964</t>
+          <t>https://m.place.naver.com/place/19813956</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4108,29 +4048,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>블링네일 종로점</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>beaulynail@naver.com</t>
-        </is>
-      </c>
+          <t>JIN네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1448-0036</t>
+          <t>0507-1392-5159</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 16-1 1층</t>
+          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beaulynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4140,12 +4076,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4161,17 +4097,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="Q40" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,12 +4116,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>60890323</t>
+          <t>1530291597</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60890323</t>
+          <t>https://m.place.naver.com/place/1530291597</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4202,29 +4138,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>엔79 Nail</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>loveucream@naver.com</t>
-        </is>
-      </c>
+          <t>에이탑네일</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1390-0326</t>
+          <t>0507-1372-2148</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
+          <t>서울특별시 중구 명동4길 12-1 3층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/a.top_nail</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4234,7 +4166,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4255,17 +4187,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>163</v>
+        <v>259</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="R41" t="n">
-        <v>182</v>
+        <v>326</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,12 +4206,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1756267523</t>
+          <t>1446197361</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756267523</t>
+          <t>https://m.place.naver.com/place/1446197361</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4296,29 +4228,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일바이안</t>
+          <t>드네일 광화문점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ye1yang@naver.com</t>
+          <t>dahaeyoo@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02-511-5621</t>
+          <t>0507-1351-9192</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로9길 12 8층</t>
+          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyahn</t>
+          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4353,13 +4285,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="Q42" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="R42" t="n">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,12 +4300,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1084164588</t>
+          <t>1372444756</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084164588</t>
+          <t>https://m.place.naver.com/place/1372444756</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4390,30 +4322,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>이츠네일</t>
+          <t>수야디나 네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>icacc89@naver.com</t>
+          <t>vastron@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1305-2499</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
+          <t>서울특별시 중구 충무로 36 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_duxhxdn</t>
+          <t>https://www.instagram.com/yun_ju423/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4434,7 +4370,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4443,13 +4379,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="R43" t="n">
-        <v>92</v>
+        <v>216</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4458,12 +4394,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>31949587</t>
+          <t>1324800762</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31949587</t>
+          <t>https://m.place.naver.com/place/1324800762</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4480,29 +4416,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
+          <t>네일쏘이</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>annoi_@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02-756-4143</t>
+          <t>0507-1334-9677</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
+          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailssoi_</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4512,7 +4448,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4533,17 +4469,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,12 +4488,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>31315234</t>
+          <t>1009120766</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315234</t>
+          <t>https://m.place.naver.com/place/1009120766</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4574,25 +4510,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>비조네일</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>shoot13445@naver.com</t>
-        </is>
-      </c>
+          <t>파라테라피네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 379</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail._.again</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4602,7 +4534,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4623,17 +4555,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>291</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R45" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4642,12 +4574,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>19813956</t>
+          <t>1996157285</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19813956</t>
+          <t>https://m.place.naver.com/place/1996157285</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4664,25 +4596,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일라이트</t>
+          <t>치즈네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>elegant1025@naver.com</t>
+          <t>43995@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02-6405-4578</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 5 3층</t>
+          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_light_</t>
+          <t>https://www.instagram.com/cheesenail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4717,13 +4653,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>540</v>
+        <v>57</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>546</v>
+        <v>58</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4732,12 +4668,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1105652769</t>
+          <t>37542182</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105652769</t>
+          <t>https://m.place.naver.com/place/37542182</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4754,29 +4690,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JIN네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>jin_nail6453@naver.com</t>
-        </is>
-      </c>
+          <t>엘로아네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1392-5159</t>
+          <t>0507-1314-9339</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/eloa__nail/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4786,7 +4718,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4807,17 +4739,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4826,12 +4758,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1530291597</t>
+          <t>2087274322</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1530291597</t>
+          <t>https://m.place.naver.com/place/2087274322</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4848,29 +4780,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>드팜므</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>mellowryu@naver.com</t>
-        </is>
-      </c>
+          <t>9층네일 명동점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1317-3395</t>
+          <t>0507-1359-1372</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 42 B110호</t>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/defemmeeee</t>
+          <t>https://www.instagram.com/9.nailstudio</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4905,13 +4833,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="Q48" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="R48" t="n">
-        <v>145</v>
+        <v>281</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,12 +4848,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1741921081</t>
+          <t>1681308543</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1741921081</t>
+          <t>https://m.place.naver.com/place/1681308543</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4942,25 +4870,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>오프엠네일</t>
+          <t>네일해썸</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hgy___g@naver.com</t>
+          <t>llllcmalll@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1342-3168</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 40 4층</t>
+          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_hatssome</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4970,7 +4902,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4986,22 +4918,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R49" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5010,12 +4942,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2099192808</t>
+          <t>1991633917</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099192808</t>
+          <t>https://m.place.naver.com/place/1991633917</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5032,25 +4964,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>세아현대아울렛동대문점</t>
+          <t>강앤니네일스</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>anne0504@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1468-2316</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 현대아울렛동대문점B1</t>
+          <t>서울특별시 중구 장충단로 227-2 4층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/kangannynails</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5060,7 +4996,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5081,17 +5017,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5100,12 +5036,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1421171519</t>
+          <t>1711237836</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421171519</t>
+          <t>https://m.place.naver.com/place/1711237836</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5122,25 +5058,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>아트만네일</t>
+          <t>레푸스 종로점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ppangsun238@naver.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+          <t>refuss_jong_ro@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>chy0802@ahasoft.co.kr</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>02-720-4544</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
+          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Txkxgfxj</t>
+          <t>https://booking.naver.com/booking/13/bizes/857013</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5150,7 +5094,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5166,7 +5110,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5175,13 +5119,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>16</v>
+        <v>862</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="R51" t="n">
-        <v>36</v>
+        <v>1222</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5190,12 +5134,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1284929161</t>
+          <t>1237692187</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284929161</t>
+          <t>https://m.place.naver.com/place/1237692187</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5212,24 +5156,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>폭시네일</t>
+          <t>드로잉쇼</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>tomebooy@naver.com</t>
+          <t>odshow@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1403-4791</t>
+          <t>02-777-1090</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동망산길 13 2층</t>
+          <t>서울특별시 중구 남대문로 60</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5269,13 +5213,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5284,12 +5228,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>40986070</t>
+          <t>1726036993</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/40986070</t>
+          <t>https://m.place.naver.com/place/1726036993</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5306,25 +5250,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>파라테라피네일</t>
+          <t>네일누하</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>anrgudtkd@naver.com</t>
+          <t>annoi_@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1348-9398</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
+          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail._.again</t>
+          <t>https://www.instagram.com/nail.nuha</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5359,13 +5307,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>291</v>
+        <v>16</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="R53" t="n">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5374,12 +5322,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1996157285</t>
+          <t>1370069746</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996157285</t>
+          <t>https://m.place.naver.com/place/1370069746</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5396,34 +5344,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>맥스네일</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>machojj@naver.com</t>
+          <t>kikiu30@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>02-2272-4141</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 204 3층</t>
+          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/machojj</t>
+          <t>http://pf.kakao.com/_pAtmG</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5433,7 +5377,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5444,7 +5388,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5453,13 +5397,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>198</v>
+        <v>1852</v>
       </c>
       <c r="Q54" t="n">
-        <v>532</v>
+        <v>61</v>
       </c>
       <c r="R54" t="n">
-        <v>730</v>
+        <v>1913</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5468,12 +5412,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>32786203</t>
+          <t>1712141242</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32786203</t>
+          <t>https://m.place.naver.com/place/1712141242</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5490,29 +5434,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>위치네일스 종로점</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>witch_nail@naver.com</t>
-        </is>
-      </c>
+          <t>모스네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0507-1364-9020</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 51</t>
+          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>https://www.instagram.com/moss.nail_</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5527,7 +5463,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5538,7 +5474,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5547,13 +5483,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1060</v>
+        <v>226</v>
       </c>
       <c r="Q55" t="n">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="R55" t="n">
-        <v>1209</v>
+        <v>239</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5562,12 +5498,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1543496206</t>
+          <t>1061088069</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543496206</t>
+          <t>https://m.place.naver.com/place/1061088069</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5584,25 +5520,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>지아네일</t>
+          <t>네일 김미쉘터</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jjaa1334@naver.com</t>
+          <t>patent37435@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1320-1993</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 40 6층</t>
+          <t>서울특별시 종로구 필운대로 55</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeonjia9</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5612,7 +5552,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5633,17 +5573,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5652,12 +5592,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1279897442</t>
+          <t>1802694964</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279897442</t>
+          <t>https://m.place.naver.com/place/1802694964</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5674,29 +5614,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>무아네일</t>
+          <t>다리아네일 안국역</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>loowowool@naver.com</t>
+          <t>puppyholic@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1436-1716</t>
+          <t>0507-1347-1494</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
+          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/daria_nail_ssu</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5731,13 +5671,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>184</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5746,12 +5686,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2038424794</t>
+          <t>1165184706</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038424794</t>
+          <t>https://m.place.naver.com/place/1165184706</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5768,29 +5708,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>마이파우치</t>
+          <t>제이뷰티 눈썹&amp;네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>323redtree@naver.com</t>
+          <t>jbeauty4022@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1402-0809</t>
+          <t>0507-1422-4022</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
+          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mypouch.kangbbin</t>
+          <t>https://blog.naver.com/jbeauty4022</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5805,7 +5745,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5825,13 +5765,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>11</v>
+        <v>3316</v>
       </c>
       <c r="Q58" t="n">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="R58" t="n">
-        <v>194</v>
+        <v>3542</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5840,12 +5780,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>38642341</t>
+          <t>1776791877</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38642341</t>
+          <t>https://m.place.naver.com/place/1776791877</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5862,39 +5802,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>꾸밈네일아트</t>
+          <t>네일지니</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>fusion02@naver.com</t>
+          <t>1231yc@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>02-733-7942</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
+          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xeTiCG</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5910,22 +5846,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>1772</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="R59" t="n">
-        <v>9</v>
+        <v>1865</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5934,12 +5870,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>614593678</t>
+          <t>1073291540</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/614593678</t>
+          <t>https://m.place.naver.com/place/1073291540</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5956,29 +5892,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일문</t>
+          <t>네일브러쉬</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>llkn@naver.com</t>
+          <t>ss7370306@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>02-730-0010</t>
+          <t>0507-1332-0306</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
+          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgate._.mr</t>
+          <t>https://blog.naver.com/ss7370306</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5993,7 +5929,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6009,17 +5945,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>592</v>
+        <v>65</v>
       </c>
       <c r="Q60" t="n">
-        <v>181</v>
+        <v>14</v>
       </c>
       <c r="R60" t="n">
-        <v>773</v>
+        <v>79</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6028,12 +5964,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13534535</t>
+          <t>35559430</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13534535</t>
+          <t>https://m.place.naver.com/place/35559430</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6050,29 +5986,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>강앤니네일스</t>
+          <t>네일 을지로지하쇼핑센터3구역점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1468-2316</t>
+          <t>02-2278-2990</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 227-2 4층</t>
+          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://instagram.com/kangannynails</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6082,7 +6018,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6103,17 +6039,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6122,12 +6058,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1711237836</t>
+          <t>37588249</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1711237836</t>
+          <t>https://m.place.naver.com/place/37588249</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6144,24 +6080,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일블라썸</t>
+          <t>네일하트</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>nailheart053@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1347-8173</t>
+          <t>0507-1484-8604</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 95호</t>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6201,13 +6137,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>333</v>
+        <v>373</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R62" t="n">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6216,12 +6152,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1794862527</t>
+          <t>1101101042</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794862527</t>
+          <t>https://m.place.naver.com/place/1101101042</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6238,25 +6174,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>리라뷰티</t>
+          <t>맥스네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>rira_225@naver.com</t>
+          <t>machojj@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>02-2272-4141</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+          <t>서울특별시 중구 퇴계로 204 3층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lira_4994/</t>
+          <t>https://blog.naver.com/machojj</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6271,7 +6211,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6291,13 +6231,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="Q63" t="n">
-        <v>276</v>
+        <v>532</v>
       </c>
       <c r="R63" t="n">
-        <v>396</v>
+        <v>730</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6306,12 +6246,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1100664846</t>
+          <t>32786203</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100664846</t>
+          <t>https://m.place.naver.com/place/32786203</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6328,29 +6268,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일쏘이</t>
+          <t>리라뷰티</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>rira_225@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1334-9677</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailssoi_</t>
+          <t>https://www.instagram.com/lira_4994/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6385,13 +6321,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="R64" t="n">
-        <v>55</v>
+        <v>396</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6400,12 +6336,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1009120766</t>
+          <t>1100664846</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009120766</t>
+          <t>https://m.place.naver.com/place/1100664846</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6422,29 +6358,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일 오우브</t>
+          <t>드팜므</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>keroo90@naver.com</t>
+          <t>mellowryu@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1407-0437</t>
+          <t>0507-1317-3395</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
+          <t>서울특별시 종로구 사직로8길 42 B110호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.ouv</t>
+          <t>http://www.instagram.com/defemmeeee</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6479,13 +6415,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="R65" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6494,12 +6430,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1559030900</t>
+          <t>1741921081</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559030900</t>
+          <t>https://m.place.naver.com/place/1741921081</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6516,29 +6452,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일로드</t>
+          <t>살롱드소피</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>lordnail@naver.com</t>
+          <t>skincare25@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>02-734-1730</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/salon_de_sophie_</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6548,7 +6480,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6569,17 +6501,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6588,12 +6520,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>206289152</t>
+          <t>13434920</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/206289152</t>
+          <t>https://m.place.naver.com/place/13434920</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6610,29 +6542,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>루이비네일</t>
+          <t>바비 네일왁싱</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>zhengyinji888@naver.com</t>
+          <t>uchka247@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1445-2047</t>
+          <t>0507-1490-9887</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
+          <t>서울특별시 중구 을지로44길 6-9 4층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://instagram.com/luyibi_nail8</t>
+          <t>https://www.instagram.com/barbie.waxnail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6667,13 +6599,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>481</v>
+        <v>161</v>
       </c>
       <c r="Q67" t="n">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>570</v>
+        <v>164</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6682,12 +6614,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>21306056</t>
+          <t>1019484164</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21306056</t>
+          <t>https://m.place.naver.com/place/1019484164</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6704,29 +6636,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일 을지로지하쇼핑센터3구역점</t>
+          <t>nail by Jade</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>02-2278-2990</t>
+          <t>0507-1360-1011</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
+          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_by_jade</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6736,7 +6668,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6757,17 +6689,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6776,12 +6708,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>37588249</t>
+          <t>944614599</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588249</t>
+          <t>https://m.place.naver.com/place/944614599</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6798,29 +6730,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>네일 오우브</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>keroo90@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>02-765-5525</t>
+          <t>0507-1407-0437</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 53-1 1층</t>
+          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.ouv</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6830,7 +6762,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6851,17 +6783,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="Q69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6870,12 +6802,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>34352879</t>
+          <t>1559030900</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34352879</t>
+          <t>https://m.place.naver.com/place/1559030900</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6892,29 +6824,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>다리아네일 안국역</t>
+          <t>지호네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>puppyholic@naver.com</t>
+          <t>yongsanly@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1347-1494</t>
+          <t>0507-1314-5759</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
+          <t>서울특별시 중구 다산로 265 5층,6층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daria_nail_ssu</t>
+          <t>https://www.instagram.com/jihonail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6949,13 +6881,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6964,12 +6896,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1165184706</t>
+          <t>1285361463</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165184706</t>
+          <t>https://m.place.naver.com/place/1285361463</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6986,39 +6918,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>아따걸네일</t>
+          <t>네일블라썸</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>addagirl2@naver.com</t>
+          <t>wilklove@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1328-8505</t>
+          <t>0507-1347-8173</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
+          <t>서울특별시 중구 소공로 102 95호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_GWaij</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7034,22 +6966,22 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="Q71" t="n">
-        <v>649</v>
+        <v>10</v>
       </c>
       <c r="R71" t="n">
-        <v>934</v>
+        <v>343</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7058,12 +6990,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>13047890</t>
+          <t>1794862527</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13047890</t>
+          <t>https://m.place.naver.com/place/1794862527</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7080,29 +7012,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>제이뷰티 눈썹&amp;네일</t>
+          <t>네일바이안</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jbeauty4022@naver.com</t>
+          <t>ye1yang@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1422-4022</t>
+          <t>02-511-5621</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
+          <t>서울특별시 중구 남대문로9길 12 8층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jbeauty4022</t>
+          <t>https://www.instagram.com/nailbyahn</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7117,7 +7049,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7137,13 +7069,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3316</v>
+        <v>56</v>
       </c>
       <c r="Q72" t="n">
-        <v>226</v>
+        <v>46</v>
       </c>
       <c r="R72" t="n">
-        <v>3542</v>
+        <v>102</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7152,12 +7084,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1776791877</t>
+          <t>1084164588</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776791877</t>
+          <t>https://m.place.naver.com/place/1084164588</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7174,29 +7106,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일,현</t>
+          <t>꾸미다</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>qkrwlsk126@naver.com</t>
+          <t>yem1104@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0507-1316-0133</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
+          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hyun.__</t>
+          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7231,13 +7159,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>197</v>
+        <v>4</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7246,12 +7174,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1120708839</t>
+          <t>1095499576</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120708839</t>
+          <t>https://m.place.naver.com/place/1095499576</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7268,25 +7196,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>어나더네일</t>
+          <t>꽁냥네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>soojinpo@naver.com</t>
+          <t>qorgh1236@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1418-2440</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 56-1 1층</t>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/another_n_ail</t>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7321,13 +7253,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>58</v>
+        <v>276</v>
       </c>
       <c r="Q74" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="R74" t="n">
-        <v>69</v>
+        <v>318</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7336,12 +7268,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1214193406</t>
+          <t>1570914826</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214193406</t>
+          <t>https://m.place.naver.com/place/1570914826</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7358,29 +7290,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>에이탑네일</t>
+          <t>네일,현</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kyoung057@naver.com</t>
+          <t>qkrwlsk126@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1372-2148</t>
+          <t>0507-1316-0133</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 12-1 3층</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.top_nail</t>
+          <t>https://www.instagram.com/nail_hyun.__</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7415,13 +7347,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>259</v>
+        <v>174</v>
       </c>
       <c r="Q75" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="R75" t="n">
-        <v>325</v>
+        <v>197</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7430,12 +7362,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1446197361</t>
+          <t>1120708839</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446197361</t>
+          <t>https://m.place.naver.com/place/1120708839</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7452,29 +7384,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일멜로우</t>
+          <t>루다네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sc09mc@naver.com</t>
+          <t>rudanail1515@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1356-7672</t>
+          <t>0507-1357-1516</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mellow_11/</t>
+          <t>http://instagram.com/rudanail_daehakro</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7500,7 +7432,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7509,13 +7441,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>389</v>
+        <v>254</v>
       </c>
       <c r="Q76" t="n">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="R76" t="n">
-        <v>423</v>
+        <v>366</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7524,12 +7456,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1933958367</t>
+          <t>34551572</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933958367</t>
+          <t>https://m.place.naver.com/place/34551572</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7546,29 +7478,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>찰스네일</t>
+          <t>네일하루</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>spotv_sports@naver.com</t>
+          <t>nail_haru@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1307-4179</t>
+          <t>0507-1361-1445</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로12길 9 3층</t>
+          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/charles__nail</t>
+          <t>https://blog.naver.com/nail_haru</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7583,7 +7515,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7599,17 +7531,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>529</v>
+        <v>67</v>
       </c>
       <c r="Q77" t="n">
-        <v>56</v>
+        <v>346</v>
       </c>
       <c r="R77" t="n">
-        <v>585</v>
+        <v>413</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7618,12 +7550,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>13034248</t>
+          <t>37089409</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13034248</t>
+          <t>https://m.place.naver.com/place/37089409</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7640,29 +7572,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>굿모닝네일</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>clsrn9606@naver.com</t>
+          <t>yeju0414@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1400-8607</t>
+          <t>02-765-5525</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+          <t>서울특별시 종로구 지봉로 53-1 1층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gmnail_eyelash</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7672,7 +7604,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7688,22 +7620,22 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>241</v>
+        <v>7</v>
       </c>
       <c r="Q78" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>247</v>
+        <v>10</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7712,12 +7644,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>13051690</t>
+          <t>34352879</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13051690</t>
+          <t>https://m.place.naver.com/place/34352879</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7734,29 +7666,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>네일해썸</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>llllcmalll@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1342-3168</t>
+          <t>0507-1358-8653</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hatssome</t>
+          <t>https://www.instagram.com/nail_lee____</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7782,7 +7714,7 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7791,13 +7723,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="Q79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R79" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7806,12 +7738,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1991633917</t>
+          <t>2065943871</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991633917</t>
+          <t>https://m.place.naver.com/place/2065943871</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7828,29 +7760,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GK네일 현대시티아울렛 동대문점</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>liziah@naver.com</t>
-        </is>
-      </c>
+          <t>마이파우치</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1339-5357</t>
+          <t>0507-1402-0809</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
+          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/mypouch.kangbbin</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7885,13 +7813,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>332</v>
+        <v>11</v>
       </c>
       <c r="Q80" t="n">
-        <v>46</v>
+        <v>183</v>
       </c>
       <c r="R80" t="n">
-        <v>378</v>
+        <v>194</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7900,12 +7828,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1245812382</t>
+          <t>38642341</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245812382</t>
+          <t>https://m.place.naver.com/place/38642341</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7922,20 +7850,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>네일해요</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>elliestar@naver.com</t>
-        </is>
-      </c>
+          <t>종로네일샵</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로44길 9 2층</t>
+          <t>서울특별시 종로구 종로 62</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7975,13 +7899,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7990,12 +7914,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1213168091</t>
+          <t>1928832758</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213168091</t>
+          <t>https://m.place.naver.com/place/1928832758</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8012,25 +7936,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>네일&amp;페일아트</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>lsbangel@naver.com</t>
-        </is>
-      </c>
+          <t>손톱그림</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 446</t>
+          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_sketch_8478/</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8040,7 +7960,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8061,17 +7981,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8080,12 +8000,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>20871402</t>
+          <t>1124095560</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20871402</t>
+          <t>https://m.place.naver.com/place/1124095560</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8102,29 +8022,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>오드리네일</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>ardusy@naver.com</t>
-        </is>
-      </c>
+          <t>베리네일</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>02-722-1384</t>
+          <t>0507-1419-6623</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
+          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreynail_official</t>
+          <t>https://www.instagram.com/berry_nail_</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8150,7 +8066,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8159,13 +8075,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="Q83" t="n">
-        <v>256</v>
+        <v>7</v>
       </c>
       <c r="R83" t="n">
-        <v>484</v>
+        <v>84</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8174,12 +8090,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>13450587</t>
+          <t>1394925944</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13450587</t>
+          <t>https://m.place.naver.com/place/1394925944</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8196,29 +8112,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>나비네일</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>jytgh@naver.com</t>
-        </is>
-      </c>
+          <t>네일문</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>02-319-7844</t>
+          <t>02-730-0010</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://instagram.com/navinailnavinail</t>
+          <t>https://www.instagram.com/nailgate._.mr</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8253,13 +8165,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>26</v>
+        <v>593</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>181</v>
       </c>
       <c r="R84" t="n">
-        <v>28</v>
+        <v>774</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8268,12 +8180,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>735546684</t>
+          <t>13534535</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/735546684</t>
+          <t>https://m.place.naver.com/place/13534535</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8290,29 +8202,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>삼층네일</t>
+          <t>안젤라네일샵</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>wang8241@naver.com</t>
+          <t>angella3977@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1327-8241</t>
+          <t>0507-1493-3335</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wang8241</t>
+          <t>https://blog.naver.com/angella3977</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8343,17 +8255,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>531</v>
+        <v>664</v>
       </c>
       <c r="Q85" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R85" t="n">
-        <v>544</v>
+        <v>676</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8362,12 +8274,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1894370134</t>
+          <t>1274163754</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1894370134</t>
+          <t>https://m.place.naver.com/place/1274163754</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8384,24 +8296,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>드로잉쇼</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>odshow@naver.com</t>
-        </is>
-      </c>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>02-777-1090</t>
+          <t>02-318-6668</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 60</t>
+          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8441,13 +8349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="Q86" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R86" t="n">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8456,12 +8364,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1726036993</t>
+          <t>1874418389</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726036993</t>
+          <t>https://m.place.naver.com/place/1874418389</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8478,39 +8386,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>네일하트</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>nailheart053@naver.com</t>
-        </is>
-      </c>
+          <t>아머네일</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1484-8604</t>
+          <t>0507-1364-4429</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_pzkMG</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8526,22 +8430,22 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>373</v>
+        <v>262</v>
       </c>
       <c r="Q87" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="R87" t="n">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8550,12 +8454,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1101101042</t>
+          <t>1312237193</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101101042</t>
+          <t>https://m.place.naver.com/place/1312237193</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8572,29 +8476,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>르모네일스튜디오</t>
+          <t>디디 네일바</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>borareview@naver.com</t>
+          <t>heeja090@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1374-9858</t>
+          <t>0507-1476-0228</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동숭4가길 2 2층</t>
+          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>http://instagram.com/_lmonail</t>
+          <t>https://www.instagram.com/didi___nailbar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8629,13 +8533,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="Q88" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="R88" t="n">
-        <v>24</v>
+        <v>213</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8644,12 +8548,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1493224095</t>
+          <t>1134899134</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493224095</t>
+          <t>https://m.place.naver.com/place/1134899134</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8666,29 +8570,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>뉴문네일</t>
+          <t>영심이손톱</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>xdaredare@naver.com</t>
+          <t>lovellies@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1354-6577</t>
+          <t>02-735-0031</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 7 2층</t>
+          <t>서울특별시 종로구 종로 88 701호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>http://instagram.com/newmoonnail_</t>
+          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8723,13 +8627,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8738,12 +8642,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1689136529</t>
+          <t>1116851430</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689136529</t>
+          <t>https://m.place.naver.com/place/1116851430</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8760,29 +8664,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>라라네일</t>
+          <t>GK네일 현대시티아울렛 동대문점</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>redpepper30@naver.com</t>
+          <t>liziah@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1344-7250</t>
+          <t>0507-1339-5357</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lalanail_myeongdong</t>
+          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8817,13 +8721,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1001</v>
+        <v>332</v>
       </c>
       <c r="Q90" t="n">
-        <v>431</v>
+        <v>46</v>
       </c>
       <c r="R90" t="n">
-        <v>1432</v>
+        <v>378</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8832,12 +8736,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1303128966</t>
+          <t>1245812382</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303128966</t>
+          <t>https://m.place.naver.com/place/1245812382</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8854,29 +8758,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>꽁냥네일</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>qorgh1236@naver.com</t>
-        </is>
-      </c>
+          <t>무아네일</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1418-2440</t>
+          <t>0507-1436-1716</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 249-28 3층</t>
+          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ggongnyang_nail</t>
+          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8911,13 +8811,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>276</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>318</v>
+        <v>1</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8926,12 +8826,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1570914826</t>
+          <t>2038424794</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570914826</t>
+          <t>https://m.place.naver.com/place/2038424794</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8948,29 +8848,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>프로뷰티</t>
+          <t>뉴문네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>probeauty_blog@naver.com</t>
+          <t>xdaredare@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1435-2789</t>
+          <t>0507-1354-6577</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8가길 9 3층</t>
+          <t>서울특별시 종로구 성균관로 7 2층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/probeauty_blog</t>
+          <t>http://instagram.com/newmoonnail_</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8985,7 +8885,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9005,13 +8905,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>570</v>
+        <v>149</v>
       </c>
       <c r="Q92" t="n">
-        <v>679</v>
+        <v>4</v>
       </c>
       <c r="R92" t="n">
-        <v>1249</v>
+        <v>153</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9020,12 +8920,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>19997455</t>
+          <t>1689136529</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19997455</t>
+          <t>https://m.place.naver.com/place/1689136529</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9042,25 +8942,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>네일지니</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1231yc@naver.com</t>
-        </is>
-      </c>
+          <t>미스에이 네일</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>070-8277-3597</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
+          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xeTiCG</t>
+          <t>https://pf.kakao.com/_jhDaG</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9095,13 +8995,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1772</v>
+        <v>54</v>
       </c>
       <c r="Q93" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="R93" t="n">
-        <v>1865</v>
+        <v>64</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9110,12 +9010,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1073291540</t>
+          <t>1758327919</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073291540</t>
+          <t>https://m.place.naver.com/place/1758327919</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9132,29 +9032,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>그리다네일</t>
+          <t>네일온 명동본점</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>gridanail2@naver.com</t>
+          <t>nailon_myeongdong@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>02-745-8375</t>
+          <t>0507-1302-8995</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로12길 77</t>
+          <t>서울특별시 중구 을지로 88 을특8호</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailon_myeongdong</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9164,12 +9064,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9185,17 +9085,17 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="Q94" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R94" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9204,12 +9104,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>142708597</t>
+          <t>2054691209</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142708597</t>
+          <t>https://m.place.naver.com/place/2054691209</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9226,29 +9126,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nail by Jade</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>hankyuldata@naver.com</t>
-        </is>
-      </c>
+          <t>굿모닝네일</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1360-1011</t>
+          <t>0507-1400-8607</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_by_jade</t>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9274,7 +9170,7 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9283,13 +9179,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>27</v>
+        <v>241</v>
       </c>
       <c r="Q95" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R95" t="n">
-        <v>28</v>
+        <v>247</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9298,12 +9194,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>944614599</t>
+          <t>13051690</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/944614599</t>
+          <t>https://m.place.naver.com/place/13051690</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9320,29 +9216,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>에이커뷰티네일</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>happymin_life@naver.com</t>
-        </is>
-      </c>
+          <t>오브 코코네일</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>02-722-5558</t>
+          <t>0507-1371-8921</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
+          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>http://instagram.com/acre_beauty</t>
+          <t>https://www.instagram.com/ofconail</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9377,13 +9269,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>117</v>
+        <v>658</v>
       </c>
       <c r="Q96" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="R96" t="n">
-        <v>121</v>
+        <v>705</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9392,12 +9284,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1812848399</t>
+          <t>1009626425</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1812848399</t>
+          <t>https://m.place.naver.com/place/1009626425</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9414,29 +9306,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>리빈네일</t>
+          <t>에이커뷰티네일</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jcj0217@naver.com</t>
+          <t>happymin_life@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1349-9808</t>
+          <t>02-722-5558</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
+          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rivin_nail</t>
+          <t>http://instagram.com/acre_beauty</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9471,13 +9363,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Q97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9486,12 +9378,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1315671750</t>
+          <t>1812848399</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315671750</t>
+          <t>https://m.place.naver.com/place/1812848399</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9508,29 +9400,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>네일원</t>
+          <t>혜리앤케어</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>nail_one@naver.com</t>
+          <t>micahyesung@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1338-0475</t>
+          <t>02-725-1741</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 52-1 2층</t>
+          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_one</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9540,7 +9432,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9561,17 +9453,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P98" t="n">
         <v>3</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9580,12 +9472,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1105911364</t>
+          <t>155402276</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105911364</t>
+          <t>https://m.place.naver.com/place/155402276</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9602,29 +9494,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>안젤라네일샵</t>
+          <t>그리드네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>angella3977@naver.com</t>
+          <t>boye_like@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1493-3335</t>
+          <t>0507-1405-0461</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
+          <t>서울특별시 종로구 옥인길 44</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/angella3977</t>
+          <t>http://instagram.com/love_grid</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9639,7 +9531,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9659,13 +9551,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>664</v>
+        <v>53</v>
       </c>
       <c r="Q99" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R99" t="n">
-        <v>676</v>
+        <v>55</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9674,12 +9566,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1274163754</t>
+          <t>38531607</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274163754</t>
+          <t>https://m.place.naver.com/place/38531607</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9696,25 +9588,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>꾸미다</t>
+          <t>너 참 예쁘다</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>yem1104@naver.com</t>
+          <t>yuiu1401@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1434-8892</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
+          <t>http://www.instagram.com/youarebeautiful_seoul</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9734,10 +9630,14 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
           <t>X</t>
@@ -9749,13 +9649,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1</v>
+        <v>529</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>840</v>
       </c>
       <c r="R100" t="n">
-        <v>4</v>
+        <v>1369</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9764,12 +9664,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1095499576</t>
+          <t>1466732665</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095499576</t>
+          <t>https://m.place.naver.com/place/1466732665</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9786,29 +9686,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Diamond Nails</t>
+          <t>크리스탈손톱</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ksj673232@naver.com</t>
+          <t>juyean123@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1420-1393</t>
+          <t>02-3398-4445</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 155 1동 102호</t>
+          <t>서울특별시 중구 장충단로 275</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9818,7 +9718,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9839,17 +9739,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9858,12 +9758,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>2040524360</t>
+          <t>1895018257</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040524360</t>
+          <t>https://m.place.naver.com/place/1895018257</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -9880,29 +9780,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>네일브러쉬</t>
+          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ss7370306@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0507-1332-0306</t>
+          <t>02-756-4143</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
+          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ss7370306</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9912,12 +9812,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9937,13 +9837,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="Q102" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9952,12 +9852,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>35559430</t>
+          <t>31315234</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35559430</t>
+          <t>https://m.place.naver.com/place/31315234</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -9974,29 +9874,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>가빈네일</t>
+          <t>살롱드벨르네일</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>happyhannj@naver.com</t>
+          <t>salondebelle_nail@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0507-1431-8259</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
+          <t>서울특별시 종로구 종로 65 2층 208호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
+          <t>https://blog.naver.com/salondebelle_nail</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10011,7 +9907,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10031,13 +9927,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>58</v>
+        <v>355</v>
       </c>
       <c r="Q103" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="R103" t="n">
-        <v>60</v>
+        <v>416</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10046,12 +9942,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>38500996</t>
+          <t>1768571536</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38500996</t>
+          <t>https://m.place.naver.com/place/1768571536</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -10068,29 +9964,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>영심이손톱</t>
+          <t>폭시네일</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>lovellies@naver.com</t>
+          <t>tomebooy@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>02-735-0031</t>
+          <t>0507-1403-4791</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 88 701호</t>
+          <t>서울특별시 종로구 동망산길 13 2층</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10100,7 +9996,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10121,17 +10017,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P104" t="n">
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10140,12 +10036,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1116851430</t>
+          <t>40986070</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116851430</t>
+          <t>https://m.place.naver.com/place/40986070</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10162,34 +10058,34 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>치즈네일</t>
+          <t>아따걸네일</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>43995@naver.com</t>
+          <t>addagirl2@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>02-6405-4578</t>
+          <t>0507-1328-8505</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheesenail</t>
+          <t>https://pf.kakao.com/_GWaij</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -10210,7 +10106,7 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -10219,13 +10115,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>57</v>
+        <v>285</v>
       </c>
       <c r="Q105" t="n">
-        <v>1</v>
+        <v>649</v>
       </c>
       <c r="R105" t="n">
-        <v>58</v>
+        <v>934</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10234,12 +10130,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>37542182</t>
+          <t>13047890</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37542182</t>
+          <t>https://m.place.naver.com/place/13047890</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10256,25 +10152,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>릴리엔젤네일</t>
+          <t>루아르블랑 네일</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>kiyu0987@naver.com</t>
+          <t>failuredw@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0507-1483-9411</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
+          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>http://instagram.com/lilyangel_nail</t>
+          <t>https://open.kakao.com/o/sHajSJei</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10300,7 +10200,7 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -10309,13 +10209,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="Q106" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="R106" t="n">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10324,12 +10224,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1110775717</t>
+          <t>2013893243</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110775717</t>
+          <t>https://m.place.naver.com/place/2013893243</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10346,34 +10246,34 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>아머네일</t>
+          <t>루이비네일</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>dntndus111@naver.com</t>
+          <t>zhengyinji888@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1364-4429</t>
+          <t>0507-1445-2047</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
+          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_pzkMG</t>
+          <t>http://instagram.com/luyibi_nail8</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10394,7 +10294,7 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -10403,13 +10303,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>262</v>
+        <v>481</v>
       </c>
       <c r="Q107" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="R107" t="n">
-        <v>359</v>
+        <v>570</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10418,12 +10318,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1312237193</t>
+          <t>21306056</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312237193</t>
+          <t>https://m.place.naver.com/place/21306056</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10440,25 +10340,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>살롱드소피</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>skincare25@naver.com</t>
-        </is>
-      </c>
+          <t>어나더네일</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
+          <t>서울특별시 종로구 지봉로 56-1 1층</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salon_de_sophie_</t>
+          <t>https://www.instagram.com/another_n_ail</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10493,13 +10389,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="Q108" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="R108" t="n">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10508,12 +10404,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>13434920</t>
+          <t>1214193406</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13434920</t>
+          <t>https://m.place.naver.com/place/1214193406</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10530,12 +10426,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>종로네일샵</t>
+          <t>해피네일데이</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>bitna0614@naver.com</t>
+          <t>happynailday@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -10543,12 +10439,12 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 62</t>
+          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/happynailday</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10558,12 +10454,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10579,17 +10475,17 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10598,12 +10494,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1928832758</t>
+          <t>298136226</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928832758</t>
+          <t>https://m.place.naver.com/place/298136226</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10620,34 +10516,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>루다네일</t>
+          <t>아트만네일</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>rudanail1515@naver.com</t>
+          <t>ppangsun238@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0507-1357-1516</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>http://instagram.com/rudanail_daehakro</t>
+          <t>http://pf.kakao.com/_Txkxgfxj</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -10677,13 +10569,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="Q110" t="n">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="R110" t="n">
-        <v>366</v>
+        <v>36</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10692,12 +10584,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>34551572</t>
+          <t>1284929161</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34551572</t>
+          <t>https://m.place.naver.com/place/1284929161</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10714,29 +10606,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>엘로아네일</t>
+          <t>위치네일스 종로점</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>hhhong88@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1314-9339</t>
+          <t>0507-1364-9020</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+          <t>서울특별시 종로구 종로 51</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eloa__nail/</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10751,7 +10643,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -10771,13 +10663,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>11</v>
+        <v>1060</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="R111" t="n">
-        <v>11</v>
+        <v>1209</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10786,12 +10678,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>2087274322</t>
+          <t>1543496206</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087274322</t>
+          <t>https://m.place.naver.com/place/1543496206</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10808,29 +10700,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>빌러브드 네일</t>
+          <t>네일원</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>novembro_12@naver.com</t>
+          <t>nail_one@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>02-733-8318</t>
+          <t>0507-1338-0475</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
+          <t>서울특별시 종로구 지봉로 52-1 2층</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beloved_nail_</t>
+          <t>http://instagram.com/_nail_one</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10865,13 +10757,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>371</v>
+        <v>3</v>
       </c>
       <c r="Q112" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10880,12 +10772,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>877681682</t>
+          <t>1105911364</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/877681682</t>
+          <t>https://m.place.naver.com/place/1105911364</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10902,29 +10794,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>네일온 명동본점</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>nailon_myeongdong@naver.com</t>
-        </is>
-      </c>
+          <t>안0네일</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0507-1302-8995</t>
+          <t>02-6052-7778</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 을특8호</t>
+          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon_myeongdong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10934,12 +10822,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10955,17 +10843,17 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Q113" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10974,12 +10862,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>2054691209</t>
+          <t>1487336161</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054691209</t>
+          <t>https://m.place.naver.com/place/1487336161</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -10996,29 +10884,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>크리스탈손톱</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>juyean123@naver.com</t>
-        </is>
-      </c>
+          <t>나비네일</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>02-3398-4445</t>
+          <t>02-319-7844</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 275</t>
+          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/navinailnavinail</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11028,7 +10912,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11049,17 +10933,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11068,12 +10952,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1895018257</t>
+          <t>735546684</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895018257</t>
+          <t>https://m.place.naver.com/place/735546684</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -11090,29 +10974,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>효녀네일</t>
+          <t>리빈네일</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>hy0d0ng2@naver.com</t>
+          <t>jcj0217@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1366-2991</t>
+          <t>0507-1349-9808</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyonyeo_nail</t>
+          <t>https://www.instagram.com/rivin_nail</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11147,13 +11031,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11162,12 +11046,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>2038116522</t>
+          <t>1315671750</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038116522</t>
+          <t>https://m.place.naver.com/place/1315671750</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">

--- a/naver-place-crawler/results_nail/종로_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/종로_네일샵.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>오드리네일</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>네일문</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>llkn@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02-722-1384</t>
+          <t>02-730-0010</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreynail_official</t>
+          <t>https://www.instagram.com/nailgate._.mr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -608,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>228</v>
+        <v>593</v>
       </c>
       <c r="Q2" t="n">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="R2" t="n">
-        <v>484</v>
+        <v>774</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13450587</t>
+          <t>13534535</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13450587</t>
+          <t>https://m.place.naver.com/place/13534535</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -654,12 +658,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아셀네일</t>
+          <t>네일지니</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>asher9809@naver.com</t>
+          <t>1231yc@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -667,22 +671,22 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 253 10층 11호</t>
+          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xeTiCG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -698,22 +702,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>59</v>
+        <v>1773</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="R3" t="n">
-        <v>82</v>
+        <v>1866</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1229434440</t>
+          <t>1073291540</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229434440</t>
+          <t>https://m.place.naver.com/place/1073291540</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -744,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>빌러브드 네일</t>
+          <t>위치네일스 종로점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>novembro_12@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-733-8318</t>
+          <t>0507-1364-9020</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
+          <t>서울특별시 종로구 종로 51</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beloved_nail_</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -781,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -801,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>371</v>
+        <v>1060</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="R4" t="n">
-        <v>400</v>
+        <v>1209</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>877681682</t>
+          <t>1543496206</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/877681682</t>
+          <t>https://m.place.naver.com/place/1543496206</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -838,25 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>뷰티숲</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>네일 김미쉘터</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>patent37435@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1438-7477</t>
+          <t>0507-1320-1993</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 37-29 103호</t>
+          <t>서울특별시 종로구 필운대로 55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailsoop_sj/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -866,7 +874,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -887,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>58</v>
+        <v>266</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>58</v>
+        <v>270</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -906,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1158436638</t>
+          <t>1802694964</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158436638</t>
+          <t>https://m.place.naver.com/place/1802694964</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -928,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>꾸밈네일아트</t>
+          <t>네일쏘이</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fusion02@naver.com</t>
+          <t>annoi_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-733-7942</t>
+          <t>0507-1334-9677</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
+          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailssoi_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -960,7 +968,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -981,17 +989,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>614593678</t>
+          <t>1009120766</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/614593678</t>
+          <t>https://m.place.naver.com/place/1009120766</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1022,29 +1030,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>효녀네일</t>
+          <t>릴리엔젤네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hy0d0ng2@naver.com</t>
+          <t>kiyu0987@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1366-2991</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
+          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyonyeo_nail</t>
+          <t>http://instagram.com/lilyangel_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>235</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>287</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,12 +1098,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2038116522</t>
+          <t>1110775717</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038116522</t>
+          <t>https://m.place.naver.com/place/1110775717</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1116,25 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>지아네일</t>
+          <t>라라네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jjaa1334@naver.com</t>
+          <t>redpepper30@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1344-7250</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 40 6층</t>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeonjia9</t>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>65</v>
+        <v>1001</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>431</v>
       </c>
       <c r="R8" t="n">
-        <v>75</v>
+        <v>1432</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1279897442</t>
+          <t>1303128966</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279897442</t>
+          <t>https://m.place.naver.com/place/1303128966</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1206,21 +1214,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>오프엠네일</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>리라뷰티</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>rira_225@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 40 4층</t>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lira_4994/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1230,7 +1242,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1251,17 +1263,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>276</v>
       </c>
       <c r="R9" t="n">
-        <v>101</v>
+        <v>397</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1270,12 +1282,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2099192808</t>
+          <t>1100664846</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099192808</t>
+          <t>https://m.place.naver.com/place/1100664846</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1292,29 +1304,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일아토</t>
+          <t>키튼네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sk3374@naver.com</t>
+          <t>dbgpwn0626@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1416-6630</t>
+          <t>02-765-8566</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
+          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ato</t>
+          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,13 +1361,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>192</v>
+        <v>488</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>215</v>
+        <v>542</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1364,12 +1376,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1446399532</t>
+          <t>1065031131</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446399532</t>
+          <t>https://m.place.naver.com/place/1065031131</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1386,30 +1398,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>찰스네일</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>아따걸네일</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>addagirl2@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1307-4179</t>
+          <t>0507-1328-8505</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로12길 9 3층</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/charles__nail</t>
+          <t>https://pf.kakao.com/_GWaij</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1430,7 +1446,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1439,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>529</v>
+        <v>285</v>
       </c>
       <c r="Q11" t="n">
-        <v>56</v>
+        <v>649</v>
       </c>
       <c r="R11" t="n">
-        <v>585</v>
+        <v>934</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1454,12 +1470,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13034248</t>
+          <t>13047890</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13034248</t>
+          <t>https://m.place.naver.com/place/13047890</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1476,12 +1492,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>릴리엔젤네일</t>
+          <t>페이브 네일 스튜디오</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kiyu0987@naver.com</t>
+          <t>ekdmaekfdpqnwk@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1489,12 +1505,12 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://instagram.com/lilyangel_nail</t>
+          <t>https://open.kakao.com/o/sUKlei7f</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1520,7 +1536,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1529,13 +1545,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>235</v>
+        <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="R12" t="n">
-        <v>287</v>
+        <v>96</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1544,12 +1560,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1110775717</t>
+          <t>1109114407</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110775717</t>
+          <t>https://m.place.naver.com/place/1109114407</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1566,29 +1582,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일멜로우</t>
+          <t>삼층네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sc09mc@naver.com</t>
+          <t>wang8241@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1356-7672</t>
+          <t>0507-1327-8241</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mellow_11/</t>
+          <t>https://blog.naver.com/wang8241</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1603,7 +1619,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1619,17 +1635,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>389</v>
+        <v>531</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>423</v>
+        <v>544</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1638,12 +1654,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1933958367</t>
+          <t>1894370134</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933958367</t>
+          <t>https://m.place.naver.com/place/1894370134</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1660,25 +1676,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>바움네일</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>네일로드</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>yu___ji@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1330-3151</t>
+          <t>02-734-1730</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로9길 37 2층</t>
+          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/baum_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1688,7 +1708,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1709,17 +1729,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>606</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1728,12 +1748,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1954514000</t>
+          <t>206289152</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954514000</t>
+          <t>https://m.place.naver.com/place/206289152</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1750,29 +1770,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>말짜네일 광화문점</t>
+          <t>수야디나 네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>malzzanail@naver.com</t>
+          <t>vastron@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1402-3734</t>
+          <t>0507-1305-2499</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
+          <t>서울특별시 중구 충무로 36 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/malzzanail</t>
+          <t>https://www.instagram.com/yun_ju423/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1787,7 +1807,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1798,7 +1818,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1807,13 +1827,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>305</v>
+        <v>184</v>
       </c>
       <c r="Q15" t="n">
-        <v>424</v>
+        <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>729</v>
+        <v>216</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1822,12 +1842,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>37997776</t>
+          <t>1324800762</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37997776</t>
+          <t>https://m.place.naver.com/place/1324800762</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1844,24 +1864,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일로드</t>
+          <t>안0네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lordnail@naver.com</t>
+          <t>ysl6161015@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02-734-1730</t>
+          <t>02-6052-7778</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
+          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1901,13 +1921,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1916,12 +1936,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>206289152</t>
+          <t>1487336161</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/206289152</t>
+          <t>https://m.place.naver.com/place/1487336161</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1938,25 +1958,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일라이트</t>
+          <t>다리아네일 안국역</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>elegant1025@naver.com</t>
+          <t>puppyholic@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1347-1494</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 5 3층</t>
+          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_light_</t>
+          <t>https://www.instagram.com/daria_nail_ssu</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1991,13 +2015,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>540</v>
+        <v>184</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>546</v>
+        <v>186</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2006,12 +2030,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1105652769</t>
+          <t>1165184706</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105652769</t>
+          <t>https://m.place.naver.com/place/1165184706</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2028,29 +2052,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>꽃소니 네일아트</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>qhpw4cpk@naver.com</t>
+          <t>jytgh@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>070-8615-3478</t>
+          <t>02-319-7844</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로5길 8 2층</t>
+          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flower_handnails</t>
+          <t>http://instagram.com/navinailnavinail</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2085,13 +2109,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2100,12 +2124,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1593950281</t>
+          <t>735546684</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593950281</t>
+          <t>https://m.place.naver.com/place/735546684</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2122,30 +2146,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>이츠네일</t>
+          <t>네일,현</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>icacc89@naver.com</t>
+          <t>qkrwlsk126@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1316-0133</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_duxhxdn</t>
+          <t>https://www.instagram.com/nail_hyun.__</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2166,7 +2194,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2175,13 +2203,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="R19" t="n">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2190,12 +2218,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>31949587</t>
+          <t>1120708839</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31949587</t>
+          <t>https://m.place.naver.com/place/1120708839</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2212,29 +2240,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>가빈네일</t>
+          <t>네일 오우브</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>happyhannj@naver.com</t>
+          <t>keroo90@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1431-8259</t>
+          <t>0507-1407-0437</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
+          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
+          <t>https://www.instagram.com/nail.ouv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2269,13 +2297,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2284,12 +2312,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>38500996</t>
+          <t>1559030900</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38500996</t>
+          <t>https://m.place.naver.com/place/1559030900</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2306,29 +2334,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>그리다네일</t>
+          <t>오토젯네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>gridanail2@naver.com</t>
+          <t>yr19850217@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>02-745-8375</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로12길 77</t>
+          <t>서울특별시 종로구 돈화문로 68</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.autoznail.com/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2338,7 +2362,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2363,13 +2387,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2378,12 +2402,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>142708597</t>
+          <t>35506860</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142708597</t>
+          <t>https://m.place.naver.com/place/35506860</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2400,12 +2424,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일&amp;페일아트</t>
+          <t>아셀네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lsbangel@naver.com</t>
+          <t>asher9809@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2413,7 +2437,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 446</t>
+          <t>서울특별시 중구 장충단로 253 10층 11호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2453,13 +2477,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2468,12 +2492,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>20871402</t>
+          <t>1229434440</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20871402</t>
+          <t>https://m.place.naver.com/place/1229434440</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2490,25 +2514,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>엔79 Nail</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>마이파우치</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>323redtree@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1390-0326</t>
+          <t>0507-1402-0809</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
+          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mypouch.kangbbin</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2518,7 +2546,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2539,17 +2567,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="R23" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2558,12 +2586,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1756267523</t>
+          <t>38642341</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756267523</t>
+          <t>https://m.place.naver.com/place/38642341</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2580,29 +2608,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>올리브네일&amp;속눈썹</t>
+          <t>에이커뷰티네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>djdjqq1663@naver.com</t>
+          <t>happymin_life@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02-2075-7775</t>
+          <t>02-722-5558</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
+          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/djdjqq1663</t>
+          <t>http://instagram.com/acre_beauty</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2617,7 +2645,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2628,7 +2656,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2637,13 +2665,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3106</v>
+        <v>117</v>
       </c>
       <c r="Q24" t="n">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>3356</v>
+        <v>121</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2652,12 +2680,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>35751284</t>
+          <t>1812848399</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35751284</t>
+          <t>https://m.place.naver.com/place/1812848399</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2674,25 +2702,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>오토젯네일</t>
+          <t>혜리앤케어</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yr19850217@naver.com</t>
+          <t>micahyesung@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>02-725-1741</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로 68</t>
+          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.autoznail.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2702,7 +2734,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2727,13 +2759,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2742,12 +2774,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>35506860</t>
+          <t>155402276</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35506860</t>
+          <t>https://m.place.naver.com/place/155402276</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2764,29 +2796,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>키튼네일</t>
+          <t>꽁냥네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dbgpwn0626@naver.com</t>
+          <t>qorgh1236@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02-765-8566</t>
+          <t>0507-1418-2440</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2821,13 +2853,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>484</v>
+        <v>276</v>
       </c>
       <c r="Q26" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="R26" t="n">
-        <v>538</v>
+        <v>318</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2836,12 +2868,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1065031131</t>
+          <t>1570914826</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065031131</t>
+          <t>https://m.place.naver.com/place/1570914826</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2858,29 +2890,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>핸더뷰티</t>
+          <t>Diamond Nails</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>koenji_nail@naver.com</t>
+          <t>ksj673232@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1380-1146</t>
+          <t>0507-1420-1393</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
+          <t>서울특별시 중구 마른내로 155 1동 102호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/koenji_nail</t>
+          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2895,7 +2927,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2915,13 +2947,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>412</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>769</v>
+        <v>0</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2930,12 +2962,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37558905</t>
+          <t>2040524360</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37558905</t>
+          <t>https://m.place.naver.com/place/2040524360</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2952,29 +2984,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>프로뷰티</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>probeauty_blog@naver.com</t>
+          <t>yeju0414@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1435-2789</t>
+          <t>02-765-5525</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8가길 9 3층</t>
+          <t>서울특별시 종로구 지봉로 53-1 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/probeauty_blog</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2984,12 +3016,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3005,17 +3037,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>570</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
-        <v>679</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1249</v>
+        <v>10</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3024,12 +3056,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>19997455</t>
+          <t>34352879</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19997455</t>
+          <t>https://m.place.naver.com/place/34352879</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3046,12 +3078,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>페이브 네일 스튜디오</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ekdmaekfdpqnwk@naver.com</t>
+          <t>kikiu30@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3059,17 +3091,17 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
+          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sUKlei7f</t>
+          <t>http://pf.kakao.com/_pAtmG</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3099,13 +3131,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>63</v>
+        <v>1852</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="R29" t="n">
-        <v>96</v>
+        <v>1913</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3114,12 +3146,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1109114407</t>
+          <t>1712141242</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109114407</t>
+          <t>https://m.place.naver.com/place/1712141242</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3136,25 +3168,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일해요</t>
+          <t>루아르블랑 네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>elliestar@naver.com</t>
+          <t>failuredw@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1483-9411</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로44길 9 2층</t>
+          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sHajSJei</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3164,7 +3200,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3180,22 +3216,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R30" t="n">
-        <v>6</v>
+        <v>240</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3204,12 +3240,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1213168091</t>
+          <t>2013893243</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213168091</t>
+          <t>https://m.place.naver.com/place/2013893243</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3226,29 +3262,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>삼층네일</t>
+          <t>루다네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>wang8241@naver.com</t>
+          <t>rudanail1515@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1327-8241</t>
+          <t>0507-1357-1516</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wang8241</t>
+          <t>http://instagram.com/rudanail_daehakro</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3263,7 +3299,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3274,22 +3310,22 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>531</v>
+        <v>254</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="R31" t="n">
-        <v>544</v>
+        <v>366</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3298,12 +3334,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1894370134</t>
+          <t>34551572</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1894370134</t>
+          <t>https://m.place.naver.com/place/34551572</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3320,30 +3356,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>르모네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>네일바이안</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ye1yang@naver.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1374-9858</t>
+          <t>02-511-5621</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동숭4가길 2 2층</t>
+          <t>서울특별시 중구 남대문로9길 12 8층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://instagram.com/_lmonail</t>
+          <t>https://www.instagram.com/nailbyahn</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3353,7 +3393,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3373,13 +3413,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="R32" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3388,12 +3428,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1493224095</t>
+          <t>1084164588</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493224095</t>
+          <t>https://m.place.naver.com/place/1084164588</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3410,34 +3450,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>아트만네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>ppangsun238@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1322-4179</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sdED0A2</t>
+          <t>http://pf.kakao.com/_Txkxgfxj</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3467,13 +3503,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>249</v>
+        <v>16</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
-        <v>264</v>
+        <v>36</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3482,12 +3518,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1054499609</t>
+          <t>1284929161</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054499609</t>
+          <t>https://m.place.naver.com/place/1284929161</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3504,29 +3540,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>블링네일 종로점</t>
+          <t>그리다네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>beaulynail@naver.com</t>
+          <t>gridanail2@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1448-0036</t>
+          <t>02-745-8375</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 16-1 1층</t>
+          <t>서울특별시 종로구 대학로12길 77</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beaulynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3536,12 +3572,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3557,17 +3593,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="Q34" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>216</v>
+        <v>23</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3576,12 +3612,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>60890323</t>
+          <t>142708597</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60890323</t>
+          <t>https://m.place.naver.com/place/142708597</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3598,25 +3634,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Diamond Nails</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>바비 네일왁싱</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>uchka247@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1420-1393</t>
+          <t>0507-1490-9887</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 155 1동 102호</t>
+          <t>서울특별시 중구 을지로44길 6-9 4층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
+          <t>https://www.instagram.com/barbie.waxnail</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3651,13 +3691,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3666,12 +3706,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2040524360</t>
+          <t>1019484164</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040524360</t>
+          <t>https://m.place.naver.com/place/1019484164</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3688,21 +3728,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일, 사월</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>에이탑네일</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>kyoung057@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1372-2148</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
+          <t>서울특별시 중구 명동4길 12-1 3층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__april</t>
+          <t>https://www.instagram.com/a.top_nail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3737,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>644</v>
+        <v>259</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="R36" t="n">
-        <v>658</v>
+        <v>326</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3752,12 +3800,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1448977317</t>
+          <t>1446197361</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448977317</t>
+          <t>https://m.place.naver.com/place/1446197361</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3774,29 +3822,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>라라네일</t>
+          <t>뉴문네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>redpepper30@naver.com</t>
+          <t>xdaredare@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1344-7250</t>
+          <t>0507-1354-6577</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+          <t>서울특별시 종로구 성균관로 7 2층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lalanail_myeongdong</t>
+          <t>http://instagram.com/newmoonnail_</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3831,13 +3879,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1001</v>
+        <v>149</v>
       </c>
       <c r="Q37" t="n">
-        <v>431</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>1432</v>
+        <v>153</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3846,12 +3894,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1303128966</t>
+          <t>1689136529</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303128966</t>
+          <t>https://m.place.naver.com/place/1689136529</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3868,34 +3916,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>르노브네일</t>
+          <t>네일원</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hshee069@naver.com</t>
+          <t>nail_one@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1307-5439</t>
+          <t>0507-1338-0475</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 38 1층</t>
+          <t>서울특별시 종로구 지봉로 52-1 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XxbVPn</t>
+          <t>http://instagram.com/_nail_one</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3916,7 +3964,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3925,13 +3973,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>406</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>427</v>
+        <v>4</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3940,12 +3988,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1890443515</t>
+          <t>1105911364</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1890443515</t>
+          <t>https://m.place.naver.com/place/1105911364</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3962,16 +4010,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>비조네일</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>폭시네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>tomebooy@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1403-4791</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 379</t>
+          <t>서울특별시 종로구 동망산길 13 2층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4011,13 +4067,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4026,12 +4082,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>19813956</t>
+          <t>40986070</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19813956</t>
+          <t>https://m.place.naver.com/place/40986070</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4048,35 +4104,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JIN네일</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>이츠네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>icacc89@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1392-5159</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
+          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_duxhxdn</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4092,22 +4148,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4116,12 +4172,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1530291597</t>
+          <t>31949587</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1530291597</t>
+          <t>https://m.place.naver.com/place/31949587</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4138,25 +4194,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에이탑네일</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>뷰티숲</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>smallwarestore@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1372-2148</t>
+          <t>0507-1438-7477</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 12-1 3층</t>
+          <t>서울특별시 종로구 지봉로 37-29 103호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.top_nail</t>
+          <t>https://www.instagram.com/nailsoop_sj/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4191,13 +4251,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>259</v>
+        <v>58</v>
       </c>
       <c r="Q41" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>326</v>
+        <v>58</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4206,12 +4266,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1446197361</t>
+          <t>1158436638</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446197361</t>
+          <t>https://m.place.naver.com/place/1158436638</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4228,29 +4288,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>드네일 광화문점</t>
+          <t>바움네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dahaeyoo@naver.com</t>
+          <t>harulov@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1351-9192</t>
+          <t>0507-1330-3151</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
+          <t>서울특별시 종로구 대학로9길 37 2층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
+          <t>https://www.instagram.com/baum_nail</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4285,13 +4345,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>20</v>
+        <v>560</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="R42" t="n">
-        <v>37</v>
+        <v>607</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4300,12 +4360,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1372444756</t>
+          <t>1954514000</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1372444756</t>
+          <t>https://m.place.naver.com/place/1954514000</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4322,29 +4382,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>수야디나 네일&amp;래쉬</t>
+          <t>네일하루</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>vastron@naver.com</t>
+          <t>nail_haru@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1305-2499</t>
+          <t>0507-1361-1445</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 중구 충무로 36 2층</t>
+          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yun_ju423/</t>
+          <t>https://blog.naver.com/nail_haru</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4359,7 +4419,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4375,17 +4435,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="Q43" t="n">
-        <v>32</v>
+        <v>346</v>
       </c>
       <c r="R43" t="n">
-        <v>216</v>
+        <v>413</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4394,12 +4454,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1324800762</t>
+          <t>37089409</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324800762</t>
+          <t>https://m.place.naver.com/place/37089409</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4416,29 +4476,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일쏘이</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1334-9677</t>
+          <t>0507-1322-4179</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
+          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailssoi_</t>
+          <t>https://open.kakao.com/o/sdED0A2</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4464,7 +4524,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4473,13 +4533,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>55</v>
+        <v>249</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R44" t="n">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4488,12 +4548,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1009120766</t>
+          <t>1054499609</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009120766</t>
+          <t>https://m.place.naver.com/place/1054499609</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4510,26 +4570,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>파라테라피네일</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>아머네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dntndus111@naver.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1364-4429</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
+          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail._.again</t>
+          <t>https://pf.kakao.com/_pzkMG</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4550,7 +4618,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4559,13 +4627,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="R45" t="n">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4574,12 +4642,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1996157285</t>
+          <t>1312237193</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996157285</t>
+          <t>https://m.place.naver.com/place/1312237193</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4596,29 +4664,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>치즈네일</t>
+          <t>르모네일스튜디오</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>43995@naver.com</t>
+          <t>menfourteen@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>02-6405-4578</t>
+          <t>0507-1374-9858</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
+          <t>서울특별시 종로구 동숭4가길 2 2층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheesenail</t>
+          <t>http://instagram.com/_lmonail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4653,13 +4721,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R46" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4668,12 +4736,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>37542182</t>
+          <t>1493224095</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37542182</t>
+          <t>https://m.place.naver.com/place/1493224095</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4690,25 +4758,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>엘로아네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>꾸미다</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>yem1104@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1314-9339</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eloa__nail/</t>
+          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4743,13 +4811,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4758,12 +4826,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2087274322</t>
+          <t>1095499576</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087274322</t>
+          <t>https://m.place.naver.com/place/1095499576</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4780,25 +4848,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9층네일 명동점</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>오드리네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ardusy@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1359-1372</t>
+          <t>02-722-1384</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 25-1 303호</t>
+          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9.nailstudio</t>
+          <t>https://www.instagram.com/audreynail_official</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4824,7 +4896,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4833,13 +4905,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>256</v>
       </c>
       <c r="R48" t="n">
-        <v>281</v>
+        <v>484</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4848,12 +4920,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1681308543</t>
+          <t>13450587</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681308543</t>
+          <t>https://m.place.naver.com/place/13450587</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4870,29 +4942,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일해썸</t>
+          <t>루이비네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>llllcmalll@naver.com</t>
+          <t>zhengyinji888@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1342-3168</t>
+          <t>0507-1445-2047</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
+          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hatssome</t>
+          <t>http://instagram.com/luyibi_nail8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4918,7 +4990,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4927,13 +4999,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>86</v>
+        <v>481</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="R49" t="n">
-        <v>96</v>
+        <v>570</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4942,12 +5014,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1991633917</t>
+          <t>21306056</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991633917</t>
+          <t>https://m.place.naver.com/place/21306056</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4964,29 +5036,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>강앤니네일스</t>
+          <t>파라테라피네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>anrgudtkd@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1468-2316</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 227-2 4층</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://instagram.com/kangannynails</t>
+          <t>http://instagram.com/nail._.again</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5021,13 +5089,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5036,12 +5104,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1711237836</t>
+          <t>1996157285</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1711237836</t>
+          <t>https://m.place.naver.com/place/1996157285</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5058,38 +5126,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>레푸스 종로점</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>refuss_jong_ro@naver.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>chy0802@ahasoft.co.kr</t>
-        </is>
-      </c>
+          <t>jjuahlee@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>02-720-4544</t>
+          <t>02-318-6668</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
+          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/857013</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5115,17 +5179,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>862</v>
+        <v>88</v>
       </c>
       <c r="Q51" t="n">
-        <v>360</v>
+        <v>14</v>
       </c>
       <c r="R51" t="n">
-        <v>1222</v>
+        <v>102</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5134,12 +5198,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1237692187</t>
+          <t>1874418389</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237692187</t>
+          <t>https://m.place.naver.com/place/1874418389</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5156,24 +5220,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>드로잉쇼</t>
+          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>odshow@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02-777-1090</t>
+          <t>02-756-4143</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 60</t>
+          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5213,13 +5277,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5228,12 +5292,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1726036993</t>
+          <t>31315234</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726036993</t>
+          <t>https://m.place.naver.com/place/31315234</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5250,29 +5314,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일누하</t>
+          <t>nail by Jade</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1348-9398</t>
+          <t>0507-1360-1011</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
+          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.nuha</t>
+          <t>http://www.instagram.com/nail_by_jade</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5307,13 +5371,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="Q53" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5322,12 +5386,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1370069746</t>
+          <t>944614599</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370069746</t>
+          <t>https://m.place.naver.com/place/944614599</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5344,30 +5408,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>말짜네일 광화문점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kikiu30@naver.com</t>
+          <t>malzzanail@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1402-3734</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
+          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pAtmG</t>
+          <t>https://blog.naver.com/malzzanail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5377,7 +5445,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5397,13 +5465,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1852</v>
+        <v>305</v>
       </c>
       <c r="Q54" t="n">
-        <v>61</v>
+        <v>424</v>
       </c>
       <c r="R54" t="n">
-        <v>1913</v>
+        <v>729</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5412,12 +5480,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1712141242</t>
+          <t>37997776</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712141242</t>
+          <t>https://m.place.naver.com/place/37997776</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5434,21 +5502,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>모스네일</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>프로뷰티</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>probeauty_blog@naver.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1435-2789</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
+          <t>서울특별시 중구 명동8가길 9 3층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss.nail_</t>
+          <t>https://blog.naver.com/probeauty_blog</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5463,7 +5539,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5474,7 +5550,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5483,13 +5559,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>226</v>
+        <v>570</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>679</v>
       </c>
       <c r="R55" t="n">
-        <v>239</v>
+        <v>1249</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5498,12 +5574,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1061088069</t>
+          <t>19997455</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061088069</t>
+          <t>https://m.place.naver.com/place/19997455</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5520,29 +5596,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일 김미쉘터</t>
+          <t>가빈네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>patent37435@naver.com</t>
+          <t>happyhannj@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1320-1993</t>
+          <t>0507-1431-8259</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 55</t>
+          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5552,7 +5628,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5573,17 +5649,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>266</v>
+        <v>58</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5592,12 +5668,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1802694964</t>
+          <t>38500996</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802694964</t>
+          <t>https://m.place.naver.com/place/38500996</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5614,29 +5690,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>다리아네일 안국역</t>
+          <t>네일아토</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>puppyholic@naver.com</t>
+          <t>sk3374@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1347-1494</t>
+          <t>0507-1416-6630</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
+          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daria_nail_ssu</t>
+          <t>https://www.instagram.com/nail_ato</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5671,13 +5747,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="R57" t="n">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5686,12 +5762,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1165184706</t>
+          <t>1446399532</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165184706</t>
+          <t>https://m.place.naver.com/place/1446399532</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5708,34 +5784,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>제이뷰티 눈썹&amp;네일</t>
+          <t>미스에이 네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jbeauty4022@naver.com</t>
+          <t>kinetixart@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1422-4022</t>
+          <t>070-8277-3597</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
+          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jbeauty4022</t>
+          <t>https://pf.kakao.com/_jhDaG</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5745,7 +5821,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5756,7 +5832,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5765,13 +5841,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3316</v>
+        <v>54</v>
       </c>
       <c r="Q58" t="n">
-        <v>226</v>
+        <v>10</v>
       </c>
       <c r="R58" t="n">
-        <v>3542</v>
+        <v>64</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5780,12 +5856,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1776791877</t>
+          <t>1758327919</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776791877</t>
+          <t>https://m.place.naver.com/place/1758327919</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5802,30 +5878,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일지니</t>
+          <t>핸더뷰티</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1231yc@naver.com</t>
+          <t>koenji_nail@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1380-1146</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
+          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xeTiCG</t>
+          <t>https://blog.naver.com/koenji_nail</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5835,7 +5915,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5846,7 +5926,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5855,13 +5935,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1772</v>
+        <v>357</v>
       </c>
       <c r="Q59" t="n">
-        <v>93</v>
+        <v>412</v>
       </c>
       <c r="R59" t="n">
-        <v>1865</v>
+        <v>769</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5870,12 +5950,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1073291540</t>
+          <t>37558905</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073291540</t>
+          <t>https://m.place.naver.com/place/37558905</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5892,29 +5972,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일브러쉬</t>
+          <t>모스네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ss7370306@naver.com</t>
+          <t>buzzerrbeate@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1332-0306</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
+          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ss7370306</t>
+          <t>https://www.instagram.com/moss.nail_</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5929,7 +6005,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5940,22 +6016,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>65</v>
+        <v>226</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R60" t="n">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5964,12 +6040,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>35559430</t>
+          <t>1061088069</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35559430</t>
+          <t>https://m.place.naver.com/place/1061088069</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5986,29 +6062,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일 을지로지하쇼핑센터3구역점</t>
+          <t>치즈네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>43995@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>02-2278-2990</t>
+          <t>02-6405-4578</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
+          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cheesenail</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6018,7 +6094,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6039,17 +6115,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6058,12 +6134,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>37588249</t>
+          <t>37542182</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588249</t>
+          <t>https://m.place.naver.com/place/37542182</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6080,24 +6156,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일하트</t>
+          <t>네일해요</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>nailheart053@naver.com</t>
+          <t>elliestar@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0507-1484-8604</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+          <t>서울특별시 종로구 종로44길 9 2층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6137,13 +6209,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>382</v>
+        <v>6</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6152,12 +6224,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1101101042</t>
+          <t>1213168091</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101101042</t>
+          <t>https://m.place.naver.com/place/1213168091</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6174,29 +6246,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>맥스네일</t>
+          <t>오프엠네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>machojj@naver.com</t>
+          <t>hgy___g@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>02-2272-4141</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 204 3층</t>
+          <t>서울특별시 중구 명동4길 40 4층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/machojj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6206,12 +6274,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6227,17 +6295,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="Q63" t="n">
-        <v>532</v>
+        <v>6</v>
       </c>
       <c r="R63" t="n">
-        <v>730</v>
+        <v>102</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6246,12 +6314,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>32786203</t>
+          <t>2099192808</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32786203</t>
+          <t>https://m.place.naver.com/place/2099192808</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6268,25 +6336,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>리라뷰티</t>
+          <t>GK네일 현대시티아울렛 동대문점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>rira_225@naver.com</t>
+          <t>liziah@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1339-5357</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lira_4994/</t>
+          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6321,13 +6393,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>120</v>
+        <v>332</v>
       </c>
       <c r="Q64" t="n">
-        <v>276</v>
+        <v>46</v>
       </c>
       <c r="R64" t="n">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6336,12 +6408,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1100664846</t>
+          <t>1245812382</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100664846</t>
+          <t>https://m.place.naver.com/place/1245812382</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6358,29 +6430,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>드팜므</t>
+          <t>비조네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mellowryu@naver.com</t>
+          <t>ozllzln17@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0507-1317-3395</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 42 B110호</t>
+          <t>서울특별시 종로구 종로 379</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/defemmeeee</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6390,7 +6458,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6411,17 +6479,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="Q65" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6430,12 +6498,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1741921081</t>
+          <t>19813956</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1741921081</t>
+          <t>https://m.place.naver.com/place/19813956</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6452,12 +6520,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>살롱드소피</t>
+          <t>지아네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>skincare25@naver.com</t>
+          <t>jjaa1334@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -6465,12 +6533,12 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
+          <t>서울특별시 중구 명동10길 40 6층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salon_de_sophie_</t>
+          <t>https://www.instagram.com/jeonjia9</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6505,13 +6573,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="Q66" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="R66" t="n">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6520,12 +6588,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>13434920</t>
+          <t>1279897442</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13434920</t>
+          <t>https://m.place.naver.com/place/1279897442</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6542,29 +6610,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>바비 네일왁싱</t>
+          <t>9층네일 명동점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>uchka247@naver.com</t>
+          <t>dmgktnqls@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1490-9887</t>
+          <t>0507-1359-1372</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로44길 6-9 4층</t>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barbie.waxnail</t>
+          <t>https://www.instagram.com/9.nailstudio</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6599,13 +6667,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="R67" t="n">
-        <v>164</v>
+        <v>281</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6614,12 +6682,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1019484164</t>
+          <t>1681308543</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1019484164</t>
+          <t>https://m.place.naver.com/place/1681308543</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6636,29 +6704,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nail by Jade</t>
+          <t>해피네일데이</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>happynailday@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1360-1011</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
+          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_by_jade</t>
+          <t>https://blog.naver.com/happynailday</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6673,7 +6737,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6693,13 +6757,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>184</v>
       </c>
       <c r="R68" t="n">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6708,12 +6772,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>944614599</t>
+          <t>298136226</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/944614599</t>
+          <t>https://m.place.naver.com/place/298136226</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6730,29 +6794,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일 오우브</t>
+          <t>빌러브드 네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>keroo90@naver.com</t>
+          <t>novembro_12@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1407-0437</t>
+          <t>02-733-8318</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
+          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.ouv</t>
+          <t>http://www.instagram.com/beloved_nail_</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6787,13 +6851,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>154</v>
+        <v>371</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="R69" t="n">
-        <v>155</v>
+        <v>400</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6802,12 +6866,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1559030900</t>
+          <t>877681682</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559030900</t>
+          <t>https://m.place.naver.com/place/877681682</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6824,29 +6888,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>지호네일</t>
+          <t>네일누하</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>yongsanly@naver.com</t>
+          <t>annoi_@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1314-5759</t>
+          <t>0507-1348-9398</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 265 5층,6층</t>
+          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jihonail</t>
+          <t>https://www.instagram.com/nail.nuha</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6881,13 +6945,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R70" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6896,12 +6960,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1285361463</t>
+          <t>1370069746</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285361463</t>
+          <t>https://m.place.naver.com/place/1370069746</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6918,24 +6982,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일블라썸</t>
+          <t>크리스탈손톱</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>juyean123@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1347-8173</t>
+          <t>02-3398-4445</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 95호</t>
+          <t>서울특별시 중구 장충단로 275</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6975,13 +7039,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>333</v>
+        <v>3</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>343</v>
+        <v>4</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6990,12 +7054,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1794862527</t>
+          <t>1895018257</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794862527</t>
+          <t>https://m.place.naver.com/place/1895018257</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7012,29 +7076,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일바이안</t>
+          <t>지호네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ye1yang@naver.com</t>
+          <t>yongsanly@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>02-511-5621</t>
+          <t>0507-1314-5759</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로9길 12 8층</t>
+          <t>서울특별시 중구 다산로 265 5층,6층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyahn</t>
+          <t>https://www.instagram.com/jihonail</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7069,13 +7133,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7084,12 +7148,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1084164588</t>
+          <t>1285361463</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084164588</t>
+          <t>https://m.place.naver.com/place/1285361463</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7106,25 +7170,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>꾸미다</t>
+          <t>블링네일 종로점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>yem1104@naver.com</t>
+          <t>beaulynail@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1448-0036</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
+          <t>서울특별시 종로구 대학로 16-1 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
+          <t>https://blog.naver.com/beaulynail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7139,7 +7207,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7159,13 +7227,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="Q73" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="R73" t="n">
-        <v>4</v>
+        <v>216</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7174,12 +7242,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1095499576</t>
+          <t>60890323</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095499576</t>
+          <t>https://m.place.naver.com/place/60890323</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7196,29 +7264,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>꽁냥네일</t>
+          <t>꽃소니 네일아트</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>qorgh1236@naver.com</t>
+          <t>qhpw4cpk@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1418-2440</t>
+          <t>070-8615-3478</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 249-28 3층</t>
+          <t>서울특별시 종로구 대학로5길 8 2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ggongnyang_nail</t>
+          <t>https://www.instagram.com/flower_handnails</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7253,13 +7321,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>276</v>
+        <v>105</v>
       </c>
       <c r="Q74" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>318</v>
+        <v>109</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7268,12 +7336,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1570914826</t>
+          <t>1593950281</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570914826</t>
+          <t>https://m.place.naver.com/place/1593950281</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7290,29 +7358,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일,현</t>
+          <t>종로네일샵</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>qkrwlsk126@naver.com</t>
+          <t>bitna0614@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1316-0133</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
+          <t>서울특별시 종로구 종로 62</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hyun.__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7322,7 +7386,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7343,17 +7407,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7362,12 +7426,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1120708839</t>
+          <t>1928832758</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120708839</t>
+          <t>https://m.place.naver.com/place/1928832758</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7384,29 +7448,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>루다네일</t>
+          <t>그리드네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>rudanail1515@naver.com</t>
+          <t>boye_like@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1357-1516</t>
+          <t>0507-1405-0461</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
+          <t>서울특별시 종로구 옥인길 44</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://instagram.com/rudanail_daehakro</t>
+          <t>http://instagram.com/love_grid</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7432,7 +7496,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7441,13 +7505,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>254</v>
+        <v>53</v>
       </c>
       <c r="Q76" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>366</v>
+        <v>55</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7456,12 +7520,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>34551572</t>
+          <t>38531607</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34551572</t>
+          <t>https://m.place.naver.com/place/38531607</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7478,29 +7542,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일하루</t>
+          <t>무아네일</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>nail_haru@naver.com</t>
+          <t>loowowool@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1361-1445</t>
+          <t>0507-1436-1716</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
+          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_haru</t>
+          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7515,7 +7579,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7531,17 +7595,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>413</v>
+        <v>1</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7550,12 +7614,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>37089409</t>
+          <t>2038424794</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37089409</t>
+          <t>https://m.place.naver.com/place/2038424794</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7572,29 +7636,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>네일온 명동본점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>nailon_myeongdong@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>02-765-5525</t>
+          <t>0507-1302-8995</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 53-1 1층</t>
+          <t>서울특별시 중구 을지로 88 을특8호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailon_myeongdong</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7604,12 +7668,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7625,17 +7689,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="Q78" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R78" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7644,12 +7708,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>34352879</t>
+          <t>2054691209</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34352879</t>
+          <t>https://m.place.naver.com/place/2054691209</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7666,29 +7730,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>살롱드벨르네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ysbfly@naver.com</t>
+          <t>salondebelle_nail@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1358-8653</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+          <t>서울특별시 종로구 종로 65 2층 208호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lee____</t>
+          <t>https://blog.naver.com/salondebelle_nail</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7703,7 +7763,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7723,13 +7783,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>111</v>
+        <v>355</v>
       </c>
       <c r="Q79" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="R79" t="n">
-        <v>120</v>
+        <v>416</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7738,12 +7798,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>2065943871</t>
+          <t>1768571536</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065943871</t>
+          <t>https://m.place.naver.com/place/1768571536</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7760,25 +7820,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>마이파우치</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>안젤라네일샵</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>angella3977@naver.com</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1402-0809</t>
+          <t>0507-1493-3335</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mypouch.kangbbin</t>
+          <t>https://blog.naver.com/angella3977</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7793,7 +7857,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7813,13 +7877,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>11</v>
+        <v>664</v>
       </c>
       <c r="Q80" t="n">
-        <v>183</v>
+        <v>12</v>
       </c>
       <c r="R80" t="n">
-        <v>194</v>
+        <v>676</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7828,12 +7892,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>38642341</t>
+          <t>1274163754</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38642341</t>
+          <t>https://m.place.naver.com/place/1274163754</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7850,21 +7914,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>종로네일샵</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>네일멜로우</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sc09mc@naver.com</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1356-7672</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 62</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_mellow_11/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7874,7 +7946,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7895,17 +7967,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7914,12 +7986,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1928832758</t>
+          <t>1933958367</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928832758</t>
+          <t>https://m.place.naver.com/place/1933958367</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -7936,26 +8008,34 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>손톱그림</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>르노브네일</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>hshee069@naver.com</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1307-5439</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
+          <t>서울특별시 종로구 성균관로 38 1층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_sketch_8478/</t>
+          <t>http://pf.kakao.com/_XxbVPn</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7976,7 +8056,7 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7985,13 +8065,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3</v>
+        <v>407</v>
       </c>
       <c r="Q82" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="R82" t="n">
-        <v>76</v>
+        <v>428</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8000,12 +8080,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1124095560</t>
+          <t>1890443515</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1124095560</t>
+          <t>https://m.place.naver.com/place/1890443515</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8022,25 +8102,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>베리네일</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>네일&amp;페일아트</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>lsbangel@naver.com</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0507-1419-6623</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
+          <t>서울특별시 종로구 진흥로 446</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/berry_nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8050,7 +8130,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8071,17 +8151,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8090,12 +8170,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1394925944</t>
+          <t>20871402</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394925944</t>
+          <t>https://m.place.naver.com/place/20871402</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8112,25 +8192,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>네일문</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>JIN네일</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>jin_nail6453@naver.com</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>02-730-0010</t>
+          <t>0507-1392-5159</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
+          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgate._.mr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8140,7 +8224,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8161,17 +8245,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>593</v>
+        <v>64</v>
       </c>
       <c r="Q84" t="n">
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>774</v>
+        <v>65</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8180,12 +8264,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>13534535</t>
+          <t>1530291597</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13534535</t>
+          <t>https://m.place.naver.com/place/1530291597</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8202,29 +8286,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>안젤라네일샵</t>
+          <t>베리네일</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>angella3977@naver.com</t>
+          <t>yeonee09@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1493-3335</t>
+          <t>0507-1419-6623</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
+          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/angella3977</t>
+          <t>https://www.instagram.com/berry_nail_</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8239,7 +8323,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8259,13 +8343,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>664</v>
+        <v>77</v>
       </c>
       <c r="Q85" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R85" t="n">
-        <v>676</v>
+        <v>84</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8274,12 +8358,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1274163754</t>
+          <t>1394925944</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274163754</t>
+          <t>https://m.place.naver.com/place/1394925944</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8296,35 +8380,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>코코네일</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>영심이손톱</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>lovellies@naver.com</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>02-318-6668</t>
+          <t>02-735-0031</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
+          <t>서울특별시 종로구 종로 88 701호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8345,17 +8433,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8364,12 +8452,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1874418389</t>
+          <t>1116851430</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874418389</t>
+          <t>https://m.place.naver.com/place/1116851430</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8386,25 +8474,33 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>아머네일</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+          <t>레푸스 종로점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>refuss_jong_ro@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>chy0802@ahasoft.co.kr</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1364-4429</t>
+          <t>02-720-4544</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
+          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_pzkMG</t>
+          <t>https://booking.naver.com/booking/13/bizes/857013</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8414,7 +8510,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8430,7 +8526,7 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -8439,13 +8535,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>262</v>
+        <v>862</v>
       </c>
       <c r="Q87" t="n">
-        <v>97</v>
+        <v>360</v>
       </c>
       <c r="R87" t="n">
-        <v>359</v>
+        <v>1222</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8454,12 +8550,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1312237193</t>
+          <t>1237692187</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312237193</t>
+          <t>https://m.place.naver.com/place/1237692187</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8476,29 +8572,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>디디 네일바</t>
+          <t>맥스네일</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>heeja090@naver.com</t>
+          <t>machojj@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1476-0228</t>
+          <t>02-2272-4141</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
+          <t>서울특별시 중구 퇴계로 204 3층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/didi___nailbar</t>
+          <t>https://blog.naver.com/machojj</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8513,7 +8609,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8533,13 +8629,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="Q88" t="n">
-        <v>24</v>
+        <v>532</v>
       </c>
       <c r="R88" t="n">
-        <v>213</v>
+        <v>730</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8548,12 +8644,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1134899134</t>
+          <t>32786203</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134899134</t>
+          <t>https://m.place.naver.com/place/32786203</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8570,29 +8666,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>영심이손톱</t>
+          <t>굿모닝네일</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>lovellies@naver.com</t>
+          <t>clsrn9606@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>02-735-0031</t>
+          <t>0507-1400-8607</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 88 701호</t>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8618,7 +8714,7 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8627,13 +8723,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R89" t="n">
-        <v>1</v>
+        <v>247</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8642,12 +8738,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1116851430</t>
+          <t>13051690</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116851430</t>
+          <t>https://m.place.naver.com/place/13051690</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8664,29 +8760,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GK네일 현대시티아울렛 동대문점</t>
+          <t>네일해썸</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>liziah@naver.com</t>
+          <t>llllcmalll@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1339-5357</t>
+          <t>0507-1342-3168</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
+          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_hatssome</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8712,7 +8808,7 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8721,13 +8817,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>332</v>
+        <v>86</v>
       </c>
       <c r="Q90" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R90" t="n">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8736,12 +8832,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1245812382</t>
+          <t>1991633917</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245812382</t>
+          <t>https://m.place.naver.com/place/1991633917</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8758,25 +8854,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>무아네일</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>올리브네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>djdjqq1663@naver.com</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1436-1716</t>
+          <t>02-2075-7775</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
+          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/djdjqq1663</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8791,7 +8891,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8802,7 +8902,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8811,13 +8911,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>3106</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>3357</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8826,12 +8926,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2038424794</t>
+          <t>35751284</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038424794</t>
+          <t>https://m.place.naver.com/place/35751284</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8848,29 +8948,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>뉴문네일</t>
+          <t>드로잉쇼</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>xdaredare@naver.com</t>
+          <t>odshow@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1354-6577</t>
+          <t>02-777-1090</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 7 2층</t>
+          <t>서울특별시 중구 남대문로 60</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>http://instagram.com/newmoonnail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8880,7 +8980,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8901,17 +9001,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>149</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R92" t="n">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -8920,12 +9020,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1689136529</t>
+          <t>1726036993</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689136529</t>
+          <t>https://m.place.naver.com/place/1726036993</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -8942,30 +9042,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>미스에이 네일</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>드네일 광화문점</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>dahaeyoo@naver.com</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>070-8277-3597</t>
+          <t>0507-1351-9192</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
+          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_jhDaG</t>
+          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -8986,7 +9090,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8995,13 +9099,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="Q93" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R93" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9010,12 +9114,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1758327919</t>
+          <t>1372444756</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758327919</t>
+          <t>https://m.place.naver.com/place/1372444756</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9032,29 +9136,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>네일온 명동본점</t>
+          <t>살롱드소피</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>nailon_myeongdong@naver.com</t>
+          <t>skincare25@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>0507-1302-8995</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 을특8호</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon_myeongdong</t>
+          <t>https://www.instagram.com/salon_de_sophie_</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9069,7 +9169,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9089,13 +9189,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="Q94" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="R94" t="n">
-        <v>38</v>
+        <v>175</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9104,12 +9204,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>2054691209</t>
+          <t>13434920</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054691209</t>
+          <t>https://m.place.naver.com/place/13434920</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9126,25 +9226,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>굿모닝네일</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>꾸밈네일아트</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>fusion02@naver.com</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1400-8607</t>
+          <t>02-733-7942</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gmnail_eyelash</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9154,7 +9258,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9170,22 +9274,22 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>241</v>
+        <v>2</v>
       </c>
       <c r="Q95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R95" t="n">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9194,12 +9298,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>13051690</t>
+          <t>614593678</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13051690</t>
+          <t>https://m.place.naver.com/place/614593678</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9216,25 +9320,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>오브 코코네일</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>디디 네일바</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>heeja090@naver.com</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1371-8921</t>
+          <t>0507-1476-0228</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
+          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ofconail</t>
+          <t>https://www.instagram.com/didi___nailbar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9269,13 +9377,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>658</v>
+        <v>189</v>
       </c>
       <c r="Q96" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="R96" t="n">
-        <v>705</v>
+        <v>213</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9284,12 +9392,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1009626425</t>
+          <t>1134899134</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009626425</t>
+          <t>https://m.place.naver.com/place/1134899134</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9306,29 +9414,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>에이커뷰티네일</t>
+          <t>네일라이트</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>happymin_life@naver.com</t>
+          <t>elegant1025@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>02-722-5558</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
+          <t>서울특별시 종로구 세종대로23길 5 3층</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>http://instagram.com/acre_beauty</t>
+          <t>http://instagram.com/_nail_light_</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9363,13 +9467,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>117</v>
+        <v>540</v>
       </c>
       <c r="Q97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R97" t="n">
-        <v>121</v>
+        <v>546</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9378,12 +9482,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1812848399</t>
+          <t>1105652769</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1812848399</t>
+          <t>https://m.place.naver.com/place/1105652769</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9400,29 +9504,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>혜리앤케어</t>
+          <t>리빈네일</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>micahyesung@naver.com</t>
+          <t>jcj0217@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>02-725-1741</t>
+          <t>0507-1349-9808</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/rivin_nail</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9432,7 +9536,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9453,17 +9557,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9472,12 +9576,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>155402276</t>
+          <t>1315671750</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/155402276</t>
+          <t>https://m.place.naver.com/place/1315671750</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9494,29 +9598,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>그리드네일</t>
+          <t>찰스네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>boye_like@naver.com</t>
+          <t>spotv_sports@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1405-0461</t>
+          <t>0507-1307-4179</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 44</t>
+          <t>서울특별시 종로구 종로12길 9 3층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>http://instagram.com/love_grid</t>
+          <t>http://www.instagram.com/charles__nail</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9551,13 +9655,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>53</v>
+        <v>529</v>
       </c>
       <c r="Q99" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="R99" t="n">
-        <v>55</v>
+        <v>585</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9566,12 +9670,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>38531607</t>
+          <t>13034248</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531607</t>
+          <t>https://m.place.naver.com/place/13034248</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9588,29 +9692,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>너 참 예쁘다</t>
+          <t>엘로아네일</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>yuiu1401@naver.com</t>
+          <t>hhhong88@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1434-8892</t>
+          <t>0507-1314-9339</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/youarebeautiful_seoul</t>
+          <t>https://www.instagram.com/eloa__nail/</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9630,14 +9734,10 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>X</t>
@@ -9649,13 +9749,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>529</v>
+        <v>11</v>
       </c>
       <c r="Q100" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>1369</v>
+        <v>11</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9664,12 +9764,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1466732665</t>
+          <t>2087274322</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466732665</t>
+          <t>https://m.place.naver.com/place/2087274322</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9686,29 +9786,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>크리스탈손톱</t>
+          <t>어나더네일</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>juyean123@naver.com</t>
+          <t>soojinpo@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>02-3398-4445</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 275</t>
+          <t>서울특별시 종로구 지봉로 56-1 1층</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/another_n_ail</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9718,7 +9814,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9739,17 +9835,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="Q101" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R101" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9758,12 +9854,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1895018257</t>
+          <t>1214193406</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895018257</t>
+          <t>https://m.place.naver.com/place/1214193406</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -9780,29 +9876,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
+          <t>제이뷰티 눈썹&amp;네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>jbeauty4022@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>02-756-4143</t>
+          <t>0507-1422-4022</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
+          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jbeauty4022</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9812,12 +9908,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9833,17 +9929,17 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>4</v>
+        <v>3316</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="R102" t="n">
-        <v>4</v>
+        <v>3542</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9852,12 +9948,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>31315234</t>
+          <t>1776791877</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315234</t>
+          <t>https://m.place.naver.com/place/1776791877</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -9874,25 +9970,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>살롱드벨르네일</t>
+          <t>오브 코코네일</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>salondebelle_nail@naver.com</t>
+          <t>9ansapres@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1371-8921</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 65 2층 208호</t>
+          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/salondebelle_nail</t>
+          <t>https://www.instagram.com/ofconail</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9907,7 +10007,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9927,13 +10027,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>355</v>
+        <v>658</v>
       </c>
       <c r="Q103" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R103" t="n">
-        <v>416</v>
+        <v>705</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -9942,12 +10042,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1768571536</t>
+          <t>1009626425</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768571536</t>
+          <t>https://m.place.naver.com/place/1009626425</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -9964,29 +10064,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>폭시네일</t>
+          <t>드팜므</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>tomebooy@naver.com</t>
+          <t>tomjelbbuu@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1403-4791</t>
+          <t>0507-1317-3395</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동망산길 13 2층</t>
+          <t>서울특별시 종로구 사직로8길 42 B110호</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/defemmeeee</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9996,7 +10096,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10017,17 +10117,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="R104" t="n">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10036,12 +10136,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>40986070</t>
+          <t>1741921081</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/40986070</t>
+          <t>https://m.place.naver.com/place/1741921081</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10058,39 +10158,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>아따걸네일</t>
+          <t>엔79 Nail</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>addagirl2@naver.com</t>
+          <t>loveucream@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1328-8505</t>
+          <t>0507-1390-0326</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
+          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_GWaij</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10106,22 +10206,22 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>285</v>
+        <v>163</v>
       </c>
       <c r="Q105" t="n">
-        <v>649</v>
+        <v>19</v>
       </c>
       <c r="R105" t="n">
-        <v>934</v>
+        <v>182</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10130,12 +10230,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>13047890</t>
+          <t>1756267523</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13047890</t>
+          <t>https://m.place.naver.com/place/1756267523</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10152,29 +10252,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>루아르블랑 네일</t>
+          <t>네일브러쉬</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>failuredw@naver.com</t>
+          <t>ss7370306@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1483-9411</t>
+          <t>0507-1332-0306</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
+          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHajSJei</t>
+          <t>https://blog.naver.com/ss7370306</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10189,7 +10289,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -10200,22 +10300,22 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="Q106" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="R106" t="n">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10224,12 +10324,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2013893243</t>
+          <t>35559430</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013893243</t>
+          <t>https://m.place.naver.com/place/35559430</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10246,29 +10346,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>루이비네일</t>
+          <t>효녀네일</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>zhengyinji888@naver.com</t>
+          <t>hy0d0ng2@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1445-2047</t>
+          <t>0507-1366-2991</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
+          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>http://instagram.com/luyibi_nail8</t>
+          <t>https://www.instagram.com/hyonyeo_nail</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10303,13 +10403,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>481</v>
+        <v>4</v>
       </c>
       <c r="Q107" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>570</v>
+        <v>4</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10318,12 +10418,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>21306056</t>
+          <t>2038116522</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21306056</t>
+          <t>https://m.place.naver.com/place/2038116522</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10340,21 +10440,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>어나더네일</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>네일 을지로지하쇼핑센터3구역점</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>02-2278-2990</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 56-1 1층</t>
+          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/another_n_ail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10364,7 +10472,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10385,17 +10493,17 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="Q108" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R108" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10404,12 +10512,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>1214193406</t>
+          <t>37588249</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214193406</t>
+          <t>https://m.place.naver.com/place/37588249</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10426,25 +10534,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>해피네일데이</t>
+          <t>네일하트</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>happynailday@naver.com</t>
+          <t>nailheart053@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0507-1484-8604</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/happynailday</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10454,12 +10566,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10475,17 +10587,17 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>166</v>
+        <v>373</v>
       </c>
       <c r="Q109" t="n">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="R109" t="n">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10494,12 +10606,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>298136226</t>
+          <t>1101101042</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/298136226</t>
+          <t>https://m.place.naver.com/place/1101101042</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10516,12 +10628,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>아트만네일</t>
+          <t>네일, 사월</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ppangsun238@naver.com</t>
+          <t>pooddin@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -10529,17 +10641,17 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
+          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Txkxgfxj</t>
+          <t>https://www.instagram.com/nail__april</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -10560,7 +10672,7 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -10569,13 +10681,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>16</v>
+        <v>644</v>
       </c>
       <c r="Q110" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R110" t="n">
-        <v>36</v>
+        <v>658</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10584,12 +10696,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1284929161</t>
+          <t>1448977317</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284929161</t>
+          <t>https://m.place.naver.com/place/1448977317</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10606,29 +10718,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>위치네일스 종로점</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1364-9020</t>
+          <t>0507-1358-8653</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 51</t>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>https://www.instagram.com/nail_lee____</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10643,7 +10755,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -10663,13 +10775,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1060</v>
+        <v>111</v>
       </c>
       <c r="Q111" t="n">
-        <v>149</v>
+        <v>9</v>
       </c>
       <c r="R111" t="n">
-        <v>1209</v>
+        <v>120</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10678,12 +10790,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1543496206</t>
+          <t>2065943871</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543496206</t>
+          <t>https://m.place.naver.com/place/2065943871</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10700,29 +10812,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>네일원</t>
+          <t>강앤니네일스</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>nail_one@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0507-1338-0475</t>
+          <t>0507-1468-2316</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 52-1 2층</t>
+          <t>서울특별시 중구 장충단로 227-2 4층</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_one</t>
+          <t>http://instagram.com/kangannynails</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10757,13 +10869,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10772,12 +10884,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1105911364</t>
+          <t>1711237836</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105911364</t>
+          <t>https://m.place.naver.com/place/1711237836</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10794,25 +10906,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>안0네일</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>손톱그림</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>on_calli@naver.com</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>02-6052-7778</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
+          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_sketch_8478/</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10822,7 +10934,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10843,17 +10955,17 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="R113" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10862,12 +10974,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1487336161</t>
+          <t>1124095560</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487336161</t>
+          <t>https://m.place.naver.com/place/1124095560</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -10884,25 +10996,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>나비네일</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>네일블라썸</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>wilklove@naver.com</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>02-319-7844</t>
+          <t>0507-1347-8173</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
+          <t>서울특별시 중구 소공로 102 95호</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>http://instagram.com/navinailnavinail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10912,7 +11028,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -10933,17 +11049,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>26</v>
+        <v>333</v>
       </c>
       <c r="Q114" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R114" t="n">
-        <v>28</v>
+        <v>343</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -10952,12 +11068,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>735546684</t>
+          <t>1794862527</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/735546684</t>
+          <t>https://m.place.naver.com/place/1794862527</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -10974,29 +11090,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>리빈네일</t>
+          <t>너 참 예쁘다</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jcj0217@naver.com</t>
+          <t>yuiu1401@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1349-9808</t>
+          <t>0507-1434-8892</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rivin_nail</t>
+          <t>http://www.instagram.com/youarebeautiful_seoul</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11016,10 +11132,14 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr">
         <is>
           <t>X</t>
@@ -11031,13 +11151,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>128</v>
+        <v>529</v>
       </c>
       <c r="Q115" t="n">
-        <v>2</v>
+        <v>840</v>
       </c>
       <c r="R115" t="n">
-        <v>130</v>
+        <v>1369</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11046,12 +11166,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1315671750</t>
+          <t>1466732665</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315671750</t>
+          <t>https://m.place.naver.com/place/1466732665</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">

--- a/naver-place-crawler/results_nail/종로_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/종로_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -567,11 +567,7 @@
           <t>미스에이 네일</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>kinetixart@naver.com</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -658,29 +654,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>베리네일</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>yeonee09@naver.com</t>
-        </is>
-      </c>
+          <t>네일 을지로지하쇼핑센터3구역점</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1419-6623</t>
+          <t>02-2278-2990</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
+          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/berry_nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +682,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +703,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +722,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1394925944</t>
+          <t>37588249</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394925944</t>
+          <t>https://m.place.naver.com/place/37588249</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,25 +744,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>살롱드소피</t>
+          <t>엔79 Nail</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>skincare25@naver.com</t>
+          <t>loveucream@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1390-0326</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
+          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salon_de_sophie_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -780,7 +776,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -801,17 +797,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="R4" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +816,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13434920</t>
+          <t>1756267523</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13434920</t>
+          <t>https://m.place.naver.com/place/1756267523</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,35 +838,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아셀네일</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>asher9809@naver.com</t>
-        </is>
-      </c>
+          <t>아머네일</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1364-4429</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 253 10층 11호</t>
+          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_pzkMG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -886,22 +882,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>59</v>
+        <v>262</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="R5" t="n">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,12 +906,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1229434440</t>
+          <t>1312237193</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229434440</t>
+          <t>https://m.place.naver.com/place/1312237193</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -932,34 +928,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>명동네일 제니뷰티</t>
+          <t>이츠네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hyoyeol@naver.com</t>
+          <t>icacc89@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1487-9603</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8길 43 3층</t>
+          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jennybeauty.md/</t>
+          <t>http://pf.kakao.com/_duxhxdn</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -980,7 +972,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,13 +981,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,12 +996,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1845062262</t>
+          <t>31949587</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845062262</t>
+          <t>https://m.place.naver.com/place/31949587</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1026,25 +1018,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>모스네일</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>buzzerrbeate@naver.com</t>
-        </is>
-      </c>
+          <t>키튼네일</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>02-765-8566</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
+          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss.nail_</t>
+          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,7 +1062,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1079,13 +1071,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>227</v>
+        <v>494</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="R7" t="n">
-        <v>240</v>
+        <v>548</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,12 +1086,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1061088069</t>
+          <t>1065031131</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061088069</t>
+          <t>https://m.place.naver.com/place/1065031131</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1116,34 +1108,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>영심이손톱</t>
+          <t>손톱그림</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lovellies@naver.com</t>
+          <t>on_calli@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>02-735-0031</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 88 701호</t>
+          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
+          <t>https://www.instagram.com/nail_sketch_8478/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1173,13 +1161,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,12 +1176,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1116851430</t>
+          <t>1124095560</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116851430</t>
+          <t>https://m.place.naver.com/place/1124095560</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1210,25 +1198,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>지아네일</t>
+          <t>핸더뷰티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jjaa1334@naver.com</t>
+          <t>koenji_nail@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1380-1146</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 40 6층</t>
+          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeonjia9</t>
+          <t>https://blog.naver.com/koenji_nail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1243,7 +1235,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1263,13 +1255,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>65</v>
+        <v>357</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>412</v>
       </c>
       <c r="R9" t="n">
-        <v>75</v>
+        <v>769</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1279897442</t>
+          <t>37558905</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279897442</t>
+          <t>https://m.place.naver.com/place/37558905</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1300,29 +1292,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일누하</t>
+          <t>오프엠네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>hgy___g@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1348-9398</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
+          <t>서울특별시 중구 명동4길 40 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.nuha</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1332,7 +1320,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1353,17 +1341,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1372,12 +1360,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1370069746</t>
+          <t>2099192808</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370069746</t>
+          <t>https://m.place.naver.com/place/2099192808</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1394,12 +1382,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아트만네일</t>
+          <t>꾸미다</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ppangsun238@naver.com</t>
+          <t>yem1104@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1407,17 +1395,17 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
+          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Txkxgfxj</t>
+          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1438,7 +1426,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1447,13 +1435,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1462,12 +1450,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1284929161</t>
+          <t>1095499576</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284929161</t>
+          <t>https://m.place.naver.com/place/1095499576</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1484,29 +1472,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일,현</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>qkrwlsk126@naver.com</t>
-        </is>
-      </c>
+          <t>꾸밈네일아트</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1316-0133</t>
+          <t>02-733-7942</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
+          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hyun.__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1516,7 +1500,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1537,17 +1521,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1556,12 +1540,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1120708839</t>
+          <t>614593678</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120708839</t>
+          <t>https://m.place.naver.com/place/614593678</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1578,29 +1562,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>바비 네일왁싱</t>
+          <t>루아르블랑 네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>uchka247@naver.com</t>
+          <t>failuredw@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1490-9887</t>
+          <t>0507-1483-9411</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로44길 6-9 4층</t>
+          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barbie.waxnail</t>
+          <t>https://open.kakao.com/o/sHajSJei</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1626,7 +1610,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1635,13 +1619,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="R13" t="n">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1650,12 +1634,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1019484164</t>
+          <t>2013893243</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1019484164</t>
+          <t>https://m.place.naver.com/place/2013893243</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1672,44 +1656,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>프로뷰티</t>
+          <t>레푸스 종로점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>probeauty_blog@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>refuss_jong_ro@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>chy0802@ahasoft.co.kr</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1435-2789</t>
+          <t>02-720-4544</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8가길 9 3층</t>
+          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/probeauty_blog</t>
+          <t>https://booking.naver.com/booking/13/bizes/857013</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1729,13 +1717,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>570</v>
+        <v>862</v>
       </c>
       <c r="Q14" t="n">
-        <v>679</v>
+        <v>360</v>
       </c>
       <c r="R14" t="n">
-        <v>1249</v>
+        <v>1222</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,12 +1732,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>19997455</t>
+          <t>1237692187</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19997455</t>
+          <t>https://m.place.naver.com/place/1237692187</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1766,29 +1754,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>올리브네일&amp;속눈썹</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>djdjqq1663@naver.com</t>
-        </is>
-      </c>
+          <t>그리드네일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>02-2075-7775</t>
+          <t>0507-1405-0461</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
+          <t>서울특별시 종로구 옥인길 44</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/djdjqq1663</t>
+          <t>http://instagram.com/love_grid</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1803,7 +1787,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1814,7 +1798,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1823,13 +1807,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3105</v>
+        <v>53</v>
       </c>
       <c r="Q15" t="n">
-        <v>252</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>3357</v>
+        <v>55</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,12 +1822,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>35751284</t>
+          <t>38531607</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35751284</t>
+          <t>https://m.place.naver.com/place/38531607</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1860,29 +1844,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>굿모닝네일</t>
+          <t>수야디나 네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>clsrn9606@naver.com</t>
+          <t>vastron@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1400-8607</t>
+          <t>0507-1305-2499</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+          <t>서울특별시 중구 충무로 36 2층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gmnail_eyelash</t>
+          <t>https://www.instagram.com/yun_ju423/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1908,7 +1892,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1917,13 +1901,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1932,12 +1916,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13051690</t>
+          <t>1324800762</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13051690</t>
+          <t>https://m.place.naver.com/place/1324800762</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1954,30 +1938,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일지니</t>
+          <t>라라네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1231yc@naver.com</t>
+          <t>redpepper30@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1344-7250</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xeTiCG</t>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1998,7 +1986,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2007,13 +1995,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1775</v>
+        <v>1001</v>
       </c>
       <c r="Q17" t="n">
-        <v>94</v>
+        <v>433</v>
       </c>
       <c r="R17" t="n">
-        <v>1869</v>
+        <v>1434</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2022,12 +2010,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1073291540</t>
+          <t>1303128966</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073291540</t>
+          <t>https://m.place.naver.com/place/1303128966</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2044,29 +2032,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>꽃소니 네일아트</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>qhpw4cpk@naver.com</t>
-        </is>
-      </c>
+          <t>네일리</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>070-8615-3478</t>
+          <t>0507-1358-8653</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로5길 8 2층</t>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flower_handnails</t>
+          <t>https://www.instagram.com/nail_lee____</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2101,13 +2085,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2116,12 +2100,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1593950281</t>
+          <t>2065943871</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593950281</t>
+          <t>https://m.place.naver.com/place/2065943871</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2138,12 +2122,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>릴리엔젤네일</t>
+          <t>살롱드소피</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kiyu0987@naver.com</t>
+          <t>skincare25@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2151,12 +2135,12 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://instagram.com/lilyangel_nail</t>
+          <t>https://www.instagram.com/salon_de_sophie_</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2191,13 +2175,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="Q19" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="R19" t="n">
-        <v>287</v>
+        <v>175</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2206,12 +2190,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1110775717</t>
+          <t>13434920</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110775717</t>
+          <t>https://m.place.naver.com/place/13434920</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2228,29 +2212,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>삼층네일</t>
+          <t>루이비네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wang8241@naver.com</t>
+          <t>zhengyinji888@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1327-8241</t>
+          <t>0507-1445-2047</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wang8241</t>
+          <t>http://instagram.com/luyibi_nail8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2265,7 +2249,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2281,17 +2265,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>531</v>
+        <v>481</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="R20" t="n">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2300,12 +2284,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1894370134</t>
+          <t>21306056</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1894370134</t>
+          <t>https://m.place.naver.com/place/21306056</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2322,25 +2306,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>오토젯네일</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>yr19850217@naver.com</t>
-        </is>
-      </c>
+          <t>네일&amp;페일아트</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로 68</t>
+          <t>서울특별시 종로구 진흥로 446</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.autoznail.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2350,7 +2330,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2375,13 +2355,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2390,12 +2370,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>35506860</t>
+          <t>20871402</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35506860</t>
+          <t>https://m.place.naver.com/place/20871402</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2412,29 +2392,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>무아네일</t>
+          <t>네일하트</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>loowowool@naver.com</t>
+          <t>nailheart053@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1436-1716</t>
+          <t>0507-1484-8604</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2444,7 +2424,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2465,17 +2445,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>382</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2484,12 +2464,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2038424794</t>
+          <t>1101101042</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038424794</t>
+          <t>https://m.place.naver.com/place/1101101042</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2506,25 +2486,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>어나더네일</t>
+          <t>말짜네일 광화문점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>soojinpo@naver.com</t>
+          <t>malzzanail@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1402-3734</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 56-1 1층</t>
+          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/another_n_ail</t>
+          <t>https://blog.naver.com/malzzanail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2539,7 +2523,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2550,7 +2534,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2559,13 +2543,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>58</v>
+        <v>305</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>424</v>
       </c>
       <c r="R23" t="n">
-        <v>69</v>
+        <v>729</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2574,12 +2558,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1214193406</t>
+          <t>37997776</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214193406</t>
+          <t>https://m.place.naver.com/place/37997776</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2596,29 +2580,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일하루</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>nail_haru@naver.com</t>
-        </is>
-      </c>
+          <t>네일, 사월</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1361-1445</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
+          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_haru</t>
+          <t>https://www.instagram.com/nail__april</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2633,7 +2609,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2649,17 +2625,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>67</v>
+        <v>646</v>
       </c>
       <c r="Q24" t="n">
-        <v>346</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>413</v>
+        <v>660</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2668,12 +2644,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>37089409</t>
+          <t>1448977317</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37089409</t>
+          <t>https://m.place.naver.com/place/1448977317</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2690,29 +2666,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diamond Nails</t>
+          <t>네일아토</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ksj673232@naver.com</t>
+          <t>sk3374@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1420-1393</t>
+          <t>0507-1416-6630</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 155 1동 102호</t>
+          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
+          <t>https://www.instagram.com/nail_ato</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2747,13 +2723,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2762,12 +2738,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2040524360</t>
+          <t>1446399532</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040524360</t>
+          <t>https://m.place.naver.com/place/1446399532</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2784,25 +2760,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>종로네일샵</t>
+          <t>안젤라네일샵</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bitna0614@naver.com</t>
+          <t>angella3977@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1493-3335</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 62</t>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/angella3977</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2812,12 +2792,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2833,17 +2813,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>676</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2852,12 +2832,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1928832758</t>
+          <t>1274163754</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928832758</t>
+          <t>https://m.place.naver.com/place/1274163754</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2874,29 +2854,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>가빈네일</t>
+          <t>꽃소니 네일아트</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>happyhannj@naver.com</t>
+          <t>qhpw4cpk@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1431-8259</t>
+          <t>070-8615-3478</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
+          <t>서울특별시 종로구 대학로5길 8 2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
+          <t>https://www.instagram.com/flower_handnails</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2931,13 +2911,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2946,12 +2926,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38500996</t>
+          <t>1593950281</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38500996</t>
+          <t>https://m.place.naver.com/place/1593950281</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2968,29 +2948,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>꽁냥네일</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>qorgh1236@naver.com</t>
-        </is>
-      </c>
+          <t>리빈네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1418-2440</t>
+          <t>0507-1349-9808</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 249-28 3층</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ggongnyang_nail</t>
+          <t>https://www.instagram.com/rivin_nail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3025,13 +3001,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>276</v>
+        <v>129</v>
       </c>
       <c r="Q28" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>318</v>
+        <v>131</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3040,12 +3016,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1570914826</t>
+          <t>1315671750</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570914826</t>
+          <t>https://m.place.naver.com/place/1315671750</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3062,34 +3038,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>비비네일</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>kikiu30@naver.com</t>
-        </is>
-      </c>
+          <t>네일,현</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1378-0246</t>
+          <t>0507-1316-0133</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pAtmG</t>
+          <t>https://www.instagram.com/nail_hyun.__</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3110,7 +3082,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3119,13 +3091,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1852</v>
+        <v>174</v>
       </c>
       <c r="Q29" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
-        <v>1913</v>
+        <v>197</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3134,12 +3106,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1712141242</t>
+          <t>1120708839</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712141242</t>
+          <t>https://m.place.naver.com/place/1120708839</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3156,29 +3128,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>효녀네일</t>
+          <t>바비 네일왁싱</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>hy0d0ng2@naver.com</t>
+          <t>uchka247@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1366-2991</t>
+          <t>0507-1490-9887</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
+          <t>서울특별시 중구 을지로44길 6-9 4층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyonyeo_nail</t>
+          <t>https://www.instagram.com/barbie.waxnail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3213,13 +3185,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>162</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3228,12 +3200,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2038116522</t>
+          <t>1019484164</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038116522</t>
+          <t>https://m.place.naver.com/place/1019484164</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3250,29 +3222,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>엔79 Nail</t>
+          <t>맥스네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>loveucream@naver.com</t>
+          <t>machojj@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1390-0326</t>
+          <t>02-2272-4141</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
+          <t>서울특별시 중구 퇴계로 204 3층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/machojj</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3282,12 +3254,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3303,17 +3275,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>532</v>
       </c>
       <c r="R31" t="n">
-        <v>182</v>
+        <v>730</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3322,12 +3294,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1756267523</t>
+          <t>32786203</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756267523</t>
+          <t>https://m.place.naver.com/place/32786203</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3344,29 +3316,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GK네일 현대시티아울렛 동대문점</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>liziah@naver.com</t>
-        </is>
-      </c>
+          <t>그리다네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1339-5357</t>
+          <t>02-745-8375</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
+          <t>서울특별시 종로구 대학로12길 77</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3376,7 +3344,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3397,17 +3365,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>378</v>
+        <v>23</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3416,12 +3384,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1245812382</t>
+          <t>142708597</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245812382</t>
+          <t>https://m.place.naver.com/place/142708597</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3438,29 +3406,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JIN네일</t>
+          <t>디디 네일바</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jin_nail6453@naver.com</t>
+          <t>heeja090@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1392-5159</t>
+          <t>0507-1476-0228</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
+          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/didi___nailbar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3470,7 +3438,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3491,17 +3459,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="R33" t="n">
-        <v>65</v>
+        <v>213</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3510,12 +3478,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1530291597</t>
+          <t>1134899134</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1530291597</t>
+          <t>https://m.place.naver.com/place/1134899134</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3532,24 +3500,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일로드</t>
+          <t>JIN네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>lordnail@naver.com</t>
+          <t>jin_nail6453@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>02-734-1730</t>
+          <t>0507-1392-5159</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
+          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3589,13 +3557,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3604,12 +3572,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>206289152</t>
+          <t>1530291597</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/206289152</t>
+          <t>https://m.place.naver.com/place/1530291597</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3626,29 +3594,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>꾸밈네일아트</t>
+          <t>GK네일 현대시티아울렛 동대문점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>fusion02@naver.com</t>
+          <t>liziah@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02-733-7942</t>
+          <t>0507-1339-5357</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
+          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3658,7 +3626,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3679,17 +3647,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
-        <v>9</v>
+        <v>378</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3698,12 +3666,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>614593678</t>
+          <t>1245812382</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/614593678</t>
+          <t>https://m.place.naver.com/place/1245812382</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3720,29 +3688,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9층네일 명동점</t>
+          <t>제이뷰티 눈썹&amp;네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dmgktnqls@naver.com</t>
+          <t>jbeauty4022@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1359-1372</t>
+          <t>0507-1422-4022</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 25-1 303호</t>
+          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9.nailstudio</t>
+          <t>https://blog.naver.com/jbeauty4022</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3757,7 +3725,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3777,13 +3745,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>258</v>
+        <v>3316</v>
       </c>
       <c r="Q36" t="n">
-        <v>23</v>
+        <v>227</v>
       </c>
       <c r="R36" t="n">
-        <v>281</v>
+        <v>3543</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3792,12 +3760,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1681308543</t>
+          <t>1776791877</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681308543</t>
+          <t>https://m.place.naver.com/place/1776791877</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3814,29 +3782,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>치즈네일</t>
+          <t>네일바이안</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>43995@naver.com</t>
+          <t>ye1yang@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>02-6405-4578</t>
+          <t>02-511-5621</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
+          <t>서울특별시 중구 남대문로9길 12 8층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheesenail</t>
+          <t>https://www.instagram.com/nailbyahn</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3871,13 +3839,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="R37" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3886,12 +3854,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>37542182</t>
+          <t>1084164588</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37542182</t>
+          <t>https://m.place.naver.com/place/1084164588</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3908,29 +3876,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>혜리앤케어</t>
+          <t>네일문</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>micahyesung@naver.com</t>
+          <t>llkn@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>02-725-1741</t>
+          <t>02-730-0010</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailgate._.mr</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3940,7 +3908,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3961,17 +3929,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3</v>
+        <v>593</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="R38" t="n">
-        <v>3</v>
+        <v>774</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3980,12 +3948,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>155402276</t>
+          <t>13534535</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/155402276</t>
+          <t>https://m.place.naver.com/place/13534535</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4002,29 +3970,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>에이탑네일</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>adw1223@naver.com</t>
-        </is>
-      </c>
+          <t>네일누하</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1372-2148</t>
+          <t>0507-1348-9398</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 12-1 3층</t>
+          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.top_nail</t>
+          <t>https://www.instagram.com/nail.nuha</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4059,13 +4023,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="Q39" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="R39" t="n">
-        <v>327</v>
+        <v>34</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4074,12 +4038,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1446197361</t>
+          <t>1370069746</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446197361</t>
+          <t>https://m.place.naver.com/place/1370069746</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4096,29 +4060,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>루다네일</t>
+          <t>파라테라피네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rudanail1515@naver.com</t>
+          <t>anrgudtkd@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1357-1516</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://instagram.com/rudanail_daehakro</t>
+          <t>http://instagram.com/nail._.again</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4144,7 +4104,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4153,13 +4113,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="Q40" t="n">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>366</v>
+        <v>300</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4168,12 +4128,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>34551572</t>
+          <t>1996157285</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34551572</t>
+          <t>https://m.place.naver.com/place/1996157285</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4190,29 +4150,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>강앤니네일스</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>beczzam@naver.com</t>
-        </is>
-      </c>
+          <t>엘로아네일</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1468-2316</t>
+          <t>0507-1314-9339</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 227-2 4층</t>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://instagram.com/kangannynails</t>
+          <t>https://www.instagram.com/eloa__nail/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,13 +4203,13 @@
         </is>
       </c>
       <c r="P41" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4262,12 +4218,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1711237836</t>
+          <t>2087274322</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1711237836</t>
+          <t>https://m.place.naver.com/place/2087274322</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4284,29 +4240,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>그리드네일</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>boye_like@naver.com</t>
-        </is>
-      </c>
+          <t>네일라이트</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1405-0461</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 44</t>
+          <t>서울특별시 종로구 세종대로23길 5 3층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://instagram.com/love_grid</t>
+          <t>http://instagram.com/_nail_light_</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4341,13 +4289,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>53</v>
+        <v>540</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
-        <v>55</v>
+        <v>546</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4356,12 +4304,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>38531607</t>
+          <t>1105652769</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531607</t>
+          <t>https://m.place.naver.com/place/1105652769</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4378,29 +4326,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일아토</t>
+          <t>너 참 예쁘다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sk3374@naver.com</t>
+          <t>yuiu1401@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1416-6630</t>
+          <t>0507-1434-8892</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ato</t>
+          <t>http://www.instagram.com/youarebeautiful_seoul</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4420,10 +4368,14 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>X</t>
@@ -4435,13 +4387,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>192</v>
+        <v>529</v>
       </c>
       <c r="Q43" t="n">
-        <v>22</v>
+        <v>841</v>
       </c>
       <c r="R43" t="n">
-        <v>214</v>
+        <v>1370</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4450,12 +4402,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1446399532</t>
+          <t>1466732665</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446399532</t>
+          <t>https://m.place.naver.com/place/1466732665</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4472,33 +4424,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>레푸스 종로점</t>
+          <t>르노브네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>refuss_jong_ro@naver.com</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>chy0802@ahasoft.co.kr</t>
-        </is>
-      </c>
+          <t>hshee069@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02-720-4544</t>
+          <t>0507-1307-5439</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
+          <t>서울특별시 종로구 성균관로 38 1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/857013</t>
+          <t>http://pf.kakao.com/_XxbVPn</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4508,7 +4456,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4524,7 +4472,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4533,13 +4481,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>862</v>
+        <v>408</v>
       </c>
       <c r="Q44" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="R44" t="n">
-        <v>1222</v>
+        <v>429</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4548,12 +4496,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1237692187</t>
+          <t>1890443515</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237692187</t>
+          <t>https://m.place.naver.com/place/1890443515</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4570,29 +4518,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>뷰티숲</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>smallwarestore@naver.com</t>
-        </is>
-      </c>
+          <t>종로네일샵</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1438-7477</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 37-29 103호</t>
+          <t>서울특별시 종로구 종로 62</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailsoop_sj/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4602,7 +4542,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4623,17 +4563,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4642,12 +4582,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1158436638</t>
+          <t>1928832758</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158436638</t>
+          <t>https://m.place.naver.com/place/1928832758</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4664,29 +4604,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>빌러브드 네일</t>
+          <t>찰스네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>novembro_12@naver.com</t>
+          <t>spotv_sports@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>02-733-8318</t>
+          <t>0507-1307-4179</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
+          <t>서울특별시 종로구 종로12길 9 3층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beloved_nail_</t>
+          <t>http://www.instagram.com/charles__nail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4721,13 +4661,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>371</v>
+        <v>529</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="R46" t="n">
-        <v>400</v>
+        <v>585</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4736,12 +4676,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>877681682</t>
+          <t>13034248</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/877681682</t>
+          <t>https://m.place.naver.com/place/13034248</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4758,25 +4698,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일라이트</t>
+          <t>바이올렛네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>elegant1025@naver.com</t>
+          <t>violet_nail@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>02-2118-8867</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 5 3층</t>
+          <t>서울특별시 중구 장충단로 247 굿모닝시티 B2 6호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_light_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4786,7 +4730,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4807,17 +4751,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>540</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>546</v>
+        <v>2</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4826,12 +4770,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1105652769</t>
+          <t>120895291</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105652769</t>
+          <t>https://m.place.naver.com/place/120895291</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4848,29 +4792,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>맥스네일</t>
+          <t>뉴문네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>machojj@naver.com</t>
+          <t>xdaredare@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02-2272-4141</t>
+          <t>0507-1354-6577</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 204 3층</t>
+          <t>서울특별시 종로구 성균관로 7 2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/machojj</t>
+          <t>http://instagram.com/newmoonnail_</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4885,7 +4829,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4905,13 +4849,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="Q48" t="n">
-        <v>532</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>730</v>
+        <v>154</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,12 +4864,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>32786203</t>
+          <t>1689136529</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32786203</t>
+          <t>https://m.place.naver.com/place/1689136529</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4942,25 +4886,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>손톱그림</t>
+          <t>마이파우치</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>on_calli@naver.com</t>
+          <t>323redtree@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1402-0809</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
+          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_sketch_8478/</t>
+          <t>https://www.instagram.com/mypouch.kangbbin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4995,13 +4943,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q49" t="n">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="R49" t="n">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5010,12 +4958,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1124095560</t>
+          <t>38642341</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1124095560</t>
+          <t>https://m.place.naver.com/place/38642341</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5032,29 +4980,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>안0네일</t>
+          <t>루다네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ysl6161015@naver.com</t>
+          <t>rudanail1515@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>02-6052-7778</t>
+          <t>0507-1357-1516</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/rudanail_daehakro</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5064,7 +5012,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5080,22 +5028,22 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="R50" t="n">
-        <v>19</v>
+        <v>366</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5104,12 +5052,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1487336161</t>
+          <t>34551572</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487336161</t>
+          <t>https://m.place.naver.com/place/34551572</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5126,29 +5074,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>수야디나 네일&amp;래쉬</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>vastron@naver.com</t>
-        </is>
-      </c>
+          <t>꽁냥네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1305-2499</t>
+          <t>0507-1418-2440</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 중구 충무로 36 2층</t>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yun_ju423/</t>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5183,13 +5127,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>184</v>
+        <v>277</v>
       </c>
       <c r="Q51" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="R51" t="n">
-        <v>216</v>
+        <v>319</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5198,12 +5142,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1324800762</t>
+          <t>1570914826</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324800762</t>
+          <t>https://m.place.naver.com/place/1570914826</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5220,29 +5164,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>바이올렛네일</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>violet_nail@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02-2118-8867</t>
+          <t>0507-1322-4179</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 247 굿모닝시티 B2 6호</t>
+          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sdED0A2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5252,7 +5196,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5268,22 +5212,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>249</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R52" t="n">
-        <v>2</v>
+        <v>264</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5292,12 +5236,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>120895291</t>
+          <t>1054499609</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/120895291</t>
+          <t>https://m.place.naver.com/place/1054499609</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5314,29 +5258,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>루아르블랑 네일</t>
+          <t>네일브러쉬</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>failuredw@naver.com</t>
+          <t>ss7370306@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1483-9411</t>
+          <t>0507-1332-0306</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
+          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHajSJei</t>
+          <t>https://blog.naver.com/ss7370306</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5351,7 +5295,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5362,22 +5306,22 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="Q53" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="R53" t="n">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5386,12 +5330,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2013893243</t>
+          <t>35559430</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013893243</t>
+          <t>https://m.place.naver.com/place/35559430</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5408,24 +5352,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>드로잉쇼</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>odshow@naver.com</t>
-        </is>
-      </c>
+          <t>네일해요</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>02-777-1090</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 60</t>
+          <t>서울특별시 종로구 종로44길 9 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5465,13 +5401,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5480,12 +5416,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1726036993</t>
+          <t>1213168091</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726036993</t>
+          <t>https://m.place.naver.com/place/1213168091</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5502,29 +5438,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>찰스네일</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>spotv_sports@naver.com</t>
-        </is>
-      </c>
+          <t>명동네일 제니뷰티</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1307-4179</t>
+          <t>0507-1487-9603</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로12길 9 3층</t>
+          <t>서울특별시 중구 명동8길 43 3층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/charles__nail</t>
+          <t>https://www.instagram.com/jennybeauty.md/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5559,13 +5491,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>529</v>
+        <v>48</v>
       </c>
       <c r="Q55" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>585</v>
+        <v>48</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5574,12 +5506,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13034248</t>
+          <t>1845062262</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13034248</t>
+          <t>https://m.place.naver.com/place/1845062262</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5596,39 +5528,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>아따걸네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>addagirl2@naver.com</t>
-        </is>
-      </c>
+          <t>네일 김미쉘터</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1328-8505</t>
+          <t>0507-1320-1993</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
+          <t>서울특별시 종로구 필운대로 55</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_GWaij</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5644,22 +5572,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="Q56" t="n">
-        <v>649</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>934</v>
+        <v>271</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5668,12 +5596,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>13047890</t>
+          <t>1802694964</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13047890</t>
+          <t>https://m.place.naver.com/place/1802694964</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5690,25 +5618,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>파라테라피네일</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>anrgudtkd@naver.com</t>
-        </is>
-      </c>
+          <t>나비네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>02-319-7844</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
+          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail._.again</t>
+          <t>http://instagram.com/navinailnavinail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5743,13 +5671,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>291</v>
+        <v>26</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>300</v>
+        <v>28</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5758,12 +5686,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1996157285</t>
+          <t>735546684</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996157285</t>
+          <t>https://m.place.naver.com/place/735546684</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5780,25 +5708,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>리라뷰티</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>rira_225@naver.com</t>
-        </is>
-      </c>
+          <t>네일멜로우</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1356-7672</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lira_4994/</t>
+          <t>https://www.instagram.com/nail_mellow_11/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5833,13 +5761,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>122</v>
+        <v>389</v>
       </c>
       <c r="Q58" t="n">
-        <v>277</v>
+        <v>34</v>
       </c>
       <c r="R58" t="n">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5848,12 +5776,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1100664846</t>
+          <t>1933958367</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100664846</t>
+          <t>https://m.place.naver.com/place/1933958367</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5870,29 +5798,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>너 참 예쁘다</t>
+          <t>네일원</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>yuiu1401@naver.com</t>
+          <t>nail_one@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1434-8892</t>
+          <t>0507-1338-0475</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
+          <t>서울특별시 종로구 지봉로 52-1 2층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/youarebeautiful_seoul</t>
+          <t>http://instagram.com/_nail_one</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5912,14 +5840,10 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>X</t>
@@ -5931,13 +5855,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>529</v>
+        <v>3</v>
       </c>
       <c r="Q59" t="n">
-        <v>841</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>1370</v>
+        <v>4</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5946,12 +5870,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1466732665</t>
+          <t>1105911364</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466732665</t>
+          <t>https://m.place.naver.com/place/1105911364</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5968,29 +5892,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일해썸</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>llllcmalll@naver.com</t>
-        </is>
-      </c>
+          <t>네일블라썸</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1342-3168</t>
+          <t>0507-1347-8173</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
+          <t>서울특별시 중구 소공로 102 95호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hatssome</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6000,7 +5920,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6016,22 +5936,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>86</v>
+        <v>333</v>
       </c>
       <c r="Q60" t="n">
         <v>10</v>
       </c>
       <c r="R60" t="n">
-        <v>96</v>
+        <v>343</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6040,12 +5960,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1991633917</t>
+          <t>1794862527</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991633917</t>
+          <t>https://m.place.naver.com/place/1794862527</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6062,29 +5982,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>블링네일 종로점</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>beaulynail@naver.com</t>
-        </is>
-      </c>
+          <t>에이커뷰티네일</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1448-0036</t>
+          <t>02-722-5558</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 16-1 1층</t>
+          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beaulynail</t>
+          <t>http://instagram.com/acre_beauty</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6099,7 +6015,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6119,13 +6035,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="Q61" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="R61" t="n">
-        <v>216</v>
+        <v>121</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6134,12 +6050,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>60890323</t>
+          <t>1812848399</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60890323</t>
+          <t>https://m.place.naver.com/place/1812848399</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6156,29 +6072,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>뉴문네일</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>xdaredare@naver.com</t>
-        </is>
-      </c>
+          <t>영심이손톱</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1354-6577</t>
+          <t>02-735-0031</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 7 2층</t>
+          <t>서울특별시 종로구 종로 88 701호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://instagram.com/newmoonnail_</t>
+          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6213,13 +6125,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6228,12 +6140,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1689136529</t>
+          <t>1116851430</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689136529</t>
+          <t>https://m.place.naver.com/place/1116851430</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6250,34 +6162,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>르노브네일</t>
+          <t>위치네일스 종로점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>hshee069@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1307-5439</t>
+          <t>0507-1364-9020</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 38 1층</t>
+          <t>서울특별시 종로구 종로 51</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XxbVPn</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6287,7 +6199,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6298,7 +6210,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6307,13 +6219,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>408</v>
+        <v>1061</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="R63" t="n">
-        <v>429</v>
+        <v>1210</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6322,12 +6234,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1890443515</t>
+          <t>1543496206</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1890443515</t>
+          <t>https://m.place.naver.com/place/1543496206</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6344,29 +6256,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>라라네일</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>redpepper30@naver.com</t>
-        </is>
-      </c>
+          <t>네일스토리</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1344-7250</t>
+          <t>02-765-5525</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+          <t>서울특별시 종로구 지봉로 53-1 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lalanail_myeongdong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6376,7 +6284,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6397,17 +6305,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1001</v>
+        <v>7</v>
       </c>
       <c r="Q64" t="n">
-        <v>431</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>1432</v>
+        <v>10</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6416,12 +6324,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1303128966</t>
+          <t>34352879</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303128966</t>
+          <t>https://m.place.naver.com/place/34352879</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6438,29 +6346,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일 김미쉘터</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>patent37435@naver.com</t>
-        </is>
-      </c>
+          <t>치즈네일</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1320-1993</t>
+          <t>02-6405-4578</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 55</t>
+          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cheesenail</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6470,7 +6374,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6491,17 +6395,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>267</v>
+        <v>57</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>271</v>
+        <v>58</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6510,12 +6414,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1802694964</t>
+          <t>37542182</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802694964</t>
+          <t>https://m.place.naver.com/place/37542182</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6532,29 +6436,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일바이안</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>ye1yang@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티숲</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>02-511-5621</t>
+          <t>0507-1438-7477</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로9길 12 8층</t>
+          <t>서울특별시 종로구 지봉로 37-29 103호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyahn</t>
+          <t>https://www.instagram.com/nailsoop_sj/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6589,13 +6489,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q66" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6604,12 +6504,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1084164588</t>
+          <t>1158436638</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084164588</t>
+          <t>https://m.place.naver.com/place/1158436638</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6626,29 +6526,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일멜로우</t>
+          <t>폭시네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sc09mc@naver.com</t>
+          <t>tomebooy@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1356-7672</t>
+          <t>0507-1403-4791</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
+          <t>서울특별시 종로구 동망산길 13 2층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mellow_11/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6658,7 +6558,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6679,17 +6579,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>389</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>423</v>
+        <v>2</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6698,12 +6598,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1933958367</t>
+          <t>40986070</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933958367</t>
+          <t>https://m.place.naver.com/place/40986070</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6720,12 +6620,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>페이브 네일 스튜디오</t>
+          <t>해피네일데이</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ekdmaekfdpqnwk@naver.com</t>
+          <t>happynailday@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -6733,12 +6633,12 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
+          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sUKlei7f</t>
+          <t>https://blog.naver.com/happynailday</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6753,7 +6653,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6764,7 +6664,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6773,13 +6673,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="Q68" t="n">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="R68" t="n">
-        <v>96</v>
+        <v>353</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6788,12 +6688,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1109114407</t>
+          <t>298136226</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109114407</t>
+          <t>https://m.place.naver.com/place/298136226</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6810,29 +6710,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nail by Jade</t>
+          <t>올리브네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>djdjqq1663@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1360-1011</t>
+          <t>02-2075-7775</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
+          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_by_jade</t>
+          <t>https://blog.naver.com/djdjqq1663</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6847,7 +6747,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6858,7 +6758,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6867,13 +6767,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>27</v>
+        <v>3105</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>253</v>
       </c>
       <c r="R69" t="n">
-        <v>28</v>
+        <v>3358</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6882,12 +6782,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>944614599</t>
+          <t>35751284</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/944614599</t>
+          <t>https://m.place.naver.com/place/35751284</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6904,25 +6804,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일, 사월</t>
+          <t>굿모닝네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>pooddin@naver.com</t>
+          <t>clsrn9606@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1400-8607</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__april</t>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6948,7 +6852,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6957,13 +6861,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>644</v>
+        <v>241</v>
       </c>
       <c r="Q70" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R70" t="n">
-        <v>658</v>
+        <v>247</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6972,12 +6876,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1448977317</t>
+          <t>13051690</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448977317</t>
+          <t>https://m.place.naver.com/place/13051690</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6994,29 +6898,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일리</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>ysbfly@naver.com</t>
-        </is>
-      </c>
+          <t>드로잉쇼</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1358-8653</t>
+          <t>02-777-1090</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+          <t>서울특별시 중구 남대문로 60</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lee____</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7026,7 +6926,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7047,17 +6947,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Q71" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R71" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7066,12 +6966,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2065943871</t>
+          <t>1726036993</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065943871</t>
+          <t>https://m.place.naver.com/place/1726036993</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7088,29 +6988,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일문</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>llkn@naver.com</t>
-        </is>
-      </c>
+          <t>9층네일 명동점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>02-730-0010</t>
+          <t>0507-1359-1372</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgate._.mr</t>
+          <t>https://www.instagram.com/9.nailstudio</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7145,13 +7041,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>593</v>
+        <v>258</v>
       </c>
       <c r="Q72" t="n">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="R72" t="n">
-        <v>774</v>
+        <v>281</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7160,12 +7056,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>13534535</t>
+          <t>1681308543</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13534535</t>
+          <t>https://m.place.naver.com/place/1681308543</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7182,29 +7078,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일블라썸</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>wilklove@naver.com</t>
-        </is>
-      </c>
+          <t>다리아네일 안국역</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1347-8173</t>
+          <t>0507-1347-1494</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 95호</t>
+          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/daria_nail_ssu</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7214,7 +7106,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7235,17 +7127,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>333</v>
+        <v>184</v>
       </c>
       <c r="Q73" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>343</v>
+        <v>186</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,12 +7146,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1794862527</t>
+          <t>1165184706</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794862527</t>
+          <t>https://m.place.naver.com/place/1165184706</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7276,24 +7168,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>폭시네일</t>
+          <t>혜리앤케어</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>tomebooy@naver.com</t>
+          <t>micahyesung@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1403-4791</t>
+          <t>02-725-1741</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동망산길 13 2층</t>
+          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7333,13 +7225,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7348,12 +7240,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>40986070</t>
+          <t>155402276</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/40986070</t>
+          <t>https://m.place.naver.com/place/155402276</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7370,29 +7262,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>제이뷰티 눈썹&amp;네일</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>jbeauty4022@naver.com</t>
-        </is>
-      </c>
+          <t>네일 오우브</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1422-4022</t>
+          <t>0507-1407-0437</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
+          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jbeauty4022</t>
+          <t>https://www.instagram.com/nail.ouv</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7407,7 +7295,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7427,13 +7315,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3315</v>
+        <v>154</v>
       </c>
       <c r="Q75" t="n">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>3542</v>
+        <v>155</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7442,12 +7330,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1776791877</t>
+          <t>1559030900</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776791877</t>
+          <t>https://m.place.naver.com/place/1559030900</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7464,29 +7352,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>다리아네일 안국역</t>
+          <t>네일온 명동본점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>puppyholic@naver.com</t>
+          <t>nailon_myeongdong@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1347-1494</t>
+          <t>0507-1302-8995</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
+          <t>서울특별시 중구 을지로 88 을특8호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daria_nail_ssu</t>
+          <t>https://blog.naver.com/nailon_myeongdong</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7501,7 +7389,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7521,13 +7409,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R76" t="n">
-        <v>186</v>
+        <v>39</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7536,12 +7424,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1165184706</t>
+          <t>2054691209</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165184706</t>
+          <t>https://m.place.naver.com/place/2054691209</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7558,29 +7446,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일 오우브</t>
+          <t>릴리엔젤네일</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>keroo90@naver.com</t>
+          <t>kiyu0987@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0507-1407-0437</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
+          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.ouv</t>
+          <t>http://instagram.com/lilyangel_nail</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7615,13 +7499,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="R77" t="n">
-        <v>155</v>
+        <v>287</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7630,12 +7514,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1559030900</t>
+          <t>1110775717</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559030900</t>
+          <t>https://m.place.naver.com/place/1110775717</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7652,29 +7536,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>르모네일스튜디오</t>
+          <t>강앤니네일스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>borareview@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1374-9858</t>
+          <t>0507-1468-2316</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동숭4가길 2 2층</t>
+          <t>서울특별시 중구 장충단로 227-2 4층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>http://instagram.com/_lmonail</t>
+          <t>http://instagram.com/kangannynails</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7709,13 +7593,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7724,12 +7608,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1493224095</t>
+          <t>1711237836</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493224095</t>
+          <t>https://m.place.naver.com/place/1711237836</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7746,29 +7630,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>네일브러쉬</t>
+          <t>오브 코코네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ss7370306@naver.com</t>
+          <t>9ansapres@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1332-0306</t>
+          <t>0507-1371-8921</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
+          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ss7370306</t>
+          <t>https://www.instagram.com/ofconail</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7783,7 +7667,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7799,17 +7683,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>65</v>
+        <v>660</v>
       </c>
       <c r="Q79" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="R79" t="n">
-        <v>79</v>
+        <v>707</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7818,12 +7702,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>35559430</t>
+          <t>1009626425</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35559430</t>
+          <t>https://m.place.naver.com/place/1009626425</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7840,34 +7724,34 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>네일쏘이</t>
+          <t>아따걸네일</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>addagirl2@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1334-9677</t>
+          <t>0507-1328-8505</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailssoi_</t>
+          <t>https://pf.kakao.com/_GWaij</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7888,7 +7772,7 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7897,13 +7781,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>55</v>
+        <v>285</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="R80" t="n">
-        <v>55</v>
+        <v>934</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7912,12 +7796,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1009120766</t>
+          <t>13047890</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009120766</t>
+          <t>https://m.place.naver.com/place/13047890</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7934,20 +7818,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>오프엠네일</t>
+          <t>안0네일</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>hgy___g@naver.com</t>
+          <t>ysl6161015@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>02-6052-7778</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 40 4층</t>
+          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7987,13 +7875,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="Q81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8002,12 +7890,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>2099192808</t>
+          <t>1487336161</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099192808</t>
+          <t>https://m.place.naver.com/place/1487336161</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8024,29 +7912,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>블링네일 종로점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>beaulynail@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>02-765-5525</t>
+          <t>0507-1448-0036</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 53-1 1층</t>
+          <t>서울특별시 종로구 대학로 16-1 1층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/beaulynail</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8056,12 +7944,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8077,17 +7965,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>7</v>
+        <v>143</v>
       </c>
       <c r="Q82" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="R82" t="n">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8096,12 +7984,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>34352879</t>
+          <t>60890323</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34352879</t>
+          <t>https://m.place.naver.com/place/60890323</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8118,29 +8006,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>바움네일</t>
+          <t>아셀네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>harulov@naver.com</t>
+          <t>asher9809@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0507-1330-3151</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로9길 37 2층</t>
+          <t>서울특별시 중구 장충단로 253 10층 11호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/baum_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8150,7 +8034,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8171,17 +8055,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>560</v>
+        <v>59</v>
       </c>
       <c r="Q83" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="R83" t="n">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8190,12 +8074,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1954514000</t>
+          <t>1229434440</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954514000</t>
+          <t>https://m.place.naver.com/place/1229434440</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8212,29 +8096,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>핸더뷰티</t>
+          <t>삼층네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>koenji_nail@naver.com</t>
+          <t>wang8241@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1380-1146</t>
+          <t>0507-1327-8241</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/koenji_nail</t>
+          <t>https://blog.naver.com/wang8241</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8265,17 +8149,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>357</v>
+        <v>531</v>
       </c>
       <c r="Q84" t="n">
-        <v>412</v>
+        <v>13</v>
       </c>
       <c r="R84" t="n">
-        <v>769</v>
+        <v>544</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8284,12 +8168,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>37558905</t>
+          <t>1894370134</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37558905</t>
+          <t>https://m.place.naver.com/place/1894370134</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8306,29 +8190,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>나비네일</t>
+          <t>효녀네일</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jytgh@naver.com</t>
+          <t>hy0d0ng2@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>02-319-7844</t>
+          <t>0507-1366-2991</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
+          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>http://instagram.com/navinailnavinail</t>
+          <t>https://www.instagram.com/hyonyeo_nail</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8363,13 +8247,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="Q85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8378,12 +8262,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>735546684</t>
+          <t>2038116522</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/735546684</t>
+          <t>https://m.place.naver.com/place/2038116522</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8400,29 +8284,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>리빈네일</t>
+          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jcj0217@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1349-9808</t>
+          <t>02-756-4143</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
+          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rivin_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8432,7 +8316,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8453,17 +8337,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="Q86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8472,12 +8356,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1315671750</t>
+          <t>31315234</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315671750</t>
+          <t>https://m.place.naver.com/place/31315234</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8494,29 +8378,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>에이커뷰티네일</t>
+          <t>르모네일스튜디오</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>happymin_life@naver.com</t>
+          <t>borareview@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>02-722-5558</t>
+          <t>0507-1374-9858</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
+          <t>서울특별시 종로구 동숭4가길 2 2층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>http://instagram.com/acre_beauty</t>
+          <t>http://instagram.com/_lmonail</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8551,13 +8435,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="Q87" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R87" t="n">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8566,12 +8450,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1812848399</t>
+          <t>1493224095</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1812848399</t>
+          <t>https://m.place.naver.com/place/1493224095</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8588,29 +8472,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>안젤라네일샵</t>
+          <t>페이브 네일 스튜디오</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>angella3977@naver.com</t>
+          <t>ekdmaekfdpqnwk@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0507-1493-3335</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/angella3977</t>
+          <t>https://open.kakao.com/o/sUKlei7f</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8625,7 +8505,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8636,7 +8516,7 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8645,13 +8525,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>664</v>
+        <v>63</v>
       </c>
       <c r="Q88" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="R88" t="n">
-        <v>676</v>
+        <v>96</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8660,12 +8540,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1274163754</t>
+          <t>1109114407</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274163754</t>
+          <t>https://m.place.naver.com/place/1109114407</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8682,29 +8562,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>오브 코코네일</t>
+          <t>모스네일</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9ansapres@naver.com</t>
+          <t>buzzerrbeate@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0507-1371-8921</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
+          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ofconail</t>
+          <t>https://www.instagram.com/moss.nail_</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8730,7 +8606,7 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8739,13 +8615,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>659</v>
+        <v>227</v>
       </c>
       <c r="Q89" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="R89" t="n">
-        <v>706</v>
+        <v>240</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8754,12 +8630,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1009626425</t>
+          <t>1061088069</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009626425</t>
+          <t>https://m.place.naver.com/place/1061088069</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8776,30 +8652,34 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>이츠네일</t>
+          <t>베리네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>icacc89@naver.com</t>
+          <t>yeonee09@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1419-6623</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
+          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_duxhxdn</t>
+          <t>https://www.instagram.com/berry_nail_</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8820,7 +8700,7 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8829,13 +8709,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="Q90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R90" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8844,12 +8724,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>31949587</t>
+          <t>1394925944</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31949587</t>
+          <t>https://m.place.naver.com/place/1394925944</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8866,29 +8746,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
+          <t>빌러브드 네일</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>novembro_12@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>02-756-4143</t>
+          <t>02-733-8318</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
+          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/beloved_nail_</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8898,7 +8778,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8919,17 +8799,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4</v>
+        <v>371</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R91" t="n">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8938,12 +8818,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>31315234</t>
+          <t>877681682</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315234</t>
+          <t>https://m.place.naver.com/place/877681682</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8960,34 +8840,34 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>드네일 광화문점</t>
+          <t>프로뷰티</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>dahaeyoo@naver.com</t>
+          <t>probeauty_blog@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1351-9192</t>
+          <t>0507-1435-2789</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
+          <t>서울특별시 중구 명동8가길 9 3층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
+          <t>https://blog.naver.com/probeauty_blog</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9017,13 +8897,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>20</v>
+        <v>571</v>
       </c>
       <c r="Q92" t="n">
-        <v>17</v>
+        <v>679</v>
       </c>
       <c r="R92" t="n">
-        <v>37</v>
+        <v>1250</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9032,12 +8912,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1372444756</t>
+          <t>19997455</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1372444756</t>
+          <t>https://m.place.naver.com/place/19997455</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9054,29 +8934,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>키튼네일</t>
+          <t>Diamond Nails</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>dbgpwn0626@naver.com</t>
+          <t>ksj673232@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>02-765-8566</t>
+          <t>0507-1420-1393</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
+          <t>서울특별시 중구 마른내로 155 1동 102호</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
+          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9111,13 +8991,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>546</v>
+        <v>0</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9126,12 +9006,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1065031131</t>
+          <t>2040524360</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065031131</t>
+          <t>https://m.place.naver.com/place/2040524360</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9148,29 +9028,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>디디 네일바</t>
+          <t>네일해썸</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>heeja090@naver.com</t>
+          <t>llllcmalll@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1476-0228</t>
+          <t>0507-1342-3168</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
+          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/didi___nailbar</t>
+          <t>https://www.instagram.com/nail_hatssome</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9196,7 +9076,7 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9205,13 +9085,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="Q94" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="R94" t="n">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9220,12 +9100,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1134899134</t>
+          <t>1991633917</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134899134</t>
+          <t>https://m.place.naver.com/place/1991633917</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9242,25 +9122,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>꾸미다</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>yem1104@naver.com</t>
-        </is>
-      </c>
+          <t>비조네일</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
+          <t>서울특별시 종로구 종로 379</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9270,7 +9146,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9291,17 +9167,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P95" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>3</v>
-      </c>
       <c r="R95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9310,12 +9186,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1095499576</t>
+          <t>19813956</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095499576</t>
+          <t>https://m.place.naver.com/place/19813956</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9332,29 +9208,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>드팜므</t>
+          <t>살롱드벨르네일</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>tomjelbbuu@naver.com</t>
+          <t>salondebelle_nail@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>0507-1317-3395</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 42 B110호</t>
+          <t>서울특별시 종로구 종로 65 2층 208호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/defemmeeee</t>
+          <t>https://blog.naver.com/salondebelle_nail</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9369,7 +9241,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9389,13 +9261,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>75</v>
+        <v>357</v>
       </c>
       <c r="Q96" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="R96" t="n">
-        <v>145</v>
+        <v>418</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9404,12 +9276,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1741921081</t>
+          <t>1768571536</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1741921081</t>
+          <t>https://m.place.naver.com/place/1768571536</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9426,25 +9298,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>비조네일</t>
+          <t>드팜므</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>shoot13445@naver.com</t>
+          <t>tomjelbbuu@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1317-3395</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 379</t>
+          <t>서울특별시 종로구 사직로8길 42 B110호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/defemmeeee</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9454,7 +9330,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9475,17 +9351,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="Q97" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9494,12 +9370,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>19813956</t>
+          <t>1741921081</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19813956</t>
+          <t>https://m.place.naver.com/place/1741921081</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9516,29 +9392,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>마이파우치</t>
+          <t>오토젯네일</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>323redtree@naver.com</t>
+          <t>yr19850217@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>0507-1402-0809</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
+          <t>서울특별시 종로구 돈화문로 68</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mypouch.kangbbin</t>
+          <t>http://www.autoznail.com/</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9569,17 +9441,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9588,12 +9460,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>38642341</t>
+          <t>35506860</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38642341</t>
+          <t>https://m.place.naver.com/place/35506860</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9610,25 +9482,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>해피네일데이</t>
+          <t>네일하루</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>happynailday@naver.com</t>
+          <t>nail_haru@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1361-1445</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
+          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/happynailday</t>
+          <t>https://blog.naver.com/nail_haru</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9659,17 +9535,17 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>166</v>
+        <v>67</v>
       </c>
       <c r="Q99" t="n">
-        <v>184</v>
+        <v>346</v>
       </c>
       <c r="R99" t="n">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9678,12 +9554,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>298136226</t>
+          <t>37089409</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/298136226</t>
+          <t>https://m.place.naver.com/place/37089409</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9700,29 +9576,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>네일원</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>nail_one@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1338-0475</t>
+          <t>02-722-1384</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 52-1 2층</t>
+          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_one</t>
+          <t>https://www.instagram.com/audreynail_official</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9748,7 +9624,7 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -9757,13 +9633,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3</v>
+        <v>228</v>
       </c>
       <c r="Q100" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="R100" t="n">
-        <v>4</v>
+        <v>484</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9772,12 +9648,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1105911364</t>
+          <t>13450587</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105911364</t>
+          <t>https://m.place.naver.com/place/13450587</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9794,29 +9670,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>네일하트</t>
+          <t>지아네일</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>nailheart053@naver.com</t>
+          <t>jjaa1334@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>0507-1484-8604</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+          <t>서울특별시 중구 명동10길 40 6층</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jeonjia9</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9826,7 +9698,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9847,17 +9719,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>373</v>
+        <v>65</v>
       </c>
       <c r="Q101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R101" t="n">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9866,12 +9738,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1101101042</t>
+          <t>1279897442</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101101042</t>
+          <t>https://m.place.naver.com/place/1279897442</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -9888,29 +9760,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>말짜네일 광화문점</t>
+          <t>어나더네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>malzzanail@naver.com</t>
+          <t>soojinpo@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>0507-1402-3734</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
+          <t>서울특별시 종로구 지봉로 56-1 1층</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/malzzanail</t>
+          <t>https://www.instagram.com/another_n_ail</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9925,7 +9793,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9936,7 +9804,7 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9945,13 +9813,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>305</v>
+        <v>58</v>
       </c>
       <c r="Q102" t="n">
-        <v>424</v>
+        <v>11</v>
       </c>
       <c r="R102" t="n">
-        <v>729</v>
+        <v>69</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9960,12 +9828,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>37997776</t>
+          <t>1214193406</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37997776</t>
+          <t>https://m.place.naver.com/place/1214193406</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -9982,25 +9850,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>네일해요</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>elliestar@naver.com</t>
-        </is>
-      </c>
+          <t>드네일 광화문점</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1351-9192</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로44길 9 2층</t>
+          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10010,7 +9878,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10031,17 +9899,17 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R103" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10050,12 +9918,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1213168091</t>
+          <t>1372444756</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213168091</t>
+          <t>https://m.place.naver.com/place/1372444756</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -10072,29 +9940,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>네일온 명동본점</t>
+          <t>무아네일</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>nailon_myeongdong@naver.com</t>
+          <t>loowowool@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1302-8995</t>
+          <t>0507-1436-1716</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 을특8호</t>
+          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon_myeongdong</t>
+          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10109,7 +9977,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -10129,13 +9997,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10144,12 +10012,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>2054691209</t>
+          <t>2038424794</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054691209</t>
+          <t>https://m.place.naver.com/place/2038424794</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10166,29 +10034,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>엘로아네일</t>
+          <t>가빈네일</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>hhhong88@naver.com</t>
+          <t>happyhannj@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1314-9339</t>
+          <t>0507-1431-8259</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eloa__nail/</t>
+          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10223,13 +10091,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R105" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10238,12 +10106,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>2087274322</t>
+          <t>38500996</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087274322</t>
+          <t>https://m.place.naver.com/place/38500996</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10260,34 +10128,34 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>아머네일</t>
+          <t>바움네일</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>dntndus111@naver.com</t>
+          <t>harulov@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1364-4429</t>
+          <t>0507-1330-3151</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
+          <t>서울특별시 종로구 대학로9길 37 2층</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_pzkMG</t>
+          <t>https://www.instagram.com/baum_nail</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10308,7 +10176,7 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -10317,13 +10185,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>262</v>
+        <v>560</v>
       </c>
       <c r="Q106" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="R106" t="n">
-        <v>359</v>
+        <v>607</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10332,12 +10200,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1312237193</t>
+          <t>1954514000</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312237193</t>
+          <t>https://m.place.naver.com/place/1954514000</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10354,29 +10222,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>오드리네일</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>ardusy@naver.com</t>
-        </is>
-      </c>
+          <t>네일쏘이</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>02-722-1384</t>
+          <t>0507-1334-9677</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
+          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreynail_official</t>
+          <t>https://www.instagram.com/nailssoi_</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10402,7 +10266,7 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -10411,13 +10275,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>228</v>
+        <v>55</v>
       </c>
       <c r="Q107" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>484</v>
+        <v>55</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10426,12 +10290,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>13450587</t>
+          <t>1009120766</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13450587</t>
+          <t>https://m.place.naver.com/place/1009120766</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10448,29 +10312,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>네일 을지로지하쇼핑센터3구역점</t>
+          <t>리라뷰티</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>rira_225@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>02-2278-2990</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lira_4994/</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10480,7 +10340,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10501,17 +10361,17 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="Q108" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
       <c r="R108" t="n">
-        <v>6</v>
+        <v>399</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10520,12 +10380,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>37588249</t>
+          <t>1100664846</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588249</t>
+          <t>https://m.place.naver.com/place/1100664846</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10542,39 +10402,35 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>그리다네일</t>
+          <t>네일지니</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>gridanail2@naver.com</t>
+          <t>1231yc@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>02-745-8375</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로12길 77</t>
+          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xeTiCG</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -10590,22 +10446,22 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>20</v>
+        <v>1777</v>
       </c>
       <c r="Q109" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="R109" t="n">
-        <v>23</v>
+        <v>1871</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10614,12 +10470,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>142708597</t>
+          <t>1073291540</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142708597</t>
+          <t>https://m.place.naver.com/place/1073291540</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10636,20 +10492,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>네일&amp;페일아트</t>
+          <t>네일로드</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>lsbangel@naver.com</t>
+          <t>lordnail@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>02-734-1730</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 446</t>
+          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10689,13 +10549,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10704,12 +10564,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>20871402</t>
+          <t>206289152</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20871402</t>
+          <t>https://m.place.naver.com/place/206289152</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10726,29 +10586,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>위치네일스 종로점</t>
+          <t>에이탑네일</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>adw1223@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1364-9020</t>
+          <t>0507-1372-2148</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 51</t>
+          <t>서울특별시 중구 명동4길 12-1 3층</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>https://www.instagram.com/a.top_nail</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10763,7 +10623,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -10783,13 +10643,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1061</v>
+        <v>260</v>
       </c>
       <c r="Q111" t="n">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="R111" t="n">
-        <v>1210</v>
+        <v>328</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10798,12 +10658,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1543496206</t>
+          <t>1446197361</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543496206</t>
+          <t>https://m.place.naver.com/place/1446197361</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10820,34 +10680,34 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>kikiu30@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0507-1322-4179</t>
+          <t>0507-1378-0246</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
+          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sdED0A2</t>
+          <t>http://pf.kakao.com/_pAtmG</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10877,13 +10737,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>249</v>
+        <v>1854</v>
       </c>
       <c r="Q112" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="R112" t="n">
-        <v>264</v>
+        <v>1915</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10892,12 +10752,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1054499609</t>
+          <t>1712141242</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054499609</t>
+          <t>https://m.place.naver.com/place/1712141242</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10914,34 +10774,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>루이비네일</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>zhengyinji888@naver.com</t>
-        </is>
-      </c>
+          <t>아트만네일</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0507-1445-2047</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>http://instagram.com/luyibi_nail8</t>
+          <t>http://pf.kakao.com/_Txkxgfxj</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10962,7 +10814,7 @@
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -10971,13 +10823,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>481</v>
+        <v>16</v>
       </c>
       <c r="Q113" t="n">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="R113" t="n">
-        <v>570</v>
+        <v>36</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10986,12 +10838,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>21306056</t>
+          <t>1284929161</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21306056</t>
+          <t>https://m.place.naver.com/place/1284929161</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -11008,25 +10860,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>살롱드벨르네일</t>
+          <t>nail by Jade</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>salondebelle_nail@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0507-1360-1011</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 65 2층 208호</t>
+          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/salondebelle_nail</t>
+          <t>http://www.instagram.com/nail_by_jade</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11041,7 +10897,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -11061,13 +10917,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>355</v>
+        <v>27</v>
       </c>
       <c r="Q114" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>416</v>
+        <v>28</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11076,12 +10932,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1768571536</t>
+          <t>944614599</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768571536</t>
+          <t>https://m.place.naver.com/place/944614599</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">

--- a/naver-place-crawler/results_nail/종로_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/종로_네일샵.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>네일아토</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>sk3374@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02-765-5525</t>
+          <t>0507-1416-6630</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 53-1 1층</t>
+          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_ato</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>192</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>214</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>34352879</t>
+          <t>1446399532</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34352879</t>
+          <t>https://m.place.naver.com/place/1446399532</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>수야디나 네일&amp;래쉬</t>
+          <t>라라네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bbbbaiyunzhu@naver.com</t>
+          <t>redpepper30@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1305-2499</t>
+          <t>0507-1344-7250</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 중구 충무로 36 2층</t>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wce1zr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>184</v>
+        <v>1004</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>433</v>
       </c>
       <c r="R3" t="n">
-        <v>216</v>
+        <v>1437</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1324800762</t>
+          <t>1303128966</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324800762</t>
+          <t>https://m.place.naver.com/place/1303128966</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>키튼네일</t>
+          <t>효녀네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dbgpwn0626@naver.com</t>
+          <t>hy0d0ng2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-765-8566</t>
+          <t>0507-1366-2991</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
+          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hyonyeo_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>502</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>556</v>
+        <v>4</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1065031131</t>
+          <t>2038116522</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065031131</t>
+          <t>https://m.place.naver.com/place/2038116522</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,39 +846,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>너 참 예쁘다</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yuiu1401@naver.com</t>
+          <t>kikiu30@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1434-8892</t>
+          <t>0507-1378-0246</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
+          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_pAtmG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -892,17 +888,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4z4qd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -911,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>529</v>
+        <v>1857</v>
       </c>
       <c r="Q5" t="n">
-        <v>842</v>
+        <v>61</v>
       </c>
       <c r="R5" t="n">
-        <v>1371</v>
+        <v>1918</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1466732665</t>
+          <t>1712141242</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466732665</t>
+          <t>https://m.place.naver.com/place/1712141242</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>말짜네일 광화문점</t>
+          <t>GK네일 현대시티아울렛 동대문점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>malzzanail@naver.com</t>
+          <t>liziah@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-3734</t>
+          <t>0507-1339-5357</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
+          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,17 +982,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3yrwzm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="Q6" t="n">
-        <v>424</v>
+        <v>46</v>
       </c>
       <c r="R6" t="n">
-        <v>730</v>
+        <v>379</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37997776</t>
+          <t>1245812382</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37997776</t>
+          <t>https://m.place.naver.com/place/1245812382</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,24 +1034,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일,현</t>
+          <t>오프엠네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>qkrwlsk126@naver.com</t>
+          <t>ttmoong@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1316-0133</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
+          <t>서울특별시 중구 명동4길 40 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1088,14 +1072,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdslomu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1103,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>197</v>
+        <v>111</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1120708839</t>
+          <t>2099192808</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120708839</t>
+          <t>https://m.place.naver.com/place/2099192808</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1144,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일하루</t>
+          <t>네일바이안</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nail_haru@naver.com</t>
+          <t>ye1yang@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1361-1445</t>
+          <t>02-511-5621</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
+          <t>서울특별시 중구 남대문로9길 12 8층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailbyahn</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1186,14 +1166,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9xdn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1201,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Q8" t="n">
-        <v>346</v>
+        <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>413</v>
+        <v>102</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37089409</t>
+          <t>1084164588</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37089409</t>
+          <t>https://m.place.naver.com/place/1084164588</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>명동네일 제니뷰티</t>
+          <t>찰스네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hyoyeol@naver.com</t>
+          <t>spotv_sports@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-9603</t>
+          <t>0507-1307-4179</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8길 43 3층</t>
+          <t>서울특별시 종로구 종로12길 9 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/charles__nail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,7 +1250,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1284,14 +1260,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgtfw3e</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>48</v>
+        <v>529</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R9" t="n">
-        <v>48</v>
+        <v>585</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1845062262</t>
+          <t>13034248</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845062262</t>
+          <t>https://m.place.naver.com/place/13034248</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라라네일</t>
+          <t>르모네일스튜디오</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>redpepper30@naver.com</t>
+          <t>borareview@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1344-7250</t>
+          <t>0507-1374-9858</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+          <t>서울특별시 종로구 동숭4가길 2 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/_lmonail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,7 +1344,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1382,14 +1354,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4xnw0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1004</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>433</v>
+        <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>1437</v>
+        <v>24</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1303128966</t>
+          <t>1493224095</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303128966</t>
+          <t>https://m.place.naver.com/place/1493224095</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,25 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비조네일</t>
+          <t>네일 오우브</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ozllzln17@naver.com</t>
+          <t>keroo90@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1407-0437</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 379</t>
+          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.ouv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,7 +1438,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1487,17 +1459,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>155</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>19813956</t>
+          <t>1559030900</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19813956</t>
+          <t>https://m.place.naver.com/place/1559030900</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1528,29 +1500,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>삼층네일</t>
+          <t>네일라이트</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wang8241@naver.com</t>
+          <t>gahee1029@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1327-8241</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+          <t>서울특별시 종로구 세종대로23길 5 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/_nail_light_</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1560,7 +1528,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1570,14 +1538,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4wxd0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1585,17 +1549,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1604,12 +1568,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1894370134</t>
+          <t>1105652769</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1894370134</t>
+          <t>https://m.place.naver.com/place/1105652769</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1626,25 +1590,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아트만네일</t>
+          <t>루다네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ppangsun238@naver.com</t>
+          <t>rudanail1515@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1357-1516</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/rudanail_daehakro</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1654,7 +1622,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1679,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>254</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="R13" t="n">
-        <v>36</v>
+        <v>366</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1694,12 +1662,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1284929161</t>
+          <t>34551572</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284929161</t>
+          <t>https://m.place.naver.com/place/34551572</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1716,24 +1684,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>뷰티숲</t>
+          <t>JIN네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>smallwarestore@naver.com</t>
+          <t>jin_nail6453@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1438-7477</t>
+          <t>0507-1392-5159</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 37-29 103호</t>
+          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,14 +1726,10 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wn1n8nl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1773,17 +1737,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1792,12 +1756,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1158436638</t>
+          <t>1530291597</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158436638</t>
+          <t>https://m.place.naver.com/place/1530291597</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1814,12 +1778,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일&amp;페일아트</t>
+          <t>모스네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lsbangel@naver.com</t>
+          <t>buzzerrbeate@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1827,12 +1791,12 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 446</t>
+          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/moss.nail_</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1842,7 +1806,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1858,22 +1822,22 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>228</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>241</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1882,12 +1846,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>20871402</t>
+          <t>1061088069</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20871402</t>
+          <t>https://m.place.naver.com/place/1061088069</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1904,25 +1868,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>지아네일</t>
+          <t>엘로아네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jjaa1334@naver.com</t>
+          <t>hhhong88@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1314-9339</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 40 6층</t>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/eloa__nail/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1932,7 +1900,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1957,13 +1925,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1972,12 +1940,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1279897442</t>
+          <t>2087274322</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279897442</t>
+          <t>https://m.place.naver.com/place/2087274322</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1994,29 +1962,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제이뷰티 눈썹&amp;네일</t>
+          <t>무아네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jbeauty4022@naver.com</t>
+          <t>min_0_97@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1422-4022</t>
+          <t>0507-1436-1716</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
+          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mooa.shop?igsh=MXRtMm53dWt4NHdmNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2026,7 +1994,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2036,14 +2004,10 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc1nha</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>X</t>
@@ -2055,13 +2019,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3318</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3545</v>
+        <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2070,12 +2034,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1776791877</t>
+          <t>2038424794</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776791877</t>
+          <t>https://m.place.naver.com/place/2038424794</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2092,29 +2056,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>드로잉쇼</t>
+          <t>손톱그림</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>odshow@naver.com</t>
+          <t>on_calli@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>02-777-1090</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 60</t>
+          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_sketch_8478/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2124,7 +2084,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2145,17 +2105,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="R18" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2164,12 +2124,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1726036993</t>
+          <t>1124095560</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726036993</t>
+          <t>https://m.place.naver.com/place/1124095560</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2186,25 +2146,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>어나더네일</t>
+          <t>루아르블랑 네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>soojinpo@naver.com</t>
+          <t>democratic9b1@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1483-9411</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 56-1 1층</t>
+          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sHajSJei</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2214,7 +2178,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2230,7 +2194,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2239,13 +2203,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="R19" t="n">
-        <v>69</v>
+        <v>245</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2254,12 +2218,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1214193406</t>
+          <t>2013893243</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214193406</t>
+          <t>https://m.place.naver.com/place/2013893243</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2276,24 +2240,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일쏘이</t>
+          <t>아셀네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>asher9809@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1334-9677</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
+          <t>서울특별시 중구 장충단로 253 10층 11호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2329,17 +2289,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R20" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2348,12 +2308,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1009120766</t>
+          <t>1229434440</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009120766</t>
+          <t>https://m.place.naver.com/place/1229434440</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2370,29 +2330,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>찰스네일</t>
+          <t>뉴문네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>spotv_sports@naver.com</t>
+          <t>xdaredare@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1307-4179</t>
+          <t>0507-1354-6577</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로12길 9 3층</t>
+          <t>서울특별시 종로구 성균관로 7 2층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/newmoonnail_</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2402,7 +2362,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2412,14 +2372,10 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4z9vd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>X</t>
@@ -2431,13 +2387,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>529</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>585</v>
+        <v>154</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2446,12 +2402,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>13034248</t>
+          <t>1689136529</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13034248</t>
+          <t>https://m.place.naver.com/place/1689136529</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2468,24 +2424,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>프로뷰티</t>
+          <t>엔79 Nail</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>s7977@naver.com</t>
+          <t>loveucream@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1435-2789</t>
+          <t>0507-1390-0326</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8가길 9 3층</t>
+          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2510,32 +2466,28 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4tx88</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>572</v>
+        <v>163</v>
       </c>
       <c r="Q22" t="n">
-        <v>679</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>1251</v>
+        <v>182</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2544,12 +2496,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>19997455</t>
+          <t>1756267523</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19997455</t>
+          <t>https://m.place.naver.com/place/1756267523</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2566,29 +2518,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>꽁냥네일</t>
+          <t>네일, 사월</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ggongnyangnail@naver.com</t>
+          <t>pooddin@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0507-1418-2440</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 249-28 3층</t>
+          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail__april</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2598,7 +2546,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2608,17 +2556,13 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmdcq0x</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2627,13 +2571,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>277</v>
+        <v>652</v>
       </c>
       <c r="Q23" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="R23" t="n">
-        <v>319</v>
+        <v>666</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2642,12 +2586,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1570914826</t>
+          <t>1448977317</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570914826</t>
+          <t>https://m.place.naver.com/place/1448977317</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2664,25 +2608,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>살롱드소피</t>
+          <t>네일온 명동본점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>skincare25@naver.com</t>
+          <t>nailon_myeongdong@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1302-8995</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
+          <t>서울특별시 중구 을지로 88 을특8호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailon_myeongdong</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2692,24 +2640,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4t9x9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>X</t>
@@ -2721,13 +2665,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2736,12 +2680,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>13434920</t>
+          <t>2054691209</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13434920</t>
+          <t>https://m.place.naver.com/place/2054691209</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2758,29 +2702,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>올리브네일&amp;속눈썹</t>
+          <t>키튼네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>djdjqq1663@naver.com</t>
+          <t>dbgpwn0626@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-2075-7775</t>
+          <t>02-765-8566</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
+          <t>서울특별시 종로구 대학로 149 3층 키튼네일</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kitten_nail_/?igsh=aWNxNmptb2lzNGZ5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2790,7 +2734,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2800,17 +2744,13 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc3k0l</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2819,13 +2759,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3108</v>
+        <v>503</v>
       </c>
       <c r="Q25" t="n">
-        <v>253</v>
+        <v>54</v>
       </c>
       <c r="R25" t="n">
-        <v>3361</v>
+        <v>557</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2834,12 +2774,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>35751284</t>
+          <t>1065031131</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35751284</t>
+          <t>https://m.place.naver.com/place/1065031131</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2856,29 +2796,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>혜리앤케어</t>
+          <t>네일해썸</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>micahyesung@naver.com</t>
+          <t>llllcmalll@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02-725-1741</t>
+          <t>0507-1342-3168</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
+          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_hatssome</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2888,7 +2828,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2904,22 +2844,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2928,12 +2868,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>155402276</t>
+          <t>1991633917</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/155402276</t>
+          <t>https://m.place.naver.com/place/1991633917</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2950,24 +2890,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>안0네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kikiu30@naver.com</t>
+          <t>ysl6161015@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1378-0246</t>
+          <t>02-6052-7778</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 혜화로3길 5 아남아파트 상가 107호 비비네일</t>
+          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2992,32 +2932,28 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49p4h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1857</v>
+        <v>19</v>
       </c>
       <c r="Q27" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1918</v>
+        <v>19</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3026,12 +2962,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1712141242</t>
+          <t>1487336161</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712141242</t>
+          <t>https://m.place.naver.com/place/1487336161</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3048,12 +2984,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>페이브 네일 스튜디오</t>
+          <t>살롱드소피</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>twolf97@naver.com</t>
+          <t>skincare25@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -3061,12 +2997,12 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 상가 1층 134호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/salon_de_sophie_</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3076,7 +3012,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3092,7 +3028,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3101,13 +3037,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="R28" t="n">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3116,12 +3052,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1109114407</t>
+          <t>13434920</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109114407</t>
+          <t>https://m.place.naver.com/place/13434920</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3138,24 +3074,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>위치네일스 종로점</t>
+          <t>네일 을지로지하쇼핑센터3구역점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1364-9020</t>
+          <t>02-2278-2990</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 51</t>
+          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3191,17 +3127,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1062</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1211</v>
+        <v>6</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3210,12 +3146,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1543496206</t>
+          <t>37588249</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543496206</t>
+          <t>https://m.place.naver.com/place/37588249</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3232,29 +3168,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nail by Jade</t>
+          <t>드팜므</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>tomjelbbuu@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1360-1011</t>
+          <t>0507-1317-3395</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
+          <t>서울특별시 종로구 사직로8길 42 B110호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/defemmeeee</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3264,7 +3200,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3289,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="R30" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3304,12 +3240,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>944614599</t>
+          <t>1741921081</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/944614599</t>
+          <t>https://m.place.naver.com/place/1741921081</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3326,29 +3262,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JIN네일</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jin_nail6453@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1392-5159</t>
+          <t>0507-1322-4179</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 38-1 3층 302호</t>
+          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sdED0A2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3358,7 +3294,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3368,32 +3304,28 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w495rw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>64</v>
+        <v>249</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R31" t="n">
-        <v>65</v>
+        <v>264</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3402,12 +3334,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1530291597</t>
+          <t>1054499609</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1530291597</t>
+          <t>https://m.place.naver.com/place/1054499609</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3424,29 +3356,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아머네일</t>
+          <t>네일멜로우</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dntndus111@naver.com</t>
+          <t>qnlwls@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1364-4429</t>
+          <t>0507-1356-7672</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_mellow_11/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3456,7 +3388,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3466,17 +3398,13 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xtcw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3485,13 +3413,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>262</v>
+        <v>389</v>
       </c>
       <c r="Q32" t="n">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="R32" t="n">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3500,12 +3428,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1312237193</t>
+          <t>1933958367</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312237193</t>
+          <t>https://m.place.naver.com/place/1933958367</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3522,29 +3450,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GK네일 현대시티아울렛 동대문점</t>
+          <t>명동네일 제니뷰티</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nailgk_ddm@naver.com</t>
+          <t>hyoyeol@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1339-5357</t>
+          <t>0507-1487-9603</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
+          <t>서울특별시 중구 명동8길 43 3층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jennybeauty.md/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3554,7 +3482,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3564,14 +3492,10 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wk22ngu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>X</t>
@@ -3583,13 +3507,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>333</v>
+        <v>48</v>
       </c>
       <c r="Q33" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>379</v>
+        <v>48</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3598,12 +3522,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1245812382</t>
+          <t>1845062262</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245812382</t>
+          <t>https://m.place.naver.com/place/1845062262</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3620,25 +3544,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>살롱드벨르네일</t>
+          <t>블링네일 종로점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>salondebelle_nail@naver.com</t>
+          <t>beaulynail@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1448-0036</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 65 2층 208호</t>
+          <t>서울특별시 종로구 대학로 16-1 1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/beaulynail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3648,24 +3576,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vb7i</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>X</t>
@@ -3677,13 +3601,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>358</v>
+        <v>145</v>
       </c>
       <c r="Q34" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R34" t="n">
-        <v>419</v>
+        <v>218</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3692,12 +3616,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1768571536</t>
+          <t>60890323</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768571536</t>
+          <t>https://m.place.naver.com/place/60890323</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3714,29 +3638,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>맥스네일</t>
+          <t>꽃소니 네일아트</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>machojj@naver.com</t>
+          <t>qhpw4cpk@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02-2272-4141</t>
+          <t>070-8615-3478</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 204 3층</t>
+          <t>서울특별시 종로구 대학로5길 8 2층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/flower_handnails</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3746,7 +3670,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3756,14 +3680,10 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4xms2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3775,13 +3695,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="Q35" t="n">
-        <v>532</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>730</v>
+        <v>109</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3790,12 +3710,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>32786203</t>
+          <t>1593950281</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32786203</t>
+          <t>https://m.place.naver.com/place/1593950281</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3812,12 +3732,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>꾸미다</t>
+          <t>네일&amp;페일아트</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yem1104@naver.com</t>
+          <t>lsbangel@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3825,7 +3745,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
+          <t>서울특별시 종로구 진흥로 446</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3861,17 +3781,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3880,12 +3800,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1095499576</t>
+          <t>20871402</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095499576</t>
+          <t>https://m.place.naver.com/place/20871402</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3902,29 +3822,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>블링네일 종로점</t>
+          <t>nail by Jade</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>beaulynail@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1448-0036</t>
+          <t>0507-1360-1011</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 16-1 1층</t>
+          <t>서울특별시 종로구 진흥로 432 요진쉐레이 410호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_by_jade</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3934,7 +3854,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3944,14 +3864,10 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u1j6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -3963,13 +3879,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>145</v>
+        <v>27</v>
       </c>
       <c r="Q37" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>218</v>
+        <v>28</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3978,12 +3894,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>60890323</t>
+          <t>944614599</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60890323</t>
+          <t>https://m.place.naver.com/place/944614599</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4000,20 +3916,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>손톱그림</t>
+          <t>네일 김미쉘터</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>on_calli@naver.com</t>
+          <t>patent37435@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1320-1993</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 96 1층 손톱그림</t>
+          <t>서울특별시 종로구 필운대로 55</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4049,17 +3969,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3</v>
+        <v>267</v>
       </c>
       <c r="Q38" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>76</v>
+        <v>271</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4068,12 +3988,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1124095560</t>
+          <t>1802694964</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1124095560</t>
+          <t>https://m.place.naver.com/place/1802694964</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4090,29 +4010,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>가빈네일</t>
+          <t>Diamond Nails</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>happyhannj@naver.com</t>
+          <t>ksj673232@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1431-8259</t>
+          <t>0507-1420-1393</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
+          <t>서울특별시 중구 마른내로 155 1동 102호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4122,7 +4042,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4132,14 +4052,10 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzrw6v8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>X</t>
@@ -4151,13 +4067,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4166,12 +4082,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>38500996</t>
+          <t>2040524360</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38500996</t>
+          <t>https://m.place.naver.com/place/2040524360</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4188,24 +4104,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>디디 네일바</t>
+          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>heeja090@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1476-0228</t>
+          <t>02-756-4143</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
+          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4230,14 +4146,10 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r9nz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4245,17 +4157,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="Q40" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>213</v>
+        <v>4</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4264,12 +4176,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1134899134</t>
+          <t>31315234</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134899134</t>
+          <t>https://m.place.naver.com/place/31315234</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4286,29 +4198,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일브러쉬</t>
+          <t>파라테라피네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ss7370306@naver.com</t>
+          <t>anrgudtkd@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1332-0306</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail._.again</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4318,7 +4226,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4328,14 +4236,10 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lb8p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4343,17 +4247,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>65</v>
+        <v>291</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R41" t="n">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4362,12 +4266,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>35559430</t>
+          <t>1996157285</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35559430</t>
+          <t>https://m.place.naver.com/place/1996157285</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4384,29 +4288,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일 을지로지하쇼핑센터3구역점</t>
+          <t>9층네일 명동점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>dmgktnqls@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02-2278-2990</t>
+          <t>0507-1359-1372</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/9.nailstudio</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4416,7 +4320,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4437,17 +4341,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>259</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="R42" t="n">
-        <v>6</v>
+        <v>282</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4456,12 +4360,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>37588249</t>
+          <t>1681308543</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588249</t>
+          <t>https://m.place.naver.com/place/1681308543</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4478,12 +4382,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오토젯네일</t>
+          <t>네일지니</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>yr19850217@naver.com</t>
+          <t>1231yc@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -4491,17 +4395,17 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로 68</t>
+          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.autoznail.com/</t>
+          <t>http://pf.kakao.com/_xeTiCG</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4522,22 +4426,22 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1782</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1876</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4546,12 +4450,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>35506860</t>
+          <t>1073291540</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35506860</t>
+          <t>https://m.place.naver.com/place/1073291540</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4568,29 +4472,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일하트</t>
+          <t>살롱드벨르네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nailheart053@naver.com</t>
+          <t>salondebelle_nail@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1484-8604</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+          <t>서울특별시 종로구 종로 65 2층 208호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/salondebelle_nail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4600,12 +4500,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4621,17 +4521,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="Q44" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="R44" t="n">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4640,12 +4540,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1101101042</t>
+          <t>1768571536</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101101042</t>
+          <t>https://m.place.naver.com/place/1768571536</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4662,29 +4562,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>다리아네일 안국역</t>
+          <t>에이탑네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>puppyholic@naver.com</t>
+          <t>sara6297@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1347-1494</t>
+          <t>0507-1372-2148</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
+          <t>서울특별시 중구 명동4길 12-1 3층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/a.top_nail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4694,7 +4594,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4704,14 +4604,10 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h26k</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -4723,13 +4619,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>184</v>
+        <v>260</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="R45" t="n">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4738,12 +4634,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1165184706</t>
+          <t>1446197361</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165184706</t>
+          <t>https://m.place.naver.com/place/1446197361</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4760,29 +4656,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9층네일 명동점</t>
+          <t>디디 네일바</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dmgktnqls@naver.com</t>
+          <t>heeja090@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1359-1372</t>
+          <t>0507-1476-0228</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 25-1 303호</t>
+          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/didi___nailbar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4792,7 +4688,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4802,14 +4698,10 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tkwj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>X</t>
@@ -4821,13 +4713,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="Q46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R46" t="n">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4836,12 +4728,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1681308543</t>
+          <t>1134899134</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681308543</t>
+          <t>https://m.place.naver.com/place/1134899134</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4858,29 +4750,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
+          <t>삼층네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>wang8241@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>02-756-4143</t>
+          <t>0507-1327-8241</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wang8241</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4890,12 +4782,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4915,13 +4807,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>532</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R47" t="n">
-        <v>4</v>
+        <v>545</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4930,12 +4822,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>31315234</t>
+          <t>1894370134</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315234</t>
+          <t>https://m.place.naver.com/place/1894370134</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4952,29 +4844,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>에이커뷰티네일</t>
+          <t>마이파우치</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>happymin_life@naver.com</t>
+          <t>323redtree@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02-722-5558</t>
+          <t>0507-1402-0809</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
+          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mypouch.kangbbin</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4984,7 +4876,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5009,13 +4901,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>184</v>
       </c>
       <c r="R48" t="n">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5024,12 +4916,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1812848399</t>
+          <t>38642341</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1812848399</t>
+          <t>https://m.place.naver.com/place/38642341</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5046,29 +4938,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일 김미쉘터</t>
+          <t>위치네일스 종로점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>patent37435@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1320-1993</t>
+          <t>0507-1364-9020</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 55</t>
+          <t>서울특별시 종로구 종로 51</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5078,12 +4970,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5099,17 +4991,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>267</v>
+        <v>1063</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="R49" t="n">
-        <v>271</v>
+        <v>1213</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5118,12 +5010,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1802694964</t>
+          <t>1543496206</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802694964</t>
+          <t>https://m.place.naver.com/place/1543496206</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5140,29 +5032,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>바이올렛네일</t>
+          <t>네일하루</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>violet_nail@naver.com</t>
+          <t>nail_haru@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>02-2118-8867</t>
+          <t>0507-1361-1445</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 247 굿모닝시티 B2 6호</t>
+          <t>서울특별시 종로구 돈화문로8길 20 삼오빌딩 603호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nail_haru</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5172,12 +5064,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5197,13 +5089,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="R50" t="n">
-        <v>2</v>
+        <v>413</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5212,12 +5104,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>120895291</t>
+          <t>37089409</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/120895291</t>
+          <t>https://m.place.naver.com/place/37089409</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5234,34 +5126,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일바이안</t>
+          <t>이츠네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ye1yang@naver.com</t>
+          <t>icacc89@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>02-511-5621</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로9길 12 8층</t>
+          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyahn</t>
+          <t>http://pf.kakao.com/_duxhxdn</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5282,7 +5170,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5291,13 +5179,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5306,12 +5194,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1084164588</t>
+          <t>31949587</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084164588</t>
+          <t>https://m.place.naver.com/place/31949587</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5328,29 +5216,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Diamond Nails</t>
+          <t>오브 코코네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ksj673232@naver.com</t>
+          <t>9ansapres@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1420-1393</t>
+          <t>0507-1371-8921</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 155 1동 102호</t>
+          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ofconail</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5360,7 +5248,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5385,13 +5273,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5400,12 +5288,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2040524360</t>
+          <t>1009626425</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040524360</t>
+          <t>https://m.place.naver.com/place/1009626425</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5422,24 +5310,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>루이비네일</t>
+          <t>네일해요</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>zhengyinji888@naver.com</t>
+          <t>elliestar@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1445-2047</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
+          <t>서울특별시 종로구 종로44길 9 2층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5464,14 +5348,10 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o9ai</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5479,17 +5359,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>481</v>
+        <v>6</v>
       </c>
       <c r="Q53" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>570</v>
+        <v>6</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5498,12 +5378,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>21306056</t>
+          <t>1213168091</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21306056</t>
+          <t>https://m.place.naver.com/place/1213168091</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5520,29 +5400,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>드팜므</t>
+          <t>오토젯네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>tomjelbbuu@naver.com</t>
+          <t>sjy5846@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1317-3395</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 42 B110호</t>
+          <t>서울특별시 종로구 돈화문로 68</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.autoznail.com/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5552,7 +5428,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5562,14 +5438,10 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47zjl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>X</t>
@@ -5577,17 +5449,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5596,12 +5468,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1741921081</t>
+          <t>35506860</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1741921081</t>
+          <t>https://m.place.naver.com/place/35506860</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5618,29 +5490,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일문</t>
+          <t>드네일 광화문점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>llkn@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>02-730-0010</t>
+          <t>0507-1351-9192</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
+          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/de_nail_gwanghwamun</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5650,7 +5522,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5660,14 +5532,10 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4tymx</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>X</t>
@@ -5679,13 +5547,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>593</v>
+        <v>20</v>
       </c>
       <c r="Q55" t="n">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="R55" t="n">
-        <v>774</v>
+        <v>38</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5694,12 +5562,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13534535</t>
+          <t>1372444756</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13534535</t>
+          <t>https://m.place.naver.com/place/1372444756</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5716,29 +5584,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>오드리네일</t>
+          <t>다리아네일 안국역</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ej4480@naver.com</t>
+          <t>puppyholic@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>02-722-1384</t>
+          <t>0507-1347-1494</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
+          <t>서울특별시 종로구 윤보선길 10 2층 15호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/daria_nail_ssu</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5748,7 +5616,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5758,17 +5626,13 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47ux5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5777,13 +5641,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="Q56" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>484</v>
+        <v>186</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5792,12 +5656,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>13450587</t>
+          <t>1165184706</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13450587</t>
+          <t>https://m.place.naver.com/place/1165184706</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5814,29 +5678,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>베리네일</t>
+          <t>너 참 예쁘다</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yeonee09@naver.com</t>
+          <t>yuiu1401@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1419-6623</t>
+          <t>0507-1434-8892</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침3단지 1층 163</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/youarebeautiful_seoul</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5846,7 +5710,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5861,7 +5725,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c3px</t>
+          <t>https://talk.naver.com/ct/profile</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5875,13 +5739,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>77</v>
+        <v>529</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>843</v>
       </c>
       <c r="R57" t="n">
-        <v>84</v>
+        <v>1372</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5890,12 +5754,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1394925944</t>
+          <t>1466732665</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394925944</t>
+          <t>https://m.place.naver.com/place/1466732665</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5912,29 +5776,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일멜로우</t>
+          <t>바비 네일왁싱</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>qnlwls@naver.com</t>
+          <t>uchka247@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1356-7672</t>
+          <t>0507-1490-9887</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 54호, 경복궁역6번출구 지하로 통하는 상가입니다.</t>
+          <t>서울특별시 중구 을지로44길 6-9 4층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mellow_11/</t>
+          <t>https://www.instagram.com/barbie.waxnail</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5969,13 +5833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>389</v>
+        <v>159</v>
       </c>
       <c r="Q58" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>423</v>
+        <v>162</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5984,12 +5848,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1933958367</t>
+          <t>1019484164</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933958367</t>
+          <t>https://m.place.naver.com/place/1019484164</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6006,29 +5870,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일아토</t>
+          <t>맥스네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sk3374@naver.com</t>
+          <t>machojj@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1416-6630</t>
+          <t>02-2272-4141</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
+          <t>서울특별시 중구 퇴계로 204 3층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ato</t>
+          <t>https://blog.naver.com/machojj</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6043,7 +5907,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6063,13 +5927,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>532</v>
       </c>
       <c r="R59" t="n">
-        <v>214</v>
+        <v>730</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6078,12 +5942,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1446399532</t>
+          <t>32786203</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446399532</t>
+          <t>https://m.place.naver.com/place/32786203</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6100,24 +5964,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>바움네일</t>
+          <t>종로네일샵</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>harulov@naver.com</t>
+          <t>bitna0614@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1330-3151</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로9길 37 2층</t>
+          <t>서울특별시 종로구 종로 62</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6153,17 +6013,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>607</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6172,12 +6032,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1954514000</t>
+          <t>1928832758</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954514000</t>
+          <t>https://m.place.naver.com/place/1928832758</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6194,29 +6054,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>엘로아네일</t>
+          <t>프로뷰티</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hhhong88@naver.com</t>
+          <t>probeauty_blog@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1314-9339</t>
+          <t>0507-1435-2789</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+          <t>서울특별시 중구 명동8가길 9 3층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/probeauty_blog</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6226,12 +6086,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6251,13 +6111,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>12</v>
+        <v>572</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>679</v>
       </c>
       <c r="R61" t="n">
-        <v>12</v>
+        <v>1251</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6266,12 +6126,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2087274322</t>
+          <t>19997455</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087274322</t>
+          <t>https://m.place.naver.com/place/19997455</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6288,25 +6148,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일지니</t>
+          <t>리빈네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1231yc@naver.com</t>
+          <t>jcj0217@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1349-9808</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 236 이화빌딩 3층 302호 네일지니</t>
+          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/rivin_nail</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6316,7 +6180,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6326,17 +6190,13 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tyvk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6345,13 +6205,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1782</v>
+        <v>130</v>
       </c>
       <c r="Q62" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>1876</v>
+        <v>132</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6360,12 +6220,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1073291540</t>
+          <t>1315671750</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073291540</t>
+          <t>https://m.place.naver.com/place/1315671750</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6382,29 +6242,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>리빈네일</t>
+          <t>가빈네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jcj0217@naver.com</t>
+          <t>happyhannj@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1349-9808</t>
+          <t>0507-1431-8259</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 리빈네일</t>
+          <t>서울특별시 종로구 지봉로12가길 63 1층 가빈네일</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gabin_nail?igsh=aWYyaTM4OHVwZjV5</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6414,7 +6274,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6424,14 +6284,10 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5uqf9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6443,13 +6299,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="Q63" t="n">
         <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6458,12 +6314,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1315671750</t>
+          <t>38500996</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315671750</t>
+          <t>https://m.place.naver.com/place/38500996</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6480,24 +6336,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>무아네일</t>
+          <t>혜리앤케어</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>min_0_97@naver.com</t>
+          <t>micahyesung@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1436-1716</t>
+          <t>02-725-1741</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 경희궁1길 27 1층 흰색 가게</t>
+          <t>서울특별시 종로구 옥인길 22-1 도담빌딩 202호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6533,17 +6389,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6552,12 +6408,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2038424794</t>
+          <t>155402276</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038424794</t>
+          <t>https://m.place.naver.com/place/155402276</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6574,24 +6430,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>엔79 Nail</t>
+          <t>그리다네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>loveucream@naver.com</t>
+          <t>gridanail2@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1390-0326</t>
+          <t>02-745-8375</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
+          <t>서울특별시 종로구 대학로12길 77</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6616,14 +6472,10 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wh99veq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>X</t>
@@ -6635,13 +6487,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="Q65" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>182</v>
+        <v>23</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6650,12 +6502,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1756267523</t>
+          <t>142708597</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756267523</t>
+          <t>https://m.place.naver.com/place/142708597</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6672,29 +6524,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>루아르블랑 네일</t>
+          <t>지아네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>democratic9b1@naver.com</t>
+          <t>jjaa1334@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1483-9411</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
+          <t>서울특별시 중구 명동10길 40 6층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jeonjia9</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6704,7 +6552,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6714,17 +6562,13 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wq9b3dr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6733,13 +6577,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="Q66" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="R66" t="n">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6748,12 +6592,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2013893243</t>
+          <t>1279897442</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013893243</t>
+          <t>https://m.place.naver.com/place/1279897442</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6770,20 +6614,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>해피네일데이</t>
+          <t>네일로드</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>happynailday@naver.com</t>
+          <t>lordnail@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>02-734-1730</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
+          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6819,17 +6667,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6838,12 +6686,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>298136226</t>
+          <t>206289152</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/298136226</t>
+          <t>https://m.place.naver.com/place/206289152</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6860,20 +6708,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>이츠네일</t>
+          <t>드로잉쇼</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>icacc89@naver.com</t>
+          <t>odshow@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02-777-1090</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 19 로얄빌딩 지하 1층 10호</t>
+          <t>서울특별시 중구 남대문로 60</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6898,32 +6750,28 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wx4fz8y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6932,12 +6780,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>31949587</t>
+          <t>1726036993</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31949587</t>
+          <t>https://m.place.naver.com/place/1726036993</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6954,29 +6802,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>안0네일</t>
+          <t>제이뷰티 눈썹&amp;네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ysl6161015@naver.com</t>
+          <t>jbeauty4022@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>02-6052-7778</t>
+          <t>0507-1422-4022</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 101 1층 제1호</t>
+          <t>서울특별시 종로구 종로 19 4층 417-1호 제이뷰티</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jbeauty4022</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6986,12 +6834,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7007,17 +6855,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>19</v>
+        <v>3318</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="R69" t="n">
-        <v>19</v>
+        <v>3545</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7026,12 +6874,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1487336161</t>
+          <t>1776791877</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487336161</t>
+          <t>https://m.place.naver.com/place/1776791877</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7048,24 +6896,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>효녀네일</t>
+          <t>꾸밈네일아트</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hy0d0ng2@naver.com</t>
+          <t>fusion02@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1366-2991</t>
+          <t>02-733-7942</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
+          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7101,17 +6949,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R70" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7120,12 +6968,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2038116522</t>
+          <t>614593678</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038116522</t>
+          <t>https://m.place.naver.com/place/614593678</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7142,29 +6990,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>바비 네일왁싱</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>uchka247@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1490-9887</t>
+          <t>0507-1358-8653</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로44길 6-9 4층</t>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_lee____</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7174,7 +7022,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7184,14 +7032,10 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40lka</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>X</t>
@@ -7203,13 +7047,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R71" t="n">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7218,12 +7062,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1019484164</t>
+          <t>2065943871</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1019484164</t>
+          <t>https://m.place.naver.com/place/2065943871</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7240,29 +7084,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>르모네일스튜디오</t>
+          <t>릴리엔젤네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>borareview@naver.com</t>
+          <t>kiyu0987@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1374-9858</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동숭4가길 2 2층</t>
+          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/lilyangel_nail</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7272,7 +7112,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7297,13 +7137,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="Q72" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="R72" t="n">
-        <v>24</v>
+        <v>287</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7312,12 +7152,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1493224095</t>
+          <t>1110775717</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493224095</t>
+          <t>https://m.place.naver.com/place/1110775717</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7334,29 +7174,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>영심이손톱</t>
+          <t>바움네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>lovellies@naver.com</t>
+          <t>harulov@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>02-735-0031</t>
+          <t>0507-1330-3151</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 88 701호</t>
+          <t>서울특별시 종로구 대학로9길 37 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
+          <t>https://www.instagram.com/baum_nail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7391,13 +7231,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>560</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="R73" t="n">
-        <v>1</v>
+        <v>607</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7406,12 +7246,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1116851430</t>
+          <t>1954514000</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116851430</t>
+          <t>https://m.place.naver.com/place/1954514000</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7428,29 +7268,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>안젤라네일샵</t>
+          <t>네일원</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>angella3977@naver.com</t>
+          <t>nail_one@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1493-3335</t>
+          <t>0507-1338-0475</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
+          <t>서울특별시 종로구 지봉로 52-1 2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/_nail_one</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7460,7 +7300,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7470,14 +7310,10 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4tjk2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7489,13 +7325,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>664</v>
+        <v>3</v>
       </c>
       <c r="Q74" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>676</v>
+        <v>4</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7504,12 +7340,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1274163754</t>
+          <t>1105911364</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274163754</t>
+          <t>https://m.place.naver.com/place/1105911364</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7526,29 +7362,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>그리다네일</t>
+          <t>어나더네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>gridanail2@naver.com</t>
+          <t>soojinpo@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>02-745-8375</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로12길 77</t>
+          <t>서울특별시 종로구 지봉로 56-1 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/another_n_ail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7558,7 +7390,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7579,17 +7411,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="Q75" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R75" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7598,12 +7430,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>142708597</t>
+          <t>1214193406</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142708597</t>
+          <t>https://m.place.naver.com/place/1214193406</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7620,39 +7452,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일원</t>
+          <t>아트만네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>nail_one@naver.com</t>
+          <t>joy3345@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1338-0475</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 52-1 2층</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 508호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_Txkxgfxj</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7668,7 +7496,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7677,13 +7505,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R76" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7692,12 +7520,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1105911364</t>
+          <t>1284929161</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105911364</t>
+          <t>https://m.place.naver.com/place/1284929161</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7714,29 +7542,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일온 명동본점</t>
+          <t>강앤니네일스</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>nailon_myeongdong@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1302-8995</t>
+          <t>0507-1468-2316</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 을특8호</t>
+          <t>서울특별시 중구 장충단로 227-2 4층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon_myeongdong</t>
+          <t>http://instagram.com/kangannynails</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7751,7 +7579,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7771,13 +7599,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7786,12 +7614,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>2054691209</t>
+          <t>1711237836</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054691209</t>
+          <t>https://m.place.naver.com/place/1711237836</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7808,29 +7636,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>네일해썸</t>
+          <t>뷰티숲</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>llllcmalll@naver.com</t>
+          <t>smallwarestore@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1342-3168</t>
+          <t>0507-1438-7477</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 47 광화문미도파 1층 17-18호</t>
+          <t>서울특별시 종로구 지봉로 37-29 103호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hatssome</t>
+          <t>https://www.instagram.com/nailsoop_sj/</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7856,7 +7684,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7865,13 +7693,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="Q78" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7880,12 +7708,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1991633917</t>
+          <t>1158436638</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991633917</t>
+          <t>https://m.place.naver.com/place/1158436638</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7902,29 +7730,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>뉴문네일</t>
+          <t>핸더뷰티</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>xdaredare@naver.com</t>
+          <t>koenji_nail@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1354-6577</t>
+          <t>0507-1380-1146</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 7 2층</t>
+          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>http://instagram.com/newmoonnail_</t>
+          <t>https://blog.naver.com/koenji_nail</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7939,7 +7767,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7959,13 +7787,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>150</v>
+        <v>357</v>
       </c>
       <c r="Q79" t="n">
-        <v>4</v>
+        <v>412</v>
       </c>
       <c r="R79" t="n">
-        <v>154</v>
+        <v>769</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7974,12 +7802,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1689136529</t>
+          <t>37558905</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689136529</t>
+          <t>https://m.place.naver.com/place/37558905</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7996,29 +7824,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>꾸미다</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ysbfly@naver.com</t>
+          <t>yem1104@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0507-1358-8653</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+          <t>서울특별시 종로구 돈화문로6나길 35 (금강빌딩) 2층 209호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/ggumida._.nail?utm_source=qr&amp;igshid=MzNlNGNkZWQ4Mg%3D%3D</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8028,7 +7852,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -8038,14 +7862,10 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdlas59</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>X</t>
@@ -8057,13 +7877,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R80" t="n">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8072,12 +7892,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2065943871</t>
+          <t>1095499576</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065943871</t>
+          <t>https://m.place.naver.com/place/1095499576</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8094,25 +7914,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>네일해요</t>
+          <t>올리브네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>elliestar@naver.com</t>
+          <t>djdjqq1663@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>02-2075-7775</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로44길 9 2층</t>
+          <t>서울특별시 종로구 종로 19 르메이에르오피스텔상가 2층 올리브네일</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/djdjqq1663</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8122,12 +7946,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8138,22 +7962,22 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>6</v>
+        <v>3108</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="R81" t="n">
-        <v>6</v>
+        <v>3361</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8162,12 +7986,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1213168091</t>
+          <t>35751284</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213168091</t>
+          <t>https://m.place.naver.com/place/35751284</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8184,25 +8008,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>종로네일샵</t>
+          <t>네일브러쉬</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>bitna0614@naver.com</t>
+          <t>ss7370306@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1332-0306</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 62</t>
+          <t>서울특별시 종로구 종로 73 F-4,5호 종각지하상가 쇼핑센터</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ss7370306</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8212,12 +8040,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8237,13 +8065,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8252,12 +8080,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1928832758</t>
+          <t>35559430</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928832758</t>
+          <t>https://m.place.naver.com/place/35559430</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8274,20 +8102,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>아셀네일</t>
+          <t>바이올렛네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>asher9809@naver.com</t>
+          <t>violet_nail@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>02-2118-8867</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 253 10층 11호</t>
+          <t>서울특별시 중구 장충단로 247 굿모닝시티 B2 6호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8327,13 +8159,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8342,12 +8174,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1229434440</t>
+          <t>120895291</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229434440</t>
+          <t>https://m.place.naver.com/place/120895291</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8364,25 +8196,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>오프엠네일</t>
+          <t>안젤라네일샵</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ttmoong@naver.com</t>
+          <t>angella3977@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1493-3335</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 40 4층</t>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/angella3977</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8392,24 +8228,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9ohuf7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>X</t>
@@ -8417,17 +8249,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>104</v>
+        <v>664</v>
       </c>
       <c r="Q84" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R84" t="n">
-        <v>111</v>
+        <v>676</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8436,12 +8268,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>2099192808</t>
+          <t>1274163754</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099192808</t>
+          <t>https://m.place.naver.com/place/1274163754</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8458,39 +8290,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>굿모닝네일</t>
+          <t>르노브네일</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>clsrn9606@naver.com</t>
+          <t>hshee069@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1400-8607</t>
+          <t>0507-1307-5439</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+          <t>서울특별시 종로구 성균관로 38 1층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_XxbVPn</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8500,14 +8332,10 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wchx9q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>O</t>
@@ -8519,13 +8347,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>241</v>
+        <v>410</v>
       </c>
       <c r="Q85" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="R85" t="n">
-        <v>247</v>
+        <v>431</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8534,12 +8362,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>13051690</t>
+          <t>1890443515</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13051690</t>
+          <t>https://m.place.naver.com/place/1890443515</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8556,25 +8384,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>네일라이트</t>
+          <t>꽁냥네일</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>gahee1029@naver.com</t>
+          <t>qorgh1236@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1418-2440</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로23길 5 3층</t>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8584,7 +8416,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8609,13 +8441,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>540</v>
+        <v>277</v>
       </c>
       <c r="Q86" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="R86" t="n">
-        <v>546</v>
+        <v>319</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8624,12 +8456,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1105652769</t>
+          <t>1570914826</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105652769</t>
+          <t>https://m.place.naver.com/place/1570914826</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8646,29 +8478,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>드네일 광화문점</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>vin2roo@naver.com</t>
-        </is>
-      </c>
+          <t>네일쏘이</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1351-9192</t>
+          <t>0507-1334-9677</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 지하1층 115비-1-2호</t>
+          <t>서울특별시 종로구 자하문로5가길 24 2층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailssoi_</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8678,7 +8506,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8703,13 +8531,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="Q87" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8718,12 +8546,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1372444756</t>
+          <t>1009120766</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1372444756</t>
+          <t>https://m.place.naver.com/place/1009120766</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8740,39 +8568,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>꽃소니 네일아트</t>
+          <t>영심이손톱</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>qhpw4cpk@naver.com</t>
+          <t>lovellies@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>070-8615-3478</t>
+          <t>02-735-0031</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로5길 8 2층</t>
+          <t>서울특별시 종로구 종로 88 701호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://maps.app.goo.gl/KxNbf4uZuQY2QVSp9</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8782,14 +8610,10 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44hi0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>X</t>
@@ -8801,13 +8625,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8816,12 +8640,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1593950281</t>
+          <t>1116851430</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593950281</t>
+          <t>https://m.place.naver.com/place/1116851430</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8838,29 +8662,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>강앤니네일스</t>
+          <t>해피네일데이</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>happynailday@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0507-1468-2316</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 227-2 4층</t>
+          <t>서울특별시 종로구 창경궁로34길 18-4 3층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/happynailday</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8870,12 +8690,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8895,13 +8715,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="R89" t="n">
-        <v>1</v>
+        <v>353</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8910,12 +8730,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1711237836</t>
+          <t>298136226</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1711237836</t>
+          <t>https://m.place.naver.com/place/298136226</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8932,35 +8752,35 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>모스네일</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>buzzerrbeate@naver.com</t>
-        </is>
-      </c>
+          <t>아따걸네일</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1328-8505</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 87 2층 MOSS</t>
+          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_GWaij</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8970,14 +8790,10 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wu2321m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>O</t>
@@ -8989,13 +8805,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="Q90" t="n">
-        <v>13</v>
+        <v>649</v>
       </c>
       <c r="R90" t="n">
-        <v>241</v>
+        <v>934</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -9004,12 +8820,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1061088069</t>
+          <t>13047890</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061088069</t>
+          <t>https://m.place.naver.com/place/13047890</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -9026,29 +8842,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>네일로드</t>
+          <t>에이커뷰티네일</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>lordnail@naver.com</t>
+          <t>happymin_life@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>02-734-1730</t>
+          <t>02-722-5558</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 두산위브파빌리온 1층 111호</t>
+          <t>서울특별시 종로구 자하문로9길 30 1층 에이커뷰티네일</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/acre_beauty</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9058,7 +8874,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -9079,17 +8895,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9098,12 +8914,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>206289152</t>
+          <t>1812848399</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/206289152</t>
+          <t>https://m.place.naver.com/place/1812848399</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9120,20 +8936,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>리라뷰티</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>rira_225@naver.com</t>
+          <t>yeju0414@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>02-765-5525</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+          <t>서울특별시 종로구 지봉로 53-1 1층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9169,17 +8989,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="Q92" t="n">
-        <v>277</v>
+        <v>3</v>
       </c>
       <c r="R92" t="n">
-        <v>399</v>
+        <v>10</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9188,12 +9008,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1100664846</t>
+          <t>34352879</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100664846</t>
+          <t>https://m.place.naver.com/place/34352879</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9210,29 +9030,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>크리스탈손톱</t>
+          <t>페이브 네일 스튜디오</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>juyean123@naver.com</t>
+          <t>twolf97@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>02-3398-4445</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 275</t>
+          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하1층 110호</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sUKlei7f</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9242,7 +9058,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -9258,22 +9074,22 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="R93" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9282,12 +9098,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1895018257</t>
+          <t>1109114407</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895018257</t>
+          <t>https://m.place.naver.com/place/1109114407</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9304,20 +9120,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>네일, 사월</t>
+          <t>폭시네일</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>pooddin@naver.com</t>
+          <t>tomebooy@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1403-4791</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 81 1층 116호</t>
+          <t>서울특별시 종로구 동망산길 13 2층</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9342,14 +9162,10 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w408z4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>X</t>
@@ -9357,17 +9173,17 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>652</v>
+        <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>666</v>
+        <v>2</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9376,12 +9192,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1448977317</t>
+          <t>40986070</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448977317</t>
+          <t>https://m.place.naver.com/place/40986070</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9398,29 +9214,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>네일누하</t>
+          <t>그리드네일</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>annoi_@naver.com</t>
+          <t>boye_like@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1348-9398</t>
+          <t>0507-1405-0461</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
+          <t>서울특별시 종로구 옥인길 44</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/love_grid</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9430,7 +9246,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9455,13 +9271,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="Q95" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9470,12 +9286,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1370069746</t>
+          <t>38531607</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370069746</t>
+          <t>https://m.place.naver.com/place/38531607</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9492,29 +9308,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>그리드네일</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>boye_like@naver.com</t>
-        </is>
-      </c>
+          <t>굿모닝네일</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1405-0461</t>
+          <t>0507-1400-8607</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 옥인길 44</t>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9524,7 +9336,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9540,7 +9352,7 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -9549,13 +9361,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>53</v>
+        <v>241</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R96" t="n">
-        <v>55</v>
+        <v>247</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9564,12 +9376,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>38531607</t>
+          <t>13051690</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38531607</t>
+          <t>https://m.place.naver.com/place/13051690</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9586,29 +9398,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>루다네일</t>
+          <t>루이비네일</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>rudanail1515@naver.com</t>
+          <t>zhengyinji888@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1357-1516</t>
+          <t>0507-1445-2047</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로3길 11 2층 루다네일</t>
+          <t>서울특별시 종로구 창경궁로 258-14 2층</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/luyibi_nail8</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9618,7 +9430,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9634,7 +9446,7 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -9643,13 +9455,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>254</v>
+        <v>481</v>
       </c>
       <c r="Q97" t="n">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="R97" t="n">
-        <v>366</v>
+        <v>570</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9658,12 +9470,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>34551572</t>
+          <t>21306056</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34551572</t>
+          <t>https://m.place.naver.com/place/21306056</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9680,29 +9492,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>네일블라썸</t>
+          <t>말짜네일 광화문점</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>malzzanail@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1347-8173</t>
+          <t>0507-1402-3734</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 95호</t>
+          <t>서울특별시 종로구 종로 19 지하1층 비 122-1호 말짜네일</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/malzzanail</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9712,12 +9524,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -9728,22 +9540,22 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>334</v>
+        <v>306</v>
       </c>
       <c r="Q98" t="n">
-        <v>10</v>
+        <v>424</v>
       </c>
       <c r="R98" t="n">
-        <v>344</v>
+        <v>730</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9752,12 +9564,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1794862527</t>
+          <t>37997776</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794862527</t>
+          <t>https://m.place.naver.com/place/37997776</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9774,25 +9586,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>릴리엔젤네일</t>
+          <t>네일문</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>kiyu0987@naver.com</t>
+          <t>llkn@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>02-730-0010</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
+          <t>서울특별시 종로구 사직로8길 34 경희궁의아침 3단지 1층 125호</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailgate._.mr</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9802,7 +9618,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9812,14 +9628,10 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jrau</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>X</t>
@@ -9831,13 +9643,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>235</v>
+        <v>593</v>
       </c>
       <c r="Q99" t="n">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="R99" t="n">
-        <v>287</v>
+        <v>774</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9846,12 +9658,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1110775717</t>
+          <t>13534535</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110775717</t>
+          <t>https://m.place.naver.com/place/13534535</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9868,24 +9680,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>르노브네일</t>
+          <t>네일블라썸</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>hshee069@naver.com</t>
+          <t>wilklove@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1307-5439</t>
+          <t>0507-1347-8173</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 성균관로 38 1층</t>
+          <t>서울특별시 중구 소공로 102 95호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9910,32 +9722,28 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wiaq2sn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>410</v>
+        <v>334</v>
       </c>
       <c r="Q100" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="R100" t="n">
-        <v>431</v>
+        <v>344</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9944,12 +9752,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1890443515</t>
+          <t>1794862527</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1890443515</t>
+          <t>https://m.place.naver.com/place/1794862527</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9966,39 +9774,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>에이탑네일</t>
+          <t>아머네일</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>sara6297@naver.com</t>
+          <t>dntndus111@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1372-2148</t>
+          <t>0507-1364-4429</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 12-1 3층</t>
+          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_pzkMG</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10008,17 +9816,13 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwafe4o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10027,13 +9831,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q101" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="R101" t="n">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -10042,12 +9846,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1446197361</t>
+          <t>1312237193</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446197361</t>
+          <t>https://m.place.naver.com/place/1312237193</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -10064,29 +9868,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>꾸밈네일아트</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>fusion02@naver.com</t>
+          <t>052young@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>02-733-7942</t>
+          <t>02-319-7844</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로5길 13 변호사회관 지하1층</t>
+          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/navinailnavinail</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10096,7 +9900,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10117,17 +9921,17 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P102" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
-        <v>7</v>
-      </c>
       <c r="R102" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -10136,12 +9940,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>614593678</t>
+          <t>735546684</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/614593678</t>
+          <t>https://m.place.naver.com/place/735546684</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -10158,29 +9962,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>핸더뷰티</t>
+          <t>리라뷰티</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>koenji_nail@naver.com</t>
+          <t>rira_225@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0507-1380-1146</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 344 종로 대우디오빌 515호</t>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lira_4994/</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10190,7 +9990,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10215,13 +10015,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>357</v>
+        <v>122</v>
       </c>
       <c r="Q103" t="n">
-        <v>412</v>
+        <v>277</v>
       </c>
       <c r="R103" t="n">
-        <v>769</v>
+        <v>399</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10230,12 +10030,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>37558905</t>
+          <t>1100664846</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37558905</t>
+          <t>https://m.place.naver.com/place/1100664846</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -10252,39 +10052,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>오브 코코네일</t>
+          <t>미스에이 네일</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>9ansapres@naver.com</t>
+          <t>kinetixart@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1371-8921</t>
+          <t>070-8277-3597</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 77 통일 빌딩 2층 202호 코코네일</t>
+          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_jhDaG</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10294,17 +10094,13 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fdjhq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -10313,13 +10109,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>664</v>
+        <v>54</v>
       </c>
       <c r="Q104" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="R104" t="n">
-        <v>711</v>
+        <v>64</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10328,12 +10124,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1009626425</t>
+          <t>1758327919</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009626425</t>
+          <t>https://m.place.naver.com/place/1758327919</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10350,29 +10146,25 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>마이파우치</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>323redtree@naver.com</t>
-        </is>
-      </c>
+          <t>빌러브드 네일</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1402-0809</t>
+          <t>02-733-8318</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로52길 52 1층 우측 마이파우치</t>
+          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/beloved_nail_</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10382,7 +10174,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10392,14 +10184,10 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wrzgsow</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>X</t>
@@ -10411,13 +10199,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>11</v>
+        <v>371</v>
       </c>
       <c r="Q105" t="n">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="R105" t="n">
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10426,12 +10214,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>38642341</t>
+          <t>877681682</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38642341</t>
+          <t>https://m.place.naver.com/place/877681682</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10448,34 +10236,38 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>네일 오우브</t>
+          <t>레푸스 종로점</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>keroo90@naver.com</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>refuss_jong_ro@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>chy0802@ahasoft.co.kr</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1407-0437</t>
+          <t>02-720-4544</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 진흥로 464 1층 네일 오우브</t>
+          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/13/bizes/857013</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10505,13 +10297,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>154</v>
+        <v>863</v>
       </c>
       <c r="Q106" t="n">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="R106" t="n">
-        <v>155</v>
+        <v>1224</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10520,12 +10312,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1559030900</t>
+          <t>1237692187</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559030900</t>
+          <t>https://m.place.naver.com/place/1237692187</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10542,34 +10334,34 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>미스에이 네일</t>
+          <t>수야디나 네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>kinetixart@naver.com</t>
+          <t>purinxoxo@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>070-8277-3597</t>
+          <t>0507-1305-2499</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 155 경희궁자이 4단지 상가 1층</t>
+          <t>서울특별시 중구 충무로 36 2층</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_jhDaG</t>
+          <t>https://www.instagram.com/yun_ju423/</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10590,7 +10382,7 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -10599,13 +10391,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="Q107" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="R107" t="n">
-        <v>64</v>
+        <v>216</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10614,12 +10406,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1758327919</t>
+          <t>1324800762</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758327919</t>
+          <t>https://m.place.naver.com/place/1324800762</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10636,29 +10428,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>나비네일</t>
+          <t>베리네일</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>052young@naver.com</t>
+          <t>yeonee09@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>02-319-7844</t>
+          <t>0507-1419-6623</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
+          <t>서울특별시 종로구 종로 347 지하 143호 베리네일 (서울특별시 종로구 숭인동 76)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/berry_nail_</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10668,7 +10460,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10693,13 +10485,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="Q108" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R108" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10708,12 +10500,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>735546684</t>
+          <t>1394925944</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/735546684</t>
+          <t>https://m.place.naver.com/place/1394925944</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10730,24 +10522,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>비조네일</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>shoot13445@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>0507-1322-4179</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 57 3층 네일그리미</t>
+          <t>서울특별시 종로구 종로 379</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10778,22 +10566,22 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>249</v>
+        <v>4</v>
       </c>
       <c r="Q109" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>264</v>
+        <v>5</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10802,12 +10590,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1054499609</t>
+          <t>19813956</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054499609</t>
+          <t>https://m.place.naver.com/place/19813956</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10824,20 +10612,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>파라테라피네일</t>
+          <t>네일하트</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>anrgudtkd@naver.com</t>
+          <t>nailheart053@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0507-1484-8604</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 4 풍림스페이스본 상가 지하 1층</t>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10862,14 +10654,10 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46zas</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>X</t>
@@ -10877,17 +10665,17 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>291</v>
+        <v>373</v>
       </c>
       <c r="Q110" t="n">
         <v>9</v>
       </c>
       <c r="R110" t="n">
-        <v>300</v>
+        <v>382</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10896,12 +10684,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1996157285</t>
+          <t>1101101042</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996157285</t>
+          <t>https://m.place.naver.com/place/1101101042</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10918,29 +10706,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>레푸스 종로점</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>02-720-4544</t>
+          <t>02-722-1384</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 4층 420, 421-1호 레푸스종로점</t>
+          <t>서울특별시 종로구 새문안로 92 광화문 오피시아빌딩 지하1층 122호</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/audreynail_official</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10950,7 +10738,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -10960,17 +10748,13 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4d9xs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -10979,13 +10763,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>863</v>
+        <v>228</v>
       </c>
       <c r="Q111" t="n">
-        <v>361</v>
+        <v>256</v>
       </c>
       <c r="R111" t="n">
-        <v>1224</v>
+        <v>484</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10994,12 +10778,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1237692187</t>
+          <t>13450587</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237692187</t>
+          <t>https://m.place.naver.com/place/13450587</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -11016,24 +10800,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>폭시네일</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>tomebooy@naver.com</t>
-        </is>
-      </c>
+          <t>크리스탈손톱</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0507-1403-4791</t>
+          <t>02-3398-4445</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동망산길 13 2층</t>
+          <t>서울특별시 중구 장충단로 275</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11073,13 +10853,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q112" t="n">
         <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -11088,12 +10868,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>40986070</t>
+          <t>1895018257</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/40986070</t>
+          <t>https://m.place.naver.com/place/1895018257</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -11110,29 +10890,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>빌러브드 네일</t>
+          <t>네일누하</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>novembro_12@naver.com</t>
+          <t>annoi_@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>02-733-8318</t>
+          <t>0507-1348-9398</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 송월길 99 상가동 1층 202동 2144호</t>
+          <t>서울특별시 종로구 필운대로 29 4층(누하동)</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.nuha</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -11142,7 +10922,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -11167,13 +10947,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>371</v>
+        <v>16</v>
       </c>
       <c r="Q113" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="R113" t="n">
-        <v>400</v>
+        <v>34</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -11182,12 +10962,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>877681682</t>
+          <t>1370069746</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/877681682</t>
+          <t>https://m.place.naver.com/place/1370069746</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -11204,34 +10984,34 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>아따걸네일</t>
+          <t>네일,현</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>addagirl2@naver.com</t>
+          <t>qkrwlsk126@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1328-8505</t>
+          <t>0507-1316-0133</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 144 중원빌딩 메가커피 2층</t>
+          <t>서울특별시 종로구 사직로 130 적선현대빌딩 지하1층 67호(경복궁역6번출구연결된상가)</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_GWaij</t>
+          <t>https://www.instagram.com/nail_hyun.__</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -11252,7 +11032,7 @@
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -11261,13 +11041,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>285</v>
+        <v>174</v>
       </c>
       <c r="Q114" t="n">
-        <v>649</v>
+        <v>23</v>
       </c>
       <c r="R114" t="n">
-        <v>934</v>
+        <v>197</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11276,12 +11056,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>13047890</t>
+          <t>1120708839</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13047890</t>
+          <t>https://m.place.naver.com/place/1120708839</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
